--- a/AAII_Financials/Quarterly/WPP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WPP_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -793,22 +793,22 @@
         <v>5</v>
       </c>
       <c r="E8" s="3">
-        <v>8958600</v>
+        <v>9207800</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G8" s="3">
-        <v>9519600</v>
+        <v>9784400</v>
       </c>
       <c r="H8" s="3">
-        <v>4432700</v>
+        <v>4555900</v>
       </c>
       <c r="I8" s="3">
-        <v>8380600</v>
+        <v>8613700</v>
       </c>
       <c r="J8" s="3">
-        <v>8273100</v>
+        <v>8503100</v>
       </c>
       <c r="K8" s="3">
         <v>4106100</v>
@@ -882,22 +882,22 @@
         <v>5</v>
       </c>
       <c r="E9" s="3">
-        <v>7638400</v>
+        <v>7850800</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G9" s="3">
-        <v>7669400</v>
+        <v>7882700</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I9" s="3">
-        <v>7081500</v>
+        <v>7278400</v>
       </c>
       <c r="J9" s="3">
-        <v>6701000</v>
+        <v>6887300</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
@@ -971,22 +971,22 @@
         <v>5</v>
       </c>
       <c r="E10" s="3">
-        <v>1320200</v>
+        <v>1357000</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G10" s="3">
-        <v>1850200</v>
+        <v>1901700</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I10" s="3">
-        <v>1299200</v>
+        <v>1335300</v>
       </c>
       <c r="J10" s="3">
-        <v>1572100</v>
+        <v>1615800</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1277,16 +1277,16 @@
         <v>5</v>
       </c>
       <c r="G14" s="3">
-        <v>72200</v>
+        <v>74200</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I14" s="3">
+        <v>97000</v>
+      </c>
+      <c r="J14" s="3">
         <v>94400</v>
-      </c>
-      <c r="J14" s="3">
-        <v>91800</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
@@ -1479,22 +1479,22 @@
         <v>5</v>
       </c>
       <c r="E17" s="3">
-        <v>8578900</v>
+        <v>8817400</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G17" s="3">
-        <v>8575200</v>
+        <v>8813600</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I17" s="3">
-        <v>7806700</v>
+        <v>8023800</v>
       </c>
       <c r="J17" s="3">
-        <v>7440100</v>
+        <v>7647000</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>5</v>
@@ -1568,22 +1568,22 @@
         <v>5</v>
       </c>
       <c r="E18" s="3">
-        <v>379700</v>
+        <v>390300</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G18" s="3">
-        <v>944500</v>
+        <v>970700</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I18" s="3">
-        <v>573900</v>
+        <v>589900</v>
       </c>
       <c r="J18" s="3">
-        <v>832900</v>
+        <v>856100</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>5</v>
@@ -1690,22 +1690,22 @@
         <v>5</v>
       </c>
       <c r="E20" s="3">
-        <v>159900</v>
+        <v>164400</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G20" s="3">
-        <v>233900</v>
+        <v>240400</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I20" s="3">
-        <v>125200</v>
+        <v>128700</v>
       </c>
       <c r="J20" s="3">
-        <v>21300</v>
+        <v>21900</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>5</v>
@@ -1791,10 +1791,10 @@
         <v>5</v>
       </c>
       <c r="I21" s="3">
-        <v>343100</v>
+        <v>352700</v>
       </c>
       <c r="J21" s="3">
-        <v>1526400</v>
+        <v>1568900</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -1868,22 +1868,22 @@
         <v>5</v>
       </c>
       <c r="E22" s="3">
-        <v>286200</v>
+        <v>294200</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G22" s="3">
-        <v>258800</v>
+        <v>266000</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I22" s="3">
-        <v>179800</v>
+        <v>184800</v>
       </c>
       <c r="J22" s="3">
-        <v>164000</v>
+        <v>168600</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>5</v>
@@ -1957,22 +1957,22 @@
         <v>5</v>
       </c>
       <c r="E23" s="3">
-        <v>253500</v>
+        <v>260500</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G23" s="3">
-        <v>919500</v>
+        <v>945100</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I23" s="3">
-        <v>519300</v>
+        <v>533800</v>
       </c>
       <c r="J23" s="3">
-        <v>690300</v>
+        <v>709500</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>5</v>
@@ -2046,22 +2046,22 @@
         <v>5</v>
       </c>
       <c r="E24" s="3">
-        <v>68200</v>
+        <v>70100</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G24" s="3">
-        <v>331100</v>
+        <v>340300</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I24" s="3">
-        <v>145800</v>
+        <v>149800</v>
       </c>
       <c r="J24" s="3">
-        <v>152600</v>
+        <v>156800</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>5</v>
@@ -2224,22 +2224,22 @@
         <v>5</v>
       </c>
       <c r="E26" s="3">
-        <v>185200</v>
+        <v>190400</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G26" s="3">
-        <v>588400</v>
+        <v>604800</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I26" s="3">
-        <v>373500</v>
+        <v>383900</v>
       </c>
       <c r="J26" s="3">
-        <v>537700</v>
+        <v>552600</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>5</v>
@@ -2313,22 +2313,22 @@
         <v>5</v>
       </c>
       <c r="E27" s="3">
-        <v>138900</v>
+        <v>142800</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G27" s="3">
-        <v>527000</v>
+        <v>541700</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I27" s="3">
-        <v>320000</v>
+        <v>328800</v>
       </c>
       <c r="J27" s="3">
-        <v>477600</v>
+        <v>490900</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>5</v>
@@ -2758,22 +2758,22 @@
         <v>5</v>
       </c>
       <c r="E32" s="3">
-        <v>-159900</v>
+        <v>-164400</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G32" s="3">
-        <v>-233900</v>
+        <v>-240400</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I32" s="3">
-        <v>-125200</v>
+        <v>-128700</v>
       </c>
       <c r="J32" s="3">
-        <v>-21300</v>
+        <v>-21900</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>5</v>
@@ -2847,22 +2847,22 @@
         <v>5</v>
       </c>
       <c r="E33" s="3">
-        <v>138900</v>
+        <v>142800</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G33" s="3">
-        <v>527000</v>
+        <v>541700</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I33" s="3">
-        <v>320000</v>
+        <v>328800</v>
       </c>
       <c r="J33" s="3">
-        <v>477600</v>
+        <v>490900</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>5</v>
@@ -3025,22 +3025,22 @@
         <v>5</v>
       </c>
       <c r="E35" s="3">
-        <v>138900</v>
+        <v>142800</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G35" s="3">
-        <v>527000</v>
+        <v>541700</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I35" s="3">
-        <v>320000</v>
+        <v>328800</v>
       </c>
       <c r="J35" s="3">
-        <v>477600</v>
+        <v>490900</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>5</v>
@@ -3271,22 +3271,22 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2434800</v>
+        <v>2502500</v>
       </c>
       <c r="E41" s="3">
-        <v>3091000</v>
+        <v>3176900</v>
       </c>
       <c r="F41" s="3">
-        <v>2202100</v>
+        <v>2263300</v>
       </c>
       <c r="G41" s="3">
-        <v>4817100</v>
+        <v>4951100</v>
       </c>
       <c r="H41" s="3">
-        <v>4399300</v>
+        <v>4521600</v>
       </c>
       <c r="I41" s="3">
-        <v>16002600</v>
+        <v>16447600</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>5</v>
@@ -3449,22 +3449,22 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>13110800</v>
+        <v>13475400</v>
       </c>
       <c r="E43" s="3">
-        <v>14903000</v>
+        <v>15317400</v>
       </c>
       <c r="F43" s="3">
-        <v>13875600</v>
+        <v>14261500</v>
       </c>
       <c r="G43" s="3">
-        <v>13622900</v>
+        <v>14001700</v>
       </c>
       <c r="H43" s="3">
-        <v>12181800</v>
+        <v>12520600</v>
       </c>
       <c r="I43" s="3">
-        <v>13113400</v>
+        <v>13478100</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>5</v>
@@ -3538,22 +3538,22 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>363100</v>
+        <v>373200</v>
       </c>
       <c r="E44" s="3">
-        <v>437200</v>
+        <v>449300</v>
       </c>
       <c r="F44" s="3">
-        <v>426500</v>
+        <v>438400</v>
       </c>
       <c r="G44" s="3">
-        <v>315100</v>
+        <v>323900</v>
       </c>
       <c r="H44" s="3">
-        <v>346300</v>
+        <v>355900</v>
       </c>
       <c r="I44" s="3">
-        <v>327600</v>
+        <v>336800</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>5</v>
@@ -3627,22 +3627,22 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>382200</v>
+        <v>392900</v>
       </c>
       <c r="E45" s="3">
-        <v>299900</v>
+        <v>308200</v>
       </c>
       <c r="F45" s="3">
-        <v>368700</v>
+        <v>379000</v>
       </c>
       <c r="G45" s="3">
-        <v>270200</v>
+        <v>277700</v>
       </c>
       <c r="H45" s="3">
-        <v>331700</v>
+        <v>341000</v>
       </c>
       <c r="I45" s="3">
-        <v>308000</v>
+        <v>316600</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>5</v>
@@ -3716,22 +3716,22 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>16290900</v>
+        <v>16744000</v>
       </c>
       <c r="E46" s="3">
-        <v>18731000</v>
+        <v>19251800</v>
       </c>
       <c r="F46" s="3">
-        <v>16872900</v>
+        <v>17342100</v>
       </c>
       <c r="G46" s="3">
-        <v>19025300</v>
+        <v>19554400</v>
       </c>
       <c r="H46" s="3">
-        <v>17259100</v>
+        <v>17739100</v>
       </c>
       <c r="I46" s="3">
-        <v>29751700</v>
+        <v>30579100</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>5</v>
@@ -3805,22 +3805,22 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>847800</v>
+        <v>871400</v>
       </c>
       <c r="E47" s="3">
-        <v>929200</v>
+        <v>955000</v>
       </c>
       <c r="F47" s="3">
-        <v>961500</v>
+        <v>988200</v>
       </c>
       <c r="G47" s="3">
-        <v>964900</v>
+        <v>991800</v>
       </c>
       <c r="H47" s="3">
-        <v>1358000</v>
+        <v>1395700</v>
       </c>
       <c r="I47" s="3">
-        <v>921500</v>
+        <v>947100</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>5</v>
@@ -3894,22 +3894,22 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2973600</v>
+        <v>3056300</v>
       </c>
       <c r="E48" s="3">
-        <v>3137700</v>
+        <v>3225000</v>
       </c>
       <c r="F48" s="3">
-        <v>3008200</v>
+        <v>3091900</v>
       </c>
       <c r="G48" s="3">
-        <v>2842800</v>
+        <v>2921900</v>
       </c>
       <c r="H48" s="3">
-        <v>2811000</v>
+        <v>2889100</v>
       </c>
       <c r="I48" s="3">
-        <v>2847700</v>
+        <v>2926900</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
@@ -3983,22 +3983,22 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>12155000</v>
+        <v>12493000</v>
       </c>
       <c r="E49" s="3">
-        <v>12288500</v>
+        <v>12630200</v>
       </c>
       <c r="F49" s="3">
-        <v>12042100</v>
+        <v>12377000</v>
       </c>
       <c r="G49" s="3">
-        <v>11130400</v>
+        <v>11439900</v>
       </c>
       <c r="H49" s="3">
-        <v>10780300</v>
+        <v>11080100</v>
       </c>
       <c r="I49" s="3">
-        <v>10890100</v>
+        <v>11193000</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>5</v>
@@ -4250,22 +4250,22 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>551600</v>
+        <v>566900</v>
       </c>
       <c r="E52" s="3">
-        <v>670800</v>
+        <v>689400</v>
       </c>
       <c r="F52" s="3">
-        <v>631000</v>
+        <v>648500</v>
       </c>
       <c r="G52" s="3">
-        <v>613000</v>
+        <v>630000</v>
       </c>
       <c r="H52" s="3">
-        <v>328500</v>
+        <v>337600</v>
       </c>
       <c r="I52" s="3">
-        <v>457900</v>
+        <v>470600</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>5</v>
@@ -4428,22 +4428,22 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>32819000</v>
+        <v>33731600</v>
       </c>
       <c r="E54" s="3">
-        <v>35757200</v>
+        <v>36751600</v>
       </c>
       <c r="F54" s="3">
-        <v>33515700</v>
+        <v>34447700</v>
       </c>
       <c r="G54" s="3">
-        <v>34576500</v>
+        <v>35538100</v>
       </c>
       <c r="H54" s="3">
-        <v>32536800</v>
+        <v>33441700</v>
       </c>
       <c r="I54" s="3">
-        <v>44868900</v>
+        <v>46116700</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>5</v>
@@ -4583,22 +4583,22 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>11691900</v>
+        <v>12017100</v>
       </c>
       <c r="E57" s="3">
-        <v>13949700</v>
+        <v>14337600</v>
       </c>
       <c r="F57" s="3">
-        <v>12051700</v>
+        <v>12386800</v>
       </c>
       <c r="G57" s="3">
-        <v>13252700</v>
+        <v>13621300</v>
       </c>
       <c r="H57" s="3">
-        <v>11147900</v>
+        <v>11457900</v>
       </c>
       <c r="I57" s="3">
-        <v>12733900</v>
+        <v>13088000</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>5</v>
@@ -4672,22 +4672,22 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1725800</v>
+        <v>1773800</v>
       </c>
       <c r="E58" s="3">
-        <v>1800600</v>
+        <v>1850700</v>
       </c>
       <c r="F58" s="3">
-        <v>722900</v>
+        <v>743000</v>
       </c>
       <c r="G58" s="3">
-        <v>1050700</v>
+        <v>1079900</v>
       </c>
       <c r="H58" s="3">
-        <v>1328400</v>
+        <v>1365400</v>
       </c>
       <c r="I58" s="3">
-        <v>11094700</v>
+        <v>11403200</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>5</v>
@@ -4761,22 +4761,22 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5031300</v>
+        <v>5171200</v>
       </c>
       <c r="E59" s="3">
-        <v>6218600</v>
+        <v>6391600</v>
       </c>
       <c r="F59" s="3">
-        <v>5689000</v>
+        <v>5847200</v>
       </c>
       <c r="G59" s="3">
-        <v>6148400</v>
+        <v>6319400</v>
       </c>
       <c r="H59" s="3">
-        <v>5013400</v>
+        <v>5152800</v>
       </c>
       <c r="I59" s="3">
-        <v>4987000</v>
+        <v>5125600</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>5</v>
@@ -4850,22 +4850,22 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>18449000</v>
+        <v>18962000</v>
       </c>
       <c r="E60" s="3">
-        <v>21968900</v>
+        <v>22579900</v>
       </c>
       <c r="F60" s="3">
-        <v>18463600</v>
+        <v>18977100</v>
       </c>
       <c r="G60" s="3">
-        <v>20451800</v>
+        <v>21020500</v>
       </c>
       <c r="H60" s="3">
-        <v>17489700</v>
+        <v>17976100</v>
       </c>
       <c r="I60" s="3">
-        <v>28815500</v>
+        <v>29616900</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>5</v>
@@ -4939,22 +4939,22 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7746200</v>
+        <v>7961600</v>
       </c>
       <c r="E61" s="3">
-        <v>7108600</v>
+        <v>7306300</v>
       </c>
       <c r="F61" s="3">
-        <v>8011200</v>
+        <v>8234000</v>
       </c>
       <c r="G61" s="3">
-        <v>7417400</v>
+        <v>7623700</v>
       </c>
       <c r="H61" s="3">
-        <v>7563100</v>
+        <v>7773400</v>
       </c>
       <c r="I61" s="3">
-        <v>8446000</v>
+        <v>8680900</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -5028,22 +5028,22 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1580600</v>
+        <v>1624600</v>
       </c>
       <c r="E62" s="3">
-        <v>1518200</v>
+        <v>1560500</v>
       </c>
       <c r="F62" s="3">
-        <v>1743000</v>
+        <v>1791500</v>
       </c>
       <c r="G62" s="3">
-        <v>1659300</v>
+        <v>1705400</v>
       </c>
       <c r="H62" s="3">
-        <v>1525900</v>
+        <v>1568400</v>
       </c>
       <c r="I62" s="3">
-        <v>1342200</v>
+        <v>1379500</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>5</v>
@@ -5384,22 +5384,22 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>28306600</v>
+        <v>29093800</v>
       </c>
       <c r="E66" s="3">
-        <v>31190800</v>
+        <v>32058200</v>
       </c>
       <c r="F66" s="3">
-        <v>28811400</v>
+        <v>29612700</v>
       </c>
       <c r="G66" s="3">
-        <v>30090000</v>
+        <v>30926800</v>
       </c>
       <c r="H66" s="3">
-        <v>26965100</v>
+        <v>27714900</v>
       </c>
       <c r="I66" s="3">
-        <v>38998400</v>
+        <v>40082900</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>5</v>
@@ -5862,22 +5862,22 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4912000</v>
+        <v>5048600</v>
       </c>
       <c r="E72" s="3">
-        <v>5018100</v>
+        <v>5157700</v>
       </c>
       <c r="F72" s="3">
-        <v>5189700</v>
+        <v>5334000</v>
       </c>
       <c r="G72" s="3">
-        <v>5001400</v>
+        <v>5140400</v>
       </c>
       <c r="H72" s="3">
-        <v>6089700</v>
+        <v>6259100</v>
       </c>
       <c r="I72" s="3">
-        <v>6389600</v>
+        <v>6567300</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>5</v>
@@ -6218,22 +6218,22 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4512300</v>
+        <v>4637800</v>
       </c>
       <c r="E76" s="3">
-        <v>4566400</v>
+        <v>4693400</v>
       </c>
       <c r="F76" s="3">
-        <v>4704200</v>
+        <v>4835100</v>
       </c>
       <c r="G76" s="3">
-        <v>4486500</v>
+        <v>4611300</v>
       </c>
       <c r="H76" s="3">
-        <v>5571800</v>
+        <v>5726700</v>
       </c>
       <c r="I76" s="3">
-        <v>5870500</v>
+        <v>6033800</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>5</v>
@@ -6493,22 +6493,22 @@
         <v>5</v>
       </c>
       <c r="E81" s="3">
-        <v>138900</v>
+        <v>142800</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G81" s="3">
-        <v>527000</v>
+        <v>541700</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I81" s="3">
-        <v>320000</v>
+        <v>328800</v>
       </c>
       <c r="J81" s="3">
-        <v>477600</v>
+        <v>490900</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>5</v>
@@ -6627,10 +6627,10 @@
         <v>5</v>
       </c>
       <c r="I83" s="3">
-        <v>-348100</v>
+        <v>-357800</v>
       </c>
       <c r="J83" s="3">
-        <v>647500</v>
+        <v>665500</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>5</v>
@@ -7161,10 +7161,10 @@
         <v>5</v>
       </c>
       <c r="I89" s="3">
-        <v>-3900000</v>
+        <v>-4008400</v>
       </c>
       <c r="J89" s="3">
-        <v>2521900</v>
+        <v>2592000</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>5</v>
@@ -7550,10 +7550,10 @@
         <v>5</v>
       </c>
       <c r="I94" s="3">
-        <v>566000</v>
+        <v>581700</v>
       </c>
       <c r="J94" s="3">
-        <v>-796700</v>
+        <v>-818900</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>5</v>
@@ -7675,7 +7675,7 @@
         <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>-390400</v>
+        <v>-401300</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8028,10 +8028,10 @@
         <v>5</v>
       </c>
       <c r="I100" s="3">
-        <v>1506700</v>
+        <v>1548600</v>
       </c>
       <c r="J100" s="3">
-        <v>-2551900</v>
+        <v>-2622900</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>5</v>
@@ -8117,10 +8117,10 @@
         <v>5</v>
       </c>
       <c r="I101" s="3">
-        <v>270600</v>
+        <v>278100</v>
       </c>
       <c r="J101" s="3">
-        <v>-161400</v>
+        <v>-165900</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>5</v>
@@ -8206,10 +8206,10 @@
         <v>5</v>
       </c>
       <c r="I102" s="3">
-        <v>-1556700</v>
+        <v>-1600000</v>
       </c>
       <c r="J102" s="3">
-        <v>-988100</v>
+        <v>-1015600</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>5</v>

--- a/AAII_Financials/Quarterly/WPP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WPP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="92">
   <si>
     <t>WPP</t>
   </si>
@@ -656,136 +656,143 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -793,88 +800,94 @@
         <v>5</v>
       </c>
       <c r="E8" s="3">
-        <v>9207800</v>
+        <v>9755200</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G8" s="3">
-        <v>9784400</v>
-      </c>
-      <c r="H8" s="3">
-        <v>4555900</v>
+        <v>9240300</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I8" s="3">
+        <v>9819000</v>
+      </c>
+      <c r="J8" s="3">
+        <v>4572000</v>
+      </c>
+      <c r="K8" s="3">
         <v>8613700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>8503100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>4106100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>7609200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>3454700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>7656000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>3512000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>6810300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>3811700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>9363600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>5576900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>8744700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>4927000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>7335700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>4628400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>9686600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>4595900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>10635100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>4759400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>9978500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>4831200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>10340000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>4754900</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -882,88 +895,94 @@
         <v>5</v>
       </c>
       <c r="E9" s="3">
-        <v>7850800</v>
+        <v>7893700</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G9" s="3">
-        <v>7882700</v>
+        <v>7878600</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I9" s="3">
+        <v>7910500</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K9" s="3">
         <v>7278400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>6887300</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" s="3">
         <v>6447300</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="3">
         <v>6181000</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3">
         <v>5861300</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="3">
         <v>7495800</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V9" s="3">
         <v>7317500</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X9" s="3">
         <v>5732800</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="3">
         <v>8039600</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB9" s="3">
         <v>8278100</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD9" s="3">
         <v>8194100</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF9" s="3">
         <v>13701700</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -971,88 +990,94 @@
         <v>5</v>
       </c>
       <c r="E10" s="3">
-        <v>1357000</v>
+        <v>1861600</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G10" s="3">
-        <v>1901700</v>
+        <v>1361800</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I10" s="3">
+        <v>1908400</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K10" s="3">
         <v>1335300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1615800</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N10" s="3">
         <v>1161900</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="3">
         <v>1475000</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3">
         <v>949100</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="3">
         <v>1867800</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="3">
         <v>1427300</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X10" s="3">
         <v>1602900</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z10" s="3">
         <v>1647000</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB10" s="3">
         <v>2357000</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD10" s="3">
         <v>1784400</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF10" s="3">
         <v>-3361800</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,8 +1109,10 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1173,8 +1200,14 @@
       <c r="AE12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,97 +1295,109 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
+      <c r="E14" s="3">
+        <v>-43500</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="3">
-        <v>74200</v>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I14" s="3">
+        <v>74500</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3">
         <v>97000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>94400</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>-14500</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
         <v>112900</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>62700</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
         <v>46600</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
         <v>18700</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="3">
         <v>17300</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z14" s="3">
         <v>36700</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD14" s="3">
         <v>25300</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF14" s="3">
         <v>-295800</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1410,11 +1455,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W15" s="3" t="s">
-        <v>5</v>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>5</v>
@@ -1428,20 +1473,26 @@
       <c r="AA15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AB15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD15" s="3">
         <v>127600</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF15" s="3">
         <v>119600</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,8 +1521,10 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1479,88 +1532,94 @@
         <v>5</v>
       </c>
       <c r="E17" s="3">
-        <v>8817400</v>
+        <v>9423900</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G17" s="3">
-        <v>8813600</v>
+        <v>8848600</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I17" s="3">
+        <v>8844800</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K17" s="3">
         <v>8023800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>7647000</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N17" s="3">
         <v>6994600</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P17" s="3">
         <v>7559900</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="3">
         <v>10228500</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T17" s="3">
         <v>8456200</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V17" s="3">
         <v>7944600</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X17" s="3">
         <v>6829900</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z17" s="3">
         <v>8634900</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB17" s="3">
         <v>9091000</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD17" s="3">
         <v>9033700</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF17" s="3">
         <v>8352300</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1568,88 +1627,94 @@
         <v>5</v>
       </c>
       <c r="E18" s="3">
-        <v>390300</v>
+        <v>331300</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G18" s="3">
-        <v>970700</v>
+        <v>391700</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I18" s="3">
+        <v>974200</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K18" s="3">
         <v>589900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>856100</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N18" s="3">
         <v>614600</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P18" s="3">
         <v>96100</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="3">
         <v>-3418200</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T18" s="3">
         <v>907500</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V18" s="3">
         <v>800200</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X18" s="3">
         <v>505700</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z18" s="3">
         <v>1051700</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB18" s="3">
         <v>1544000</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD18" s="3">
         <v>944800</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF18" s="3">
         <v>1987700</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,8 +1746,10 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1690,177 +1757,189 @@
         <v>5</v>
       </c>
       <c r="E20" s="3">
-        <v>164400</v>
+        <v>39800</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G20" s="3">
-        <v>240400</v>
+        <v>164900</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I20" s="3">
+        <v>241200</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
         <v>128700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>21900</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>57400</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3">
         <v>-164900</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>-265800</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T20" s="3">
         <v>429700</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V20" s="3">
         <v>3800</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X20" s="3">
         <v>224700</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z20" s="3">
         <v>210900</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB20" s="3">
         <v>361800</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD20" s="3">
         <v>239100</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF20" s="3">
         <v>109800</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>5</v>
+      <c r="E21" s="3">
+        <v>1874100</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>5</v>
+      <c r="G21" s="3">
+        <v>887500</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I21" s="3">
+        <v>1871900</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K21" s="3">
         <v>352700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1568900</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
         <v>683700</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3">
         <v>1782500</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3">
         <v>1298100</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="3">
         <v>1169300</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="3">
         <v>1536000</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB21" s="3">
         <v>2206400</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="3">
         <v>1486100</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF21" s="3">
         <v>2400000</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1868,88 +1947,94 @@
         <v>5</v>
       </c>
       <c r="E22" s="3">
-        <v>294200</v>
+        <v>189400</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G22" s="3">
-        <v>266000</v>
+        <v>295200</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I22" s="3">
+        <v>266900</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K22" s="3">
         <v>184800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>168600</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N22" s="3">
         <v>182600</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P22" s="3">
         <v>180700</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R22" s="3">
         <v>191900</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T22" s="3">
         <v>238900</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V22" s="3">
         <v>242400</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X22" s="3">
         <v>187400</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z22" s="3">
         <v>168200</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB22" s="3">
         <v>171000</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD22" s="3">
         <v>167600</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF22" s="3">
         <v>167900</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1957,88 +2042,94 @@
         <v>5</v>
       </c>
       <c r="E23" s="3">
-        <v>260500</v>
+        <v>181700</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G23" s="3">
-        <v>945100</v>
+        <v>261400</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I23" s="3">
+        <v>948400</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K23" s="3">
         <v>533800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>709500</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N23" s="3">
         <v>489400</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P23" s="3">
         <v>-249500</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R23" s="3">
         <v>-3875900</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T23" s="3">
         <v>1098300</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V23" s="3">
         <v>561600</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X23" s="3">
         <v>543000</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z23" s="3">
         <v>1094400</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB23" s="3">
         <v>1734900</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD23" s="3">
         <v>1016300</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF23" s="3">
         <v>1929600</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2046,88 +2137,94 @@
         <v>5</v>
       </c>
       <c r="E24" s="3">
-        <v>70100</v>
+        <v>120400</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G24" s="3">
-        <v>340300</v>
+        <v>70400</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I24" s="3">
+        <v>341500</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K24" s="3">
         <v>149800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>156800</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N24" s="3">
         <v>132900</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P24" s="3">
         <v>125600</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" s="3">
         <v>13300</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T24" s="3">
         <v>226000</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V24" s="3">
         <v>150100</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X24" s="3">
         <v>151900</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z24" s="3">
         <v>182300</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB24" s="3">
         <v>335900</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD24" s="3">
         <v>189800</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF24" s="3">
         <v>323700</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,8 +2312,14 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2224,88 +2327,94 @@
         <v>5</v>
       </c>
       <c r="E26" s="3">
-        <v>190400</v>
+        <v>61300</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G26" s="3">
-        <v>604800</v>
+        <v>191000</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I26" s="3">
+        <v>606900</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K26" s="3">
         <v>383900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>552600</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N26" s="3">
         <v>356500</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P26" s="3">
         <v>-375000</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R26" s="3">
         <v>-3889200</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T26" s="3">
         <v>872300</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V26" s="3">
         <v>411500</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X26" s="3">
         <v>391100</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z26" s="3">
         <v>912100</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB26" s="3">
         <v>1399000</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD26" s="3">
         <v>826500</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF26" s="3">
         <v>1606000</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2313,88 +2422,94 @@
         <v>5</v>
       </c>
       <c r="E27" s="3">
-        <v>142800</v>
+        <v>-2000</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G27" s="3">
-        <v>541700</v>
+        <v>143300</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I27" s="3">
+        <v>543600</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K27" s="3">
         <v>328800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>490900</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N27" s="3">
         <v>313600</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P27" s="3">
         <v>-414200</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R27" s="3">
         <v>-3914900</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T27" s="3">
         <v>805900</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V27" s="3">
         <v>369700</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X27" s="3">
         <v>348800</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z27" s="3">
         <v>869300</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB27" s="3">
         <v>1323200</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD27" s="3">
         <v>777500</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF27" s="3">
         <v>1520000</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2597,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2496,17 +2617,17 @@
       <c r="F29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
+      <c r="G29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>5</v>
@@ -2518,50 +2639,50 @@
         <v>5</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P29" s="3">
         <v>15900</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R29" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T29" s="3">
         <v>-64100</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V29" s="3">
         <v>59300</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X29" s="3">
         <v>166900</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB29" s="3">
         <v>268700</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2571,8 +2692,14 @@
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2787,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2882,14 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2758,88 +2897,94 @@
         <v>5</v>
       </c>
       <c r="E32" s="3">
-        <v>-164400</v>
+        <v>-39800</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G32" s="3">
-        <v>-240400</v>
+        <v>-164900</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I32" s="3">
+        <v>-241200</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
         <v>-128700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-21900</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>-57400</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3">
         <v>164900</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>265800</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T32" s="3">
         <v>-429700</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V32" s="3">
         <v>-3800</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X32" s="3">
         <v>-224700</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-210900</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-361800</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-239100</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-109800</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2847,88 +2992,94 @@
         <v>5</v>
       </c>
       <c r="E33" s="3">
-        <v>142800</v>
+        <v>-2000</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G33" s="3">
-        <v>541700</v>
+        <v>143300</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I33" s="3">
+        <v>543600</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K33" s="3">
         <v>328800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>490900</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N33" s="3">
         <v>313600</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P33" s="3">
         <v>-398300</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R33" s="3">
         <v>-3923200</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T33" s="3">
         <v>741800</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V33" s="3">
         <v>429000</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X33" s="3">
         <v>515800</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z33" s="3">
         <v>869300</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB33" s="3">
         <v>1591900</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD33" s="3">
         <v>777500</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF33" s="3">
         <v>1520000</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,8 +3167,14 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3025,182 +3182,194 @@
         <v>5</v>
       </c>
       <c r="E35" s="3">
-        <v>142800</v>
+        <v>-2000</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G35" s="3">
-        <v>541700</v>
+        <v>143300</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I35" s="3">
+        <v>543600</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K35" s="3">
         <v>328800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>490900</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N35" s="3">
         <v>313600</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P35" s="3">
         <v>-398300</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R35" s="3">
         <v>-3923200</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T35" s="3">
         <v>741800</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V35" s="3">
         <v>429000</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X35" s="3">
         <v>515800</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z35" s="3">
         <v>869300</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB35" s="3">
         <v>1591900</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD35" s="3">
         <v>777500</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF35" s="3">
         <v>1520000</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3401,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,97 +3436,105 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2502500</v>
+        <v>2837500</v>
       </c>
       <c r="E41" s="3">
-        <v>3176900</v>
+        <v>2511400</v>
       </c>
       <c r="F41" s="3">
-        <v>2263300</v>
+        <v>3188100</v>
       </c>
       <c r="G41" s="3">
-        <v>4951100</v>
+        <v>2271300</v>
       </c>
       <c r="H41" s="3">
-        <v>4521600</v>
+        <v>4968600</v>
       </c>
       <c r="I41" s="3">
+        <v>4537600</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K41" s="3">
         <v>16447600</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O41" s="3">
         <v>13482200</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R41" s="3">
+      <c r="R41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T41" s="3">
         <v>15418600</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V41" s="3">
         <v>2984200</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X41" s="3">
         <v>3491100</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z41" s="3">
         <v>2871300</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB41" s="3">
         <v>3119100</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD41" s="3">
         <v>3725100</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF41" s="3">
         <v>2970900</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3425,11 +3604,11 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA42" s="3" t="s">
-        <v>5</v>
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3">
+        <v>0</v>
       </c>
       <c r="AB42" s="3" t="s">
         <v>5</v>
@@ -3437,637 +3616,685 @@
       <c r="AC42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AD42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF42" s="3">
         <v>237900</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>13475400</v>
+        <v>14346900</v>
       </c>
       <c r="E43" s="3">
-        <v>15317400</v>
+        <v>13523000</v>
       </c>
       <c r="F43" s="3">
-        <v>14261500</v>
+        <v>15371600</v>
       </c>
       <c r="G43" s="3">
-        <v>14001700</v>
+        <v>14311900</v>
       </c>
       <c r="H43" s="3">
-        <v>12520600</v>
+        <v>14051300</v>
       </c>
       <c r="I43" s="3">
+        <v>12564900</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K43" s="3">
         <v>13478100</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O43" s="3">
         <v>27605700</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R43" s="3">
+      <c r="R43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T43" s="3">
         <v>15478600</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V43" s="3">
         <v>17299200</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X43" s="3">
         <v>16701500</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z43" s="3">
         <v>15659500</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB43" s="3">
         <v>15736500</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD43" s="3">
         <v>14605800</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF43" s="3">
         <v>16171500</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>373200</v>
+        <v>350100</v>
       </c>
       <c r="E44" s="3">
-        <v>449300</v>
+        <v>374500</v>
       </c>
       <c r="F44" s="3">
-        <v>438400</v>
+        <v>450900</v>
       </c>
       <c r="G44" s="3">
-        <v>323900</v>
+        <v>439900</v>
       </c>
       <c r="H44" s="3">
-        <v>355900</v>
+        <v>325000</v>
       </c>
       <c r="I44" s="3">
+        <v>357100</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K44" s="3">
         <v>336800</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O44" s="3">
         <v>416800</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R44" s="3">
+      <c r="R44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T44" s="3">
         <v>476600</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V44" s="3">
         <v>576100</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X44" s="3">
         <v>484100</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z44" s="3">
         <v>524600</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB44" s="3">
         <v>1076600</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD44" s="3">
         <v>1113600</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF44" s="3">
         <v>527200</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>392900</v>
+        <v>307900</v>
       </c>
       <c r="E45" s="3">
-        <v>308200</v>
+        <v>394200</v>
       </c>
       <c r="F45" s="3">
-        <v>379000</v>
+        <v>309300</v>
       </c>
       <c r="G45" s="3">
-        <v>277700</v>
+        <v>380300</v>
       </c>
       <c r="H45" s="3">
-        <v>341000</v>
+        <v>278700</v>
       </c>
       <c r="I45" s="3">
+        <v>342200</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K45" s="3">
         <v>316600</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O45" s="3">
         <v>922800</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R45" s="3">
+      <c r="R45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T45" s="3">
         <v>1055300</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V45" s="3">
         <v>550600</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X45" s="3">
         <v>381200</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z45" s="3">
         <v>546200</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB45" s="3">
         <v>390400</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD45" s="3">
         <v>529400</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF45" s="3">
         <v>427600</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>16744000</v>
+        <v>17842400</v>
       </c>
       <c r="E46" s="3">
-        <v>19251800</v>
+        <v>16803200</v>
       </c>
       <c r="F46" s="3">
-        <v>17342100</v>
+        <v>19319900</v>
       </c>
       <c r="G46" s="3">
-        <v>19554400</v>
+        <v>17403500</v>
       </c>
       <c r="H46" s="3">
-        <v>17739100</v>
+        <v>19623600</v>
       </c>
       <c r="I46" s="3">
+        <v>17801800</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K46" s="3">
         <v>30579100</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O46" s="3">
         <v>28329100</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R46" s="3">
+      <c r="R46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T46" s="3">
         <v>32429200</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V46" s="3">
         <v>21410100</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X46" s="3">
         <v>21057900</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z46" s="3">
         <v>19601700</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB46" s="3">
         <v>19769200</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD46" s="3">
         <v>19395900</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF46" s="3">
         <v>20335200</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>871400</v>
+        <v>890200</v>
       </c>
       <c r="E47" s="3">
-        <v>955000</v>
+        <v>874500</v>
       </c>
       <c r="F47" s="3">
-        <v>988200</v>
+        <v>958400</v>
       </c>
       <c r="G47" s="3">
-        <v>991800</v>
+        <v>991700</v>
       </c>
       <c r="H47" s="3">
-        <v>1395700</v>
+        <v>995300</v>
       </c>
       <c r="I47" s="3">
+        <v>1400700</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K47" s="3">
         <v>947100</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O47" s="3">
         <v>1727800</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R47" s="3">
+      <c r="R47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T47" s="3">
         <v>1788300</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V47" s="3">
         <v>1804800</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X47" s="3">
         <v>1933000</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z47" s="3">
         <v>2366400</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB47" s="3">
         <v>2893900</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD47" s="3">
         <v>3138300</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF47" s="3">
         <v>3133600</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3056300</v>
+        <v>2828800</v>
       </c>
       <c r="E48" s="3">
-        <v>3225000</v>
+        <v>3067100</v>
       </c>
       <c r="F48" s="3">
-        <v>3091900</v>
+        <v>3236400</v>
       </c>
       <c r="G48" s="3">
-        <v>2921900</v>
+        <v>3102800</v>
       </c>
       <c r="H48" s="3">
-        <v>2889100</v>
+        <v>2932200</v>
       </c>
       <c r="I48" s="3">
+        <v>2899300</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K48" s="3">
         <v>2926900</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O48" s="3">
         <v>3113000</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R48" s="3">
+      <c r="R48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T48" s="3">
         <v>3560200</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V48" s="3">
         <v>3858100</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X48" s="3">
         <v>1430400</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z48" s="3">
         <v>1332600</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB48" s="3">
         <v>1277600</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD48" s="3">
         <v>1213700</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF48" s="3">
         <v>1275600</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>12493000</v>
+        <v>11822100</v>
       </c>
       <c r="E49" s="3">
-        <v>12630200</v>
+        <v>12537200</v>
       </c>
       <c r="F49" s="3">
-        <v>12377000</v>
+        <v>12674900</v>
       </c>
       <c r="G49" s="3">
-        <v>11439900</v>
+        <v>12420800</v>
       </c>
       <c r="H49" s="3">
-        <v>11080100</v>
+        <v>11480400</v>
       </c>
       <c r="I49" s="3">
+        <v>11119300</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K49" s="3">
         <v>11193000</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M49" s="3">
+      <c r="M49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O49" s="3">
         <v>13808600</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R49" s="3">
+      <c r="R49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T49" s="3">
         <v>15791900</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V49" s="3">
         <v>20650400</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X49" s="3">
         <v>19871000</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z49" s="3">
         <v>19246300</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB49" s="3">
         <v>19527200</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD49" s="3">
         <v>19816900</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF49" s="3">
         <v>20320200</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4382,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,97 +4477,109 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>566900</v>
+        <v>682800</v>
       </c>
       <c r="E52" s="3">
-        <v>689400</v>
+        <v>568900</v>
       </c>
       <c r="F52" s="3">
-        <v>648500</v>
+        <v>691900</v>
       </c>
       <c r="G52" s="3">
-        <v>630000</v>
+        <v>650800</v>
       </c>
       <c r="H52" s="3">
-        <v>337600</v>
+        <v>632300</v>
       </c>
       <c r="I52" s="3">
+        <v>338800</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K52" s="3">
         <v>470600</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O52" s="3">
         <v>388200</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R52" s="3">
+      <c r="R52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T52" s="3">
         <v>443900</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V52" s="3">
         <v>464300</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X52" s="3">
         <v>439800</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z52" s="3">
         <v>439900</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB52" s="3">
         <v>438900</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD52" s="3">
         <v>466900</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF52" s="3">
         <v>454700</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4667,109 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>33731600</v>
+        <v>34066300</v>
       </c>
       <c r="E54" s="3">
-        <v>36751600</v>
+        <v>33850900</v>
       </c>
       <c r="F54" s="3">
-        <v>34447700</v>
+        <v>36881600</v>
       </c>
       <c r="G54" s="3">
-        <v>35538100</v>
+        <v>34569600</v>
       </c>
       <c r="H54" s="3">
-        <v>33441700</v>
+        <v>35663800</v>
       </c>
       <c r="I54" s="3">
+        <v>33559900</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K54" s="3">
         <v>46116700</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O54" s="3">
         <v>47202600</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R54" s="3">
+      <c r="R54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T54" s="3">
         <v>54013400</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V54" s="3">
         <v>48187700</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X54" s="3">
         <v>44732100</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z54" s="3">
         <v>42987000</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB54" s="3">
         <v>43906700</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD54" s="3">
         <v>44031700</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF54" s="3">
         <v>45519200</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4801,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,403 +4836,429 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>12017100</v>
+        <v>13946500</v>
       </c>
       <c r="E57" s="3">
-        <v>14337600</v>
+        <v>12059600</v>
       </c>
       <c r="F57" s="3">
-        <v>12386800</v>
+        <v>14388300</v>
       </c>
       <c r="G57" s="3">
-        <v>13621300</v>
+        <v>12430600</v>
       </c>
       <c r="H57" s="3">
-        <v>11457900</v>
+        <v>13669400</v>
       </c>
       <c r="I57" s="3">
+        <v>11498400</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K57" s="3">
         <v>13088000</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O57" s="3">
         <v>29450100</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R57" s="3">
+      <c r="R57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T57" s="3">
         <v>14330400</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V57" s="3">
         <v>13887500</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X57" s="3">
         <v>14096100</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z57" s="3">
         <v>12676500</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB57" s="3">
         <v>13139200</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD57" s="3">
         <v>12223200</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF57" s="3">
         <v>13939300</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1773800</v>
+        <v>1584900</v>
       </c>
       <c r="E58" s="3">
-        <v>1850700</v>
+        <v>1780100</v>
       </c>
       <c r="F58" s="3">
-        <v>743000</v>
+        <v>1857200</v>
       </c>
       <c r="G58" s="3">
-        <v>1079900</v>
+        <v>745600</v>
       </c>
       <c r="H58" s="3">
-        <v>1365400</v>
+        <v>1083700</v>
       </c>
       <c r="I58" s="3">
+        <v>1370200</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K58" s="3">
         <v>11403200</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M58" s="3">
+      <c r="M58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O58" s="3">
         <v>21343800</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R58" s="3">
+      <c r="R58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T58" s="3">
         <v>12732200</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V58" s="3">
         <v>2091600</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X58" s="3">
         <v>1353900</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z58" s="3">
         <v>413100</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB58" s="3">
         <v>1628000</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD58" s="3">
         <v>2433800</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF58" s="3">
         <v>1320100</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5171200</v>
+        <v>5263300</v>
       </c>
       <c r="E59" s="3">
-        <v>6391600</v>
+        <v>5189500</v>
       </c>
       <c r="F59" s="3">
-        <v>5847200</v>
+        <v>6414200</v>
       </c>
       <c r="G59" s="3">
-        <v>6319400</v>
+        <v>5867900</v>
       </c>
       <c r="H59" s="3">
-        <v>5152800</v>
+        <v>6341700</v>
       </c>
       <c r="I59" s="3">
+        <v>5171000</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K59" s="3">
         <v>5125600</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O59" s="3">
         <v>5603100</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R59" s="3">
+      <c r="R59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T59" s="3">
         <v>6277400</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V59" s="3">
         <v>6517600</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X59" s="3">
         <v>6487500</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z59" s="3">
         <v>6098600</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB59" s="3">
         <v>6282500</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD59" s="3">
         <v>6122800</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF59" s="3">
         <v>6816900</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>18962000</v>
+        <v>20794700</v>
       </c>
       <c r="E60" s="3">
-        <v>22579900</v>
+        <v>19029100</v>
       </c>
       <c r="F60" s="3">
-        <v>18977100</v>
+        <v>22659700</v>
       </c>
       <c r="G60" s="3">
-        <v>21020500</v>
+        <v>19044200</v>
       </c>
       <c r="H60" s="3">
-        <v>17976100</v>
+        <v>21094900</v>
       </c>
       <c r="I60" s="3">
+        <v>18039700</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K60" s="3">
         <v>29616900</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O60" s="3">
         <v>28685000</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R60" s="3">
+      <c r="R60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T60" s="3">
         <v>32674500</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V60" s="3">
         <v>22496700</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X60" s="3">
         <v>21937500</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z60" s="3">
         <v>19188100</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB60" s="3">
         <v>20235700</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD60" s="3">
         <v>19563000</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF60" s="3">
         <v>22076200</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7961600</v>
+        <v>7213400</v>
       </c>
       <c r="E61" s="3">
-        <v>7306300</v>
+        <v>7989800</v>
       </c>
       <c r="F61" s="3">
-        <v>8234000</v>
+        <v>7332200</v>
       </c>
       <c r="G61" s="3">
-        <v>7623700</v>
+        <v>8263100</v>
       </c>
       <c r="H61" s="3">
-        <v>7773400</v>
+        <v>7650700</v>
       </c>
       <c r="I61" s="3">
+        <v>7800900</v>
+      </c>
+      <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>8680900</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>7148900</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -4981,138 +5266,150 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>8175600</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>9978600</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>7442400</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>8446400</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>8152500</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>8598700</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>7327800</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1624600</v>
+        <v>1153800</v>
       </c>
       <c r="E62" s="3">
-        <v>1560500</v>
+        <v>1630400</v>
       </c>
       <c r="F62" s="3">
-        <v>1791500</v>
+        <v>1566000</v>
       </c>
       <c r="G62" s="3">
-        <v>1705400</v>
+        <v>1797900</v>
       </c>
       <c r="H62" s="3">
-        <v>1568400</v>
+        <v>1711500</v>
       </c>
       <c r="I62" s="3">
+        <v>1573900</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K62" s="3">
         <v>1379500</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O62" s="3">
         <v>2010300</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R62" s="3">
+      <c r="R62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T62" s="3">
         <v>1685900</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V62" s="3">
         <v>1930800</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X62" s="3">
         <v>2399700</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z62" s="3">
         <v>2432700</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB62" s="3">
         <v>2532700</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD62" s="3">
         <v>3021700</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF62" s="3">
         <v>3253300</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5497,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5592,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5687,109 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>29093800</v>
+        <v>29746800</v>
       </c>
       <c r="E66" s="3">
-        <v>32058200</v>
+        <v>29196700</v>
       </c>
       <c r="F66" s="3">
-        <v>29612700</v>
+        <v>32171600</v>
       </c>
       <c r="G66" s="3">
-        <v>30926800</v>
+        <v>29717400</v>
       </c>
       <c r="H66" s="3">
-        <v>27714900</v>
+        <v>31036200</v>
       </c>
       <c r="I66" s="3">
+        <v>27813000</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K66" s="3">
         <v>40082900</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O66" s="3">
         <v>37750900</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R66" s="3">
+      <c r="R66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T66" s="3">
         <v>43042600</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V66" s="3">
         <v>34961600</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X66" s="3">
         <v>32340200</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z66" s="3">
         <v>30603800</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB66" s="3">
         <v>31532300</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD66" s="3">
         <v>31753700</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF66" s="3">
         <v>33240800</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5821,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5912,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +6007,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +6102,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6197,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>5048600</v>
+        <v>4702600</v>
       </c>
       <c r="E72" s="3">
-        <v>5157700</v>
+        <v>5066500</v>
       </c>
       <c r="F72" s="3">
-        <v>5334000</v>
+        <v>5175900</v>
       </c>
       <c r="G72" s="3">
-        <v>5140400</v>
+        <v>5352900</v>
       </c>
       <c r="H72" s="3">
-        <v>6259100</v>
+        <v>5158600</v>
       </c>
       <c r="I72" s="3">
+        <v>6281200</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K72" s="3">
         <v>6567300</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O72" s="3">
         <v>10018900</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R72" s="3">
+      <c r="R72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T72" s="3">
         <v>11619500</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V72" s="3">
         <v>13918500</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X72" s="3">
         <v>13121900</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z72" s="3">
         <v>13135200</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB72" s="3">
         <v>12986500</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD72" s="3">
         <v>12828500</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF72" s="3">
         <v>12629500</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6387,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6482,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6577,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4637800</v>
+        <v>4319500</v>
       </c>
       <c r="E76" s="3">
-        <v>4693400</v>
+        <v>4654200</v>
       </c>
       <c r="F76" s="3">
-        <v>4835100</v>
+        <v>4710000</v>
       </c>
       <c r="G76" s="3">
-        <v>4611300</v>
+        <v>4852200</v>
       </c>
       <c r="H76" s="3">
-        <v>5726700</v>
+        <v>4627600</v>
       </c>
       <c r="I76" s="3">
+        <v>5747000</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K76" s="3">
         <v>6033800</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O76" s="3">
         <v>9451700</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R76" s="3">
+      <c r="R76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T76" s="3">
         <v>10970900</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V76" s="3">
         <v>13226200</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X76" s="3">
         <v>12391900</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z76" s="3">
         <v>12383200</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB76" s="3">
         <v>12374400</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD76" s="3">
         <v>12278000</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF76" s="3">
         <v>12278400</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,102 +6767,114 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6493,88 +6882,94 @@
         <v>5</v>
       </c>
       <c r="E81" s="3">
-        <v>142800</v>
+        <v>-2000</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G81" s="3">
-        <v>541700</v>
+        <v>143300</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I81" s="3">
+        <v>543600</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K81" s="3">
         <v>328800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>490900</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N81" s="3">
         <v>313600</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P81" s="3">
         <v>-398300</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R81" s="3">
         <v>-3923200</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T81" s="3">
         <v>741800</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V81" s="3">
         <v>429000</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X81" s="3">
         <v>515800</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z81" s="3">
         <v>869300</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB81" s="3">
         <v>1591900</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD81" s="3">
         <v>777500</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF81" s="3">
         <v>1520000</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,97 +7001,105 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>5</v>
+      <c r="E83" s="3">
+        <v>1471300</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>5</v>
+      <c r="G83" s="3">
+        <v>319400</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I83" s="3">
+        <v>628500</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K83" s="3">
         <v>-357800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>665500</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
         <v>710500</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
         <v>429900</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V83" s="3">
         <v>468900</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X83" s="3">
         <v>412000</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z83" s="3">
         <v>249800</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB83" s="3">
         <v>277000</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD83" s="3">
         <v>278300</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF83" s="3">
         <v>275200</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +7187,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7282,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7377,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7472,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7567,109 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>5</v>
+      <c r="E89" s="3">
+        <v>1584400</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>5</v>
+      <c r="G89" s="3">
+        <v>-568300</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I89" s="3">
+        <v>896900</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K89" s="3">
         <v>-4008400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>2592000</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3">
         <v>2450400</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
         <v>2696100</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V89" s="3">
         <v>-173600</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X89" s="3">
         <v>2140900</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z89" s="3">
         <v>94200</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB89" s="3">
         <v>1724900</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD89" s="3">
         <v>111600</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF89" s="3">
         <v>2248600</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,97 +7701,105 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-113400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-103800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-106300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-117000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-154800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-138300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-132200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
+        <v>-132200</v>
+      </c>
+      <c r="L91" s="3">
         <v>-140500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-140500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-227100</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P91" s="3">
         <v>-260300</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T91" s="3">
         <v>-263800</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V91" s="3">
         <v>-200300</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X91" s="3">
         <v>-207100</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-204300</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-246400</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-130400</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-187600</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7887,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,97 +7982,109 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>5</v>
+      <c r="E94" s="3">
+        <v>-486800</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>5</v>
+      <c r="G94" s="3">
+        <v>-368500</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I94" s="3">
+        <v>-523200</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K94" s="3">
         <v>581700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-818900</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
         <v>-199900</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
         <v>2316500</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3">
         <v>83800</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X94" s="3">
         <v>-34200</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z94" s="3">
         <v>272000</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-238300</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-413500</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-790700</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +8116,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7660,7 +8127,7 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>-541000</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
@@ -7672,76 +8139,82 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>-467600</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-401300</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-145500</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-1023500</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-987200</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-980200</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-811800</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8302,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8397,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,271 +8492,295 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>5</v>
+      <c r="E100" s="3">
+        <v>-1157700</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>5</v>
+      <c r="G100" s="3">
+        <v>410000</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I100" s="3">
+        <v>-2445300</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K100" s="3">
         <v>1548600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-2622900</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
         <v>-298700</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
         <v>-3561900</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V100" s="3">
         <v>-426000</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X100" s="3">
         <v>-1759300</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-364300</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-1706200</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD100" s="3">
         <v>681500</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-1132700</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>5</v>
+      <c r="E101" s="3">
+        <v>-101900</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>5</v>
+      <c r="G101" s="3">
+        <v>-75500</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I101" s="3">
+        <v>82200</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K101" s="3">
         <v>278100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-165900</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
         <v>-118300</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
         <v>-138300</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V101" s="3">
         <v>16100</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X101" s="3">
         <v>21900</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-101000</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-58700</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD101" s="3">
         <v>23200</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF101" s="3">
         <v>71900</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E102" s="3" t="s">
-        <v>5</v>
+      <c r="E102" s="3">
+        <v>-161900</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G102" s="3" t="s">
-        <v>5</v>
+      <c r="G102" s="3">
+        <v>-602300</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I102" s="3">
+        <v>-1989500</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K102" s="3">
         <v>-1600000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1015600</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N102" s="3">
+      <c r="N102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3">
         <v>1833500</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
         <v>1312400</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3">
         <v>-499700</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3">
         <v>369300</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-99000</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-278200</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD102" s="3">
         <v>402900</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF102" s="3">
         <v>397000</v>
       </c>
-      <c r="AE102" s="3" t="s">
+      <c r="AG102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WPP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WPP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="92">
   <si>
     <t>WPP</t>
   </si>
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="3">
-        <v>9755200</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G8" s="3">
-        <v>9240300</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I8" s="3">
-        <v>9819000</v>
+      <c r="D8" s="3">
+        <v>9483300</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3">
+        <v>10003700</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="3">
+        <v>9475700</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J8" s="3">
+        <v>10069000</v>
+      </c>
+      <c r="K8" s="3">
         <v>4572000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8613700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8503100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4106100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7609200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3454700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7656000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3512000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6810300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3811700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>9363600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5576900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8744700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4927000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7335700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4628400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>9686600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4595900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>10635100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4759400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>9978500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4831200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>10340000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4754900</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3">
-        <v>7893700</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="3">
-        <v>7878600</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="3">
-        <v>7910500</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="D9" s="3">
+        <v>8118600</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="3">
+        <v>8094700</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" s="3">
+        <v>8079200</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" s="3">
+        <v>8112000</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L9" s="3">
         <v>7278400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6887300</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O9" s="3">
         <v>6447300</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3">
         <v>6181000</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R9" s="3">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3">
         <v>5861300</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T9" s="3">
+      <c r="T9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U9" s="3">
         <v>7495800</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="V9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W9" s="3">
         <v>7317500</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X9" s="3">
+      <c r="X9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y9" s="3">
         <v>5732800</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z9" s="3">
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA9" s="3">
         <v>8039600</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB9" s="3">
+      <c r="AB9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC9" s="3">
         <v>8278100</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD9" s="3">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE9" s="3">
         <v>8194100</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF9" s="3">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG9" s="3">
         <v>13701700</v>
       </c>
-      <c r="AG9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1861600</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1361800</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1908400</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="D10" s="3">
+        <v>1364700</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1909000</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1396400</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1957000</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L10" s="3">
         <v>1335300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1615800</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O10" s="3">
         <v>1161900</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3">
         <v>1475000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3">
         <v>949100</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T10" s="3">
+      <c r="T10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U10" s="3">
         <v>1867800</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="V10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W10" s="3">
         <v>1427300</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y10" s="3">
         <v>1602900</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z10" s="3">
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA10" s="3">
         <v>1647000</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB10" s="3">
+      <c r="AB10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC10" s="3">
         <v>2357000</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD10" s="3">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE10" s="3">
         <v>1784400</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF10" s="3">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="3">
         <v>-3361800</v>
       </c>
-      <c r="AG10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,19 +1318,22 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3">
-        <v>-43500</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-44600</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
@@ -1321,83 +1341,86 @@
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="3">
-        <v>74500</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
+        <v>76400</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>97000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>94400</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="3">
         <v>-14500</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3">
         <v>112900</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3">
         <v>62700</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="3">
         <v>46600</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W14" s="3">
         <v>18700</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y14" s="3">
         <v>17300</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA14" s="3">
         <v>36700</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE14" s="3">
         <v>25300</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF14" s="3">
+      <c r="AF14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG14" s="3">
         <v>-295800</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1461,8 +1484,8 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>5</v>
+      <c r="X15" s="3">
+        <v>0</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>5</v>
@@ -1479,20 +1502,23 @@
       <c r="AC15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AD15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE15" s="3">
         <v>127600</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF15" s="3">
+      <c r="AF15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG15" s="3">
         <v>119600</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E17" s="3">
-        <v>9423900</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G17" s="3">
-        <v>8848600</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I17" s="3">
-        <v>8844800</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="D17" s="3">
+        <v>8928200</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="3">
+        <v>9664000</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="3">
+        <v>9074000</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" s="3">
+        <v>9070100</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L17" s="3">
         <v>8023800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7647000</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O17" s="3">
         <v>6994600</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="P17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="3">
         <v>7559900</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R17" s="3">
+      <c r="R17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S17" s="3">
         <v>10228500</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T17" s="3">
+      <c r="T17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U17" s="3">
         <v>8456200</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="V17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W17" s="3">
         <v>7944600</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="X17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y17" s="3">
         <v>6829900</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z17" s="3">
+      <c r="Z17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA17" s="3">
         <v>8634900</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB17" s="3">
+      <c r="AB17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC17" s="3">
         <v>9091000</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD17" s="3">
+      <c r="AD17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE17" s="3">
         <v>9033700</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF17" s="3">
+      <c r="AF17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG17" s="3">
         <v>8352300</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E18" s="3">
-        <v>331300</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G18" s="3">
-        <v>391700</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I18" s="3">
-        <v>974200</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="D18" s="3">
+        <v>555100</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="3">
+        <v>339700</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="3">
+        <v>401700</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J18" s="3">
+        <v>999000</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L18" s="3">
         <v>589900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>856100</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O18" s="3">
         <v>614600</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="3">
         <v>96100</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S18" s="3">
         <v>-3418200</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U18" s="3">
         <v>907500</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W18" s="3">
         <v>800200</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y18" s="3">
         <v>505700</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA18" s="3">
         <v>1051700</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC18" s="3">
         <v>1544000</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD18" s="3">
+      <c r="AD18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE18" s="3">
         <v>944800</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF18" s="3">
+      <c r="AF18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG18" s="3">
         <v>1987700</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,483 +1781,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="3">
-        <v>39800</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G20" s="3">
-        <v>164900</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I20" s="3">
-        <v>241200</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="D20" s="3">
+        <v>164000</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3">
+        <v>40800</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3">
+        <v>169100</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3">
+        <v>247300</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>128700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>21900</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O20" s="3">
         <v>57400</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-164900</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S20" s="3">
         <v>-265800</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U20" s="3">
         <v>429700</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W20" s="3">
         <v>3800</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y20" s="3">
         <v>224700</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="Z20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA20" s="3">
         <v>210900</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC20" s="3">
         <v>361800</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD20" s="3">
+      <c r="AD20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE20" s="3">
         <v>239100</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF20" s="3">
+      <c r="AF20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG20" s="3">
         <v>109800</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="3">
-        <v>1874100</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G21" s="3">
-        <v>887500</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I21" s="3">
-        <v>1871900</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="D21" s="3">
+        <v>1062900</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1921800</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H21" s="3">
+        <v>910100</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J21" s="3">
+        <v>1919600</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L21" s="3">
         <v>352700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1568900</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3">
         <v>683700</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U21" s="3">
         <v>1782500</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W21" s="3">
         <v>1298100</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y21" s="3">
         <v>1169300</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA21" s="3">
         <v>1536000</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC21" s="3">
         <v>2206400</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE21" s="3">
         <v>1486100</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG21" s="3">
         <v>2400000</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E22" s="3">
-        <v>189400</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G22" s="3">
-        <v>295200</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I22" s="3">
-        <v>266900</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="D22" s="3">
+        <v>275600</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3">
+        <v>194200</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3">
+        <v>302700</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3">
+        <v>273700</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L22" s="3">
         <v>184800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>168600</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O22" s="3">
         <v>182600</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="3">
         <v>180700</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R22" s="3">
+      <c r="R22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S22" s="3">
         <v>191900</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T22" s="3">
+      <c r="T22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U22" s="3">
         <v>238900</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W22" s="3">
         <v>242400</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y22" s="3">
         <v>187400</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA22" s="3">
         <v>168200</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB22" s="3">
+      <c r="AB22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC22" s="3">
         <v>171000</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD22" s="3">
+      <c r="AD22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE22" s="3">
         <v>167600</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF22" s="3">
+      <c r="AF22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG22" s="3">
         <v>167900</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="3">
-        <v>181700</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G23" s="3">
-        <v>261400</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I23" s="3">
-        <v>948400</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="D23" s="3">
+        <v>443500</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="3">
+        <v>186300</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" s="3">
+        <v>268100</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J23" s="3">
+        <v>972600</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L23" s="3">
         <v>533800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>709500</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O23" s="3">
         <v>489400</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P23" s="3">
+      <c r="P23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-249500</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R23" s="3">
+      <c r="R23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S23" s="3">
         <v>-3875900</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T23" s="3">
+      <c r="T23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U23" s="3">
         <v>1098300</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="V23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W23" s="3">
         <v>561600</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="X23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y23" s="3">
         <v>543000</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z23" s="3">
+      <c r="Z23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA23" s="3">
         <v>1094400</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB23" s="3">
+      <c r="AB23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC23" s="3">
         <v>1734900</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD23" s="3">
+      <c r="AD23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE23" s="3">
         <v>1016300</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF23" s="3">
+      <c r="AF23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG23" s="3">
         <v>1929600</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E24" s="3">
-        <v>120400</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" s="3">
-        <v>70400</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I24" s="3">
-        <v>341500</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="D24" s="3">
+        <v>120700</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3">
+        <v>123500</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3">
+        <v>72200</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="3">
+        <v>350200</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L24" s="3">
         <v>149800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>156800</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O24" s="3">
         <v>132900</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q24" s="3">
         <v>125600</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="R24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S24" s="3">
         <v>13300</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="T24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U24" s="3">
         <v>226000</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="V24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W24" s="3">
         <v>150100</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="X24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y24" s="3">
         <v>151900</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z24" s="3">
+      <c r="Z24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA24" s="3">
         <v>182300</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB24" s="3">
+      <c r="AB24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC24" s="3">
         <v>335900</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD24" s="3">
+      <c r="AD24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE24" s="3">
         <v>189800</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF24" s="3">
+      <c r="AF24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG24" s="3">
         <v>323700</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E26" s="3">
-        <v>61300</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G26" s="3">
-        <v>191000</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I26" s="3">
-        <v>606900</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="D26" s="3">
+        <v>322800</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3">
+        <v>62900</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="3">
+        <v>195900</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J26" s="3">
+        <v>622400</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L26" s="3">
         <v>383900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>552600</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O26" s="3">
         <v>356500</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P26" s="3">
+      <c r="P26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-375000</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R26" s="3">
+      <c r="R26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S26" s="3">
         <v>-3889200</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T26" s="3">
+      <c r="T26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U26" s="3">
         <v>872300</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="V26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W26" s="3">
         <v>411500</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="X26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y26" s="3">
         <v>391100</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z26" s="3">
+      <c r="Z26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA26" s="3">
         <v>912100</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB26" s="3">
+      <c r="AB26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC26" s="3">
         <v>1399000</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD26" s="3">
+      <c r="AD26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE26" s="3">
         <v>826500</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF26" s="3">
+      <c r="AF26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG26" s="3">
         <v>1606000</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G27" s="3">
-        <v>143300</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I27" s="3">
-        <v>543600</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="D27" s="3">
+        <v>269000</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H27" s="3">
+        <v>147000</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J27" s="3">
+        <v>557400</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L27" s="3">
         <v>328800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>490900</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O27" s="3">
         <v>313600</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="P27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-414200</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R27" s="3">
+      <c r="R27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S27" s="3">
         <v>-3914900</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T27" s="3">
+      <c r="T27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U27" s="3">
         <v>805900</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="V27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W27" s="3">
         <v>369700</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="X27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y27" s="3">
         <v>348800</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z27" s="3">
+      <c r="Z27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA27" s="3">
         <v>869300</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB27" s="3">
+      <c r="AB27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC27" s="3">
         <v>1323200</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD27" s="3">
+      <c r="AD27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE27" s="3">
         <v>777500</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF27" s="3">
+      <c r="AF27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG27" s="3">
         <v>1520000</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,89 +2661,92 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>5</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>5</v>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P29" s="3">
+      <c r="L29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q29" s="3">
         <v>15900</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R29" s="3">
+      <c r="R29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S29" s="3">
         <v>-8300</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U29" s="3">
         <v>-64100</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W29" s="3">
         <v>59300</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y29" s="3">
         <v>166900</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="3">
         <v>268700</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-39800</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-164900</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-241200</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="D32" s="3">
+        <v>-164000</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-40800</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-169100</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-247300</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>-128700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-21900</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O32" s="3">
         <v>-57400</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="3">
         <v>164900</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S32" s="3">
         <v>265800</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U32" s="3">
         <v>-429700</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W32" s="3">
         <v>-3800</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-224700</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="Z32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-210900</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-361800</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AD32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-239100</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF32" s="3">
+      <c r="AF32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-109800</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G33" s="3">
-        <v>143300</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I33" s="3">
-        <v>543600</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="D33" s="3">
+        <v>269000</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H33" s="3">
+        <v>147000</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J33" s="3">
+        <v>557400</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L33" s="3">
         <v>328800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>490900</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O33" s="3">
         <v>313600</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P33" s="3">
+      <c r="P33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-398300</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R33" s="3">
+      <c r="R33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S33" s="3">
         <v>-3923200</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T33" s="3">
+      <c r="T33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U33" s="3">
         <v>741800</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="V33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W33" s="3">
         <v>429000</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X33" s="3">
+      <c r="X33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y33" s="3">
         <v>515800</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z33" s="3">
+      <c r="Z33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA33" s="3">
         <v>869300</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB33" s="3">
+      <c r="AB33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC33" s="3">
         <v>1591900</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD33" s="3">
+      <c r="AD33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE33" s="3">
         <v>777500</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF33" s="3">
+      <c r="AF33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG33" s="3">
         <v>1520000</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G35" s="3">
-        <v>143300</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I35" s="3">
-        <v>543600</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="D35" s="3">
+        <v>269000</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H35" s="3">
+        <v>147000</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J35" s="3">
+        <v>557400</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L35" s="3">
         <v>328800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>490900</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O35" s="3">
         <v>313600</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="P35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-398300</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R35" s="3">
+      <c r="R35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S35" s="3">
         <v>-3923200</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T35" s="3">
+      <c r="T35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U35" s="3">
         <v>741800</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="V35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W35" s="3">
         <v>429000</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X35" s="3">
+      <c r="X35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y35" s="3">
         <v>515800</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z35" s="3">
+      <c r="Z35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA35" s="3">
         <v>869300</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB35" s="3">
+      <c r="AB35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC35" s="3">
         <v>1591900</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD35" s="3">
+      <c r="AD35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE35" s="3">
         <v>777500</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF35" s="3">
+      <c r="AF35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG35" s="3">
         <v>1520000</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,50 +3524,51 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2837500</v>
+        <v>2792400</v>
       </c>
       <c r="E41" s="3">
-        <v>2511400</v>
+        <v>2909800</v>
       </c>
       <c r="F41" s="3">
-        <v>3188100</v>
+        <v>2575300</v>
       </c>
       <c r="G41" s="3">
-        <v>2271300</v>
+        <v>3269300</v>
       </c>
       <c r="H41" s="3">
-        <v>4968600</v>
+        <v>2329200</v>
       </c>
       <c r="I41" s="3">
-        <v>4537600</v>
+        <v>5095100</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L41" s="3">
         <v>16447600</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O41" s="3">
+      <c r="O41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P41" s="3">
         <v>13482200</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>5</v>
       </c>
@@ -3491,50 +3578,53 @@
       <c r="S41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T41" s="3">
+      <c r="T41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U41" s="3">
         <v>15418600</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V41" s="3">
+      <c r="V41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W41" s="3">
         <v>2984200</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X41" s="3">
+      <c r="X41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y41" s="3">
         <v>3491100</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z41" s="3">
+      <c r="Z41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA41" s="3">
         <v>2871300</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB41" s="3">
+      <c r="AB41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC41" s="3">
         <v>3119100</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD41" s="3">
+      <c r="AD41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE41" s="3">
         <v>3725100</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF41" s="3">
+      <c r="AF41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG41" s="3">
         <v>2970900</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3610,8 +3700,8 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>5</v>
+      <c r="AB42" s="3">
+        <v>0</v>
       </c>
       <c r="AC42" s="3" t="s">
         <v>5</v>
@@ -3622,56 +3712,59 @@
       <c r="AE42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AF42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG42" s="3">
         <v>237900</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>14346900</v>
+        <v>14758300</v>
       </c>
       <c r="E43" s="3">
-        <v>13523000</v>
+        <v>14712300</v>
       </c>
       <c r="F43" s="3">
-        <v>15371600</v>
+        <v>13867500</v>
       </c>
       <c r="G43" s="3">
-        <v>14311900</v>
+        <v>15763100</v>
       </c>
       <c r="H43" s="3">
-        <v>14051300</v>
+        <v>14676400</v>
       </c>
       <c r="I43" s="3">
-        <v>12564900</v>
+        <v>14409100</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L43" s="3">
         <v>13478100</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P43" s="3">
         <v>27605700</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>5</v>
       </c>
@@ -3681,92 +3774,95 @@
       <c r="S43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T43" s="3">
+      <c r="T43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U43" s="3">
         <v>15478600</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V43" s="3">
+      <c r="V43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W43" s="3">
         <v>17299200</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X43" s="3">
+      <c r="X43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y43" s="3">
         <v>16701500</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z43" s="3">
+      <c r="Z43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA43" s="3">
         <v>15659500</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB43" s="3">
+      <c r="AB43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC43" s="3">
         <v>15736500</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD43" s="3">
+      <c r="AD43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE43" s="3">
         <v>14605800</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF43" s="3">
+      <c r="AF43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG43" s="3">
         <v>16171500</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>350100</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E44" s="3">
-        <v>374500</v>
+        <v>359000</v>
       </c>
       <c r="F44" s="3">
-        <v>450900</v>
+        <v>384100</v>
       </c>
       <c r="G44" s="3">
-        <v>439900</v>
+        <v>462400</v>
       </c>
       <c r="H44" s="3">
-        <v>325000</v>
+        <v>451100</v>
       </c>
       <c r="I44" s="3">
-        <v>357100</v>
+        <v>333300</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L44" s="3">
         <v>336800</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O44" s="3">
+      <c r="O44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P44" s="3">
         <v>416800</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>5</v>
       </c>
@@ -3776,92 +3872,95 @@
       <c r="S44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T44" s="3">
+      <c r="T44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U44" s="3">
         <v>476600</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V44" s="3">
+      <c r="V44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W44" s="3">
         <v>576100</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X44" s="3">
+      <c r="X44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y44" s="3">
         <v>484100</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z44" s="3">
+      <c r="Z44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA44" s="3">
         <v>524600</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB44" s="3">
+      <c r="AB44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC44" s="3">
         <v>1076600</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD44" s="3">
+      <c r="AD44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE44" s="3">
         <v>1113600</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF44" s="3">
+      <c r="AF44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG44" s="3">
         <v>527200</v>
       </c>
-      <c r="AG44" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>307900</v>
+      <c r="D45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E45" s="3">
-        <v>394200</v>
+        <v>315700</v>
       </c>
       <c r="F45" s="3">
-        <v>309300</v>
+        <v>404300</v>
       </c>
       <c r="G45" s="3">
-        <v>380300</v>
+        <v>317200</v>
       </c>
       <c r="H45" s="3">
-        <v>278700</v>
+        <v>390000</v>
       </c>
       <c r="I45" s="3">
-        <v>342200</v>
+        <v>285800</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L45" s="3">
         <v>316600</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P45" s="3">
         <v>922800</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>5</v>
       </c>
@@ -3871,92 +3970,95 @@
       <c r="S45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T45" s="3">
+      <c r="T45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U45" s="3">
         <v>1055300</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V45" s="3">
+      <c r="V45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W45" s="3">
         <v>550600</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X45" s="3">
+      <c r="X45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y45" s="3">
         <v>381200</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z45" s="3">
+      <c r="Z45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA45" s="3">
         <v>546200</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB45" s="3">
+      <c r="AB45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC45" s="3">
         <v>390400</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD45" s="3">
+      <c r="AD45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE45" s="3">
         <v>529400</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF45" s="3">
+      <c r="AF45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG45" s="3">
         <v>427600</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>17842400</v>
+        <v>17550700</v>
       </c>
       <c r="E46" s="3">
-        <v>16803200</v>
+        <v>18296800</v>
       </c>
       <c r="F46" s="3">
-        <v>19319900</v>
+        <v>17231200</v>
       </c>
       <c r="G46" s="3">
-        <v>17403500</v>
+        <v>19812000</v>
       </c>
       <c r="H46" s="3">
-        <v>19623600</v>
+        <v>17846700</v>
       </c>
       <c r="I46" s="3">
-        <v>17801800</v>
+        <v>20123400</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L46" s="3">
         <v>30579100</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O46" s="3">
+      <c r="O46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P46" s="3">
         <v>28329100</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>5</v>
       </c>
@@ -3966,92 +4068,95 @@
       <c r="S46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T46" s="3">
+      <c r="T46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U46" s="3">
         <v>32429200</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V46" s="3">
+      <c r="V46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W46" s="3">
         <v>21410100</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X46" s="3">
+      <c r="X46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y46" s="3">
         <v>21057900</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z46" s="3">
+      <c r="Z46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA46" s="3">
         <v>19601700</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB46" s="3">
+      <c r="AB46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC46" s="3">
         <v>19769200</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD46" s="3">
+      <c r="AD46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE46" s="3">
         <v>19395900</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF46" s="3">
+      <c r="AF46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG46" s="3">
         <v>20335200</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>890200</v>
+        <v>1066800</v>
       </c>
       <c r="E47" s="3">
-        <v>874500</v>
+        <v>912900</v>
       </c>
       <c r="F47" s="3">
-        <v>958400</v>
+        <v>896800</v>
       </c>
       <c r="G47" s="3">
-        <v>991700</v>
+        <v>982800</v>
       </c>
       <c r="H47" s="3">
-        <v>995300</v>
+        <v>1017000</v>
       </c>
       <c r="I47" s="3">
-        <v>1400700</v>
+        <v>1020600</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L47" s="3">
         <v>947100</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P47" s="3">
         <v>1727800</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4061,92 +4166,95 @@
       <c r="S47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T47" s="3">
+      <c r="T47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U47" s="3">
         <v>1788300</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V47" s="3">
+      <c r="V47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W47" s="3">
         <v>1804800</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X47" s="3">
+      <c r="X47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y47" s="3">
         <v>1933000</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z47" s="3">
+      <c r="Z47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA47" s="3">
         <v>2366400</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB47" s="3">
+      <c r="AB47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC47" s="3">
         <v>2893900</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD47" s="3">
+      <c r="AD47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE47" s="3">
         <v>3138300</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF47" s="3">
+      <c r="AF47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG47" s="3">
         <v>3133600</v>
       </c>
-      <c r="AG47" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2828800</v>
+        <v>2817300</v>
       </c>
       <c r="E48" s="3">
-        <v>3067100</v>
+        <v>2900900</v>
       </c>
       <c r="F48" s="3">
-        <v>3236400</v>
+        <v>3145200</v>
       </c>
       <c r="G48" s="3">
-        <v>3102800</v>
+        <v>3318800</v>
       </c>
       <c r="H48" s="3">
-        <v>2932200</v>
+        <v>3181800</v>
       </c>
       <c r="I48" s="3">
-        <v>2899300</v>
+        <v>3006900</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L48" s="3">
         <v>2926900</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P48" s="3">
         <v>3113000</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4156,92 +4264,95 @@
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T48" s="3">
+      <c r="T48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U48" s="3">
         <v>3560200</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V48" s="3">
+      <c r="V48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W48" s="3">
         <v>3858100</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X48" s="3">
+      <c r="X48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y48" s="3">
         <v>1430400</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z48" s="3">
+      <c r="Z48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA48" s="3">
         <v>1332600</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB48" s="3">
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC48" s="3">
         <v>1277600</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD48" s="3">
+      <c r="AD48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE48" s="3">
         <v>1213700</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF48" s="3">
+      <c r="AF48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG48" s="3">
         <v>1275600</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>11822100</v>
+        <v>11990900</v>
       </c>
       <c r="E49" s="3">
-        <v>12537200</v>
+        <v>12123200</v>
       </c>
       <c r="F49" s="3">
-        <v>12674900</v>
+        <v>12856500</v>
       </c>
       <c r="G49" s="3">
-        <v>12420800</v>
+        <v>12997700</v>
       </c>
       <c r="H49" s="3">
-        <v>11480400</v>
+        <v>12737100</v>
       </c>
       <c r="I49" s="3">
-        <v>11119300</v>
+        <v>11772800</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K49" s="3">
+      <c r="K49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L49" s="3">
         <v>11193000</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O49" s="3">
+      <c r="O49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P49" s="3">
         <v>13808600</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>5</v>
       </c>
@@ -4251,50 +4362,53 @@
       <c r="S49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T49" s="3">
+      <c r="T49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U49" s="3">
         <v>15791900</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V49" s="3">
+      <c r="V49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W49" s="3">
         <v>20650400</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X49" s="3">
+      <c r="X49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y49" s="3">
         <v>19871000</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z49" s="3">
+      <c r="Z49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA49" s="3">
         <v>19246300</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB49" s="3">
+      <c r="AB49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC49" s="3">
         <v>19527200</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD49" s="3">
+      <c r="AD49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE49" s="3">
         <v>19816900</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF49" s="3">
+      <c r="AF49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG49" s="3">
         <v>20320200</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,50 +4600,53 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>682800</v>
+        <v>446100</v>
       </c>
       <c r="E52" s="3">
-        <v>568900</v>
+        <v>700200</v>
       </c>
       <c r="F52" s="3">
-        <v>691900</v>
+        <v>583400</v>
       </c>
       <c r="G52" s="3">
-        <v>650800</v>
+        <v>709500</v>
       </c>
       <c r="H52" s="3">
-        <v>632300</v>
+        <v>667400</v>
       </c>
       <c r="I52" s="3">
-        <v>338800</v>
+        <v>648400</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L52" s="3">
         <v>470600</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P52" s="3">
         <v>388200</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>5</v>
       </c>
@@ -4536,50 +4656,53 @@
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T52" s="3">
+      <c r="T52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U52" s="3">
         <v>443900</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V52" s="3">
+      <c r="V52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W52" s="3">
         <v>464300</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X52" s="3">
+      <c r="X52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y52" s="3">
         <v>439800</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z52" s="3">
+      <c r="Z52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA52" s="3">
         <v>439900</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB52" s="3">
+      <c r="AB52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC52" s="3">
         <v>438900</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD52" s="3">
+      <c r="AD52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE52" s="3">
         <v>466900</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF52" s="3">
+      <c r="AF52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG52" s="3">
         <v>454700</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,50 +4796,53 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>34066300</v>
+        <v>33871800</v>
       </c>
       <c r="E54" s="3">
-        <v>33850900</v>
+        <v>34933900</v>
       </c>
       <c r="F54" s="3">
-        <v>36881600</v>
+        <v>34713100</v>
       </c>
       <c r="G54" s="3">
-        <v>34569600</v>
+        <v>37820900</v>
       </c>
       <c r="H54" s="3">
-        <v>35663800</v>
+        <v>35450000</v>
       </c>
       <c r="I54" s="3">
-        <v>33559900</v>
+        <v>36572100</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L54" s="3">
         <v>46116700</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P54" s="3">
         <v>47202600</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>5</v>
       </c>
@@ -4726,50 +4852,53 @@
       <c r="S54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T54" s="3">
+      <c r="T54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U54" s="3">
         <v>54013400</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V54" s="3">
+      <c r="V54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W54" s="3">
         <v>48187700</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X54" s="3">
+      <c r="X54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y54" s="3">
         <v>44732100</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z54" s="3">
+      <c r="Z54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA54" s="3">
         <v>42987000</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB54" s="3">
+      <c r="AB54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC54" s="3">
         <v>43906700</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD54" s="3">
+      <c r="AD54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE54" s="3">
         <v>44031700</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF54" s="3">
+      <c r="AF54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG54" s="3">
         <v>45519200</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,50 +4968,51 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>13946500</v>
+        <v>15630900</v>
       </c>
       <c r="E57" s="3">
-        <v>12059600</v>
+        <v>14301700</v>
       </c>
       <c r="F57" s="3">
-        <v>14388300</v>
+        <v>12366700</v>
       </c>
       <c r="G57" s="3">
-        <v>12430600</v>
+        <v>14754800</v>
       </c>
       <c r="H57" s="3">
-        <v>13669400</v>
+        <v>12747200</v>
       </c>
       <c r="I57" s="3">
-        <v>11498400</v>
+        <v>14017600</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L57" s="3">
         <v>13088000</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P57" s="3">
         <v>29450100</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>5</v>
       </c>
@@ -4891,92 +5022,95 @@
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T57" s="3">
+      <c r="T57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U57" s="3">
         <v>14330400</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V57" s="3">
+      <c r="V57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W57" s="3">
         <v>13887500</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X57" s="3">
+      <c r="X57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y57" s="3">
         <v>14096100</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z57" s="3">
+      <c r="Z57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA57" s="3">
         <v>12676500</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB57" s="3">
+      <c r="AB57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC57" s="3">
         <v>13139200</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD57" s="3">
+      <c r="AD57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE57" s="3">
         <v>12223200</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF57" s="3">
+      <c r="AF57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG57" s="3">
         <v>13939300</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1584900</v>
+        <v>1921100</v>
       </c>
       <c r="E58" s="3">
-        <v>1780100</v>
+        <v>1625300</v>
       </c>
       <c r="F58" s="3">
-        <v>1857200</v>
+        <v>1825400</v>
       </c>
       <c r="G58" s="3">
-        <v>745600</v>
+        <v>1904500</v>
       </c>
       <c r="H58" s="3">
-        <v>1083700</v>
+        <v>764600</v>
       </c>
       <c r="I58" s="3">
-        <v>1370200</v>
+        <v>1111300</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K58" s="3">
+      <c r="K58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L58" s="3">
         <v>11403200</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O58" s="3">
+      <c r="O58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P58" s="3">
         <v>21343800</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>5</v>
       </c>
@@ -4986,92 +5120,95 @@
       <c r="S58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T58" s="3">
+      <c r="T58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U58" s="3">
         <v>12732200</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V58" s="3">
+      <c r="V58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W58" s="3">
         <v>2091600</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X58" s="3">
+      <c r="X58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y58" s="3">
         <v>1353900</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z58" s="3">
+      <c r="Z58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA58" s="3">
         <v>413100</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB58" s="3">
+      <c r="AB58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC58" s="3">
         <v>1628000</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD58" s="3">
+      <c r="AD58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE58" s="3">
         <v>2433800</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF58" s="3">
+      <c r="AF58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG58" s="3">
         <v>1320100</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5263300</v>
+        <v>2115300</v>
       </c>
       <c r="E59" s="3">
-        <v>5189500</v>
+        <v>5397300</v>
       </c>
       <c r="F59" s="3">
-        <v>6414200</v>
+        <v>5321600</v>
       </c>
       <c r="G59" s="3">
-        <v>5867900</v>
+        <v>6577500</v>
       </c>
       <c r="H59" s="3">
-        <v>6341700</v>
+        <v>6017400</v>
       </c>
       <c r="I59" s="3">
-        <v>5171000</v>
+        <v>6503300</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L59" s="3">
         <v>5125600</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P59" s="3">
         <v>5603100</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5081,92 +5218,95 @@
       <c r="S59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T59" s="3">
+      <c r="T59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U59" s="3">
         <v>6277400</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V59" s="3">
+      <c r="V59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W59" s="3">
         <v>6517600</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X59" s="3">
+      <c r="X59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y59" s="3">
         <v>6487500</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z59" s="3">
+      <c r="Z59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA59" s="3">
         <v>6098600</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB59" s="3">
+      <c r="AB59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC59" s="3">
         <v>6282500</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD59" s="3">
+      <c r="AD59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE59" s="3">
         <v>6122800</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF59" s="3">
+      <c r="AF59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG59" s="3">
         <v>6816900</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>20794700</v>
+        <v>19667300</v>
       </c>
       <c r="E60" s="3">
-        <v>19029100</v>
+        <v>21324300</v>
       </c>
       <c r="F60" s="3">
-        <v>22659700</v>
+        <v>19513700</v>
       </c>
       <c r="G60" s="3">
-        <v>19044200</v>
+        <v>23236800</v>
       </c>
       <c r="H60" s="3">
-        <v>21094900</v>
+        <v>19529200</v>
       </c>
       <c r="I60" s="3">
-        <v>18039700</v>
+        <v>21632100</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L60" s="3">
         <v>29616900</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O60" s="3">
+      <c r="O60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P60" s="3">
         <v>28685000</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>5</v>
       </c>
@@ -5176,80 +5316,83 @@
       <c r="S60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T60" s="3">
+      <c r="T60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U60" s="3">
         <v>32674500</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V60" s="3">
+      <c r="V60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W60" s="3">
         <v>22496700</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X60" s="3">
+      <c r="X60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y60" s="3">
         <v>21937500</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z60" s="3">
+      <c r="Z60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA60" s="3">
         <v>19188100</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB60" s="3">
+      <c r="AB60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC60" s="3">
         <v>20235700</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD60" s="3">
+      <c r="AD60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE60" s="3">
         <v>19563000</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF60" s="3">
+      <c r="AF60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG60" s="3">
         <v>22076200</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7213400</v>
+        <v>7975600</v>
       </c>
       <c r="E61" s="3">
-        <v>7989800</v>
+        <v>7397100</v>
       </c>
       <c r="F61" s="3">
-        <v>7332200</v>
+        <v>8193200</v>
       </c>
       <c r="G61" s="3">
-        <v>8263100</v>
+        <v>7518900</v>
       </c>
       <c r="H61" s="3">
-        <v>7650700</v>
+        <v>8473500</v>
       </c>
       <c r="I61" s="3">
-        <v>7800900</v>
+        <v>7845500</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>8680900</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5257,11 +5400,11 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>7148900</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -5272,91 +5415,94 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>8175600</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>9978600</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
         <v>7442400</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>8446400</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>8152500</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>8598700</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
         <v>7327800</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1153800</v>
+        <v>1035300</v>
       </c>
       <c r="E62" s="3">
-        <v>1630400</v>
+        <v>1183200</v>
       </c>
       <c r="F62" s="3">
-        <v>1566000</v>
+        <v>1671900</v>
       </c>
       <c r="G62" s="3">
-        <v>1797900</v>
+        <v>1605900</v>
       </c>
       <c r="H62" s="3">
-        <v>1711500</v>
+        <v>1843600</v>
       </c>
       <c r="I62" s="3">
-        <v>1573900</v>
+        <v>1755100</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L62" s="3">
         <v>1379500</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P62" s="3">
         <v>2010300</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>5</v>
       </c>
@@ -5366,50 +5512,53 @@
       <c r="S62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T62" s="3">
+      <c r="T62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U62" s="3">
         <v>1685900</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V62" s="3">
+      <c r="V62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W62" s="3">
         <v>1930800</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X62" s="3">
+      <c r="X62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y62" s="3">
         <v>2399700</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z62" s="3">
+      <c r="Z62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA62" s="3">
         <v>2432700</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB62" s="3">
+      <c r="AB62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC62" s="3">
         <v>2532700</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD62" s="3">
+      <c r="AD62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE62" s="3">
         <v>3021700</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF62" s="3">
+      <c r="AF62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG62" s="3">
         <v>3253300</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,50 +5848,53 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>29746800</v>
+        <v>29283100</v>
       </c>
       <c r="E66" s="3">
-        <v>29196700</v>
+        <v>30504500</v>
       </c>
       <c r="F66" s="3">
-        <v>32171600</v>
+        <v>29940300</v>
       </c>
       <c r="G66" s="3">
-        <v>29717400</v>
+        <v>32990900</v>
       </c>
       <c r="H66" s="3">
-        <v>31036200</v>
+        <v>30474300</v>
       </c>
       <c r="I66" s="3">
-        <v>27813000</v>
+        <v>31826600</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L66" s="3">
         <v>40082900</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P66" s="3">
         <v>37750900</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>5</v>
       </c>
@@ -5746,50 +5904,53 @@
       <c r="S66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T66" s="3">
+      <c r="T66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U66" s="3">
         <v>43042600</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V66" s="3">
+      <c r="V66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W66" s="3">
         <v>34961600</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X66" s="3">
+      <c r="X66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y66" s="3">
         <v>32340200</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z66" s="3">
+      <c r="Z66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA66" s="3">
         <v>30603800</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB66" s="3">
+      <c r="AB66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC66" s="3">
         <v>31532300</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD66" s="3">
+      <c r="AD66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE66" s="3">
         <v>31753700</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF66" s="3">
+      <c r="AF66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG66" s="3">
         <v>33240800</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,50 +6374,53 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4702600</v>
+        <v>4915500</v>
       </c>
       <c r="E72" s="3">
-        <v>5066500</v>
+        <v>4822300</v>
       </c>
       <c r="F72" s="3">
-        <v>5175900</v>
+        <v>5195500</v>
       </c>
       <c r="G72" s="3">
-        <v>5352900</v>
+        <v>5307700</v>
       </c>
       <c r="H72" s="3">
-        <v>5158600</v>
+        <v>5489200</v>
       </c>
       <c r="I72" s="3">
-        <v>6281200</v>
+        <v>5290000</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L72" s="3">
         <v>6567300</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P72" s="3">
         <v>10018900</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>5</v>
       </c>
@@ -6256,50 +6430,53 @@
       <c r="S72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U72" s="3">
         <v>11619500</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V72" s="3">
+      <c r="V72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W72" s="3">
         <v>13918500</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X72" s="3">
+      <c r="X72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y72" s="3">
         <v>13121900</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z72" s="3">
+      <c r="Z72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA72" s="3">
         <v>13135200</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC72" s="3">
         <v>12986500</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD72" s="3">
+      <c r="AD72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE72" s="3">
         <v>12828500</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF72" s="3">
+      <c r="AF72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG72" s="3">
         <v>12629500</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,50 +6766,53 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4319500</v>
+        <v>4588800</v>
       </c>
       <c r="E76" s="3">
-        <v>4654200</v>
+        <v>4429500</v>
       </c>
       <c r="F76" s="3">
-        <v>4710000</v>
+        <v>4772700</v>
       </c>
       <c r="G76" s="3">
-        <v>4852200</v>
+        <v>4829900</v>
       </c>
       <c r="H76" s="3">
-        <v>4627600</v>
+        <v>4975700</v>
       </c>
       <c r="I76" s="3">
-        <v>5747000</v>
+        <v>4745400</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L76" s="3">
         <v>6033800</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O76" s="3">
+      <c r="O76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P76" s="3">
         <v>9451700</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>5</v>
       </c>
@@ -6636,50 +6822,53 @@
       <c r="S76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T76" s="3">
+      <c r="T76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U76" s="3">
         <v>10970900</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V76" s="3">
+      <c r="V76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W76" s="3">
         <v>13226200</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X76" s="3">
+      <c r="X76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y76" s="3">
         <v>12391900</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z76" s="3">
+      <c r="Z76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA76" s="3">
         <v>12383200</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB76" s="3">
+      <c r="AB76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC76" s="3">
         <v>12374400</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD76" s="3">
+      <c r="AD76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE76" s="3">
         <v>12278000</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF76" s="3">
+      <c r="AF76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG76" s="3">
         <v>12278400</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G81" s="3">
-        <v>143300</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I81" s="3">
-        <v>543600</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="D81" s="3">
+        <v>269000</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H81" s="3">
+        <v>147000</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J81" s="3">
+        <v>557400</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L81" s="3">
         <v>328800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>490900</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O81" s="3">
         <v>313600</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P81" s="3">
+      <c r="P81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-398300</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R81" s="3">
+      <c r="R81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S81" s="3">
         <v>-3923200</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T81" s="3">
+      <c r="T81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U81" s="3">
         <v>741800</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="V81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W81" s="3">
         <v>429000</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X81" s="3">
+      <c r="X81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y81" s="3">
         <v>515800</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z81" s="3">
+      <c r="Z81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA81" s="3">
         <v>869300</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB81" s="3">
+      <c r="AB81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC81" s="3">
         <v>1591900</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD81" s="3">
+      <c r="AD81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE81" s="3">
         <v>777500</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF81" s="3">
+      <c r="AF81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG81" s="3">
         <v>1520000</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E83" s="3">
-        <v>1471300</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G83" s="3">
-        <v>319400</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I83" s="3">
-        <v>628500</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="D83" s="3">
+        <v>325400</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3">
+        <v>1508800</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H83" s="3">
+        <v>327500</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3">
+        <v>644600</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L83" s="3">
         <v>-357800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>665500</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q83" s="3">
         <v>710500</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U83" s="3">
         <v>429900</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V83" s="3">
+      <c r="V83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W83" s="3">
         <v>468900</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X83" s="3">
+      <c r="X83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y83" s="3">
         <v>412000</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z83" s="3">
+      <c r="Z83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA83" s="3">
         <v>249800</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB83" s="3">
+      <c r="AB83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC83" s="3">
         <v>277000</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD83" s="3">
+      <c r="AD83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE83" s="3">
         <v>278300</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF83" s="3">
+      <c r="AF83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG83" s="3">
         <v>275200</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E89" s="3">
-        <v>1584400</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-568300</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I89" s="3">
-        <v>896900</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="D89" s="3">
+        <v>-708600</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3">
+        <v>1624800</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-582700</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J89" s="3">
+        <v>919700</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L89" s="3">
         <v>-4008400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2592000</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q89" s="3">
         <v>2450400</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U89" s="3">
         <v>2696100</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V89" s="3">
+      <c r="V89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W89" s="3">
         <v>-173600</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X89" s="3">
+      <c r="X89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y89" s="3">
         <v>2140900</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z89" s="3">
+      <c r="Z89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA89" s="3">
         <v>94200</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB89" s="3">
+      <c r="AB89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC89" s="3">
         <v>1724900</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD89" s="3">
+      <c r="AD89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE89" s="3">
         <v>111600</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF89" s="3">
+      <c r="AF89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG89" s="3">
         <v>2248600</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-107000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-113400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-103800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-106300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-117000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-154800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-138300</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-132200</v>
       </c>
       <c r="K91" s="3">
         <v>-132200</v>
       </c>
       <c r="L91" s="3">
-        <v>-140500</v>
+        <v>-132200</v>
       </c>
       <c r="M91" s="3">
         <v>-140500</v>
       </c>
       <c r="N91" s="3">
+        <v>-140500</v>
+      </c>
+      <c r="O91" s="3">
         <v>-227100</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-260300</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="R91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U91" s="3">
         <v>-263800</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V91" s="3">
+      <c r="V91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W91" s="3">
         <v>-200300</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="X91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-207100</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z91" s="3">
+      <c r="Z91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-204300</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB91" s="3">
+      <c r="AB91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-246400</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD91" s="3">
+      <c r="AD91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-130400</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF91" s="3">
+      <c r="AF91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-187600</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-486800</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-368500</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-523200</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="D94" s="3">
+        <v>-144300</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-499200</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-377900</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-536600</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L94" s="3">
         <v>581700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-818900</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-199900</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U94" s="3">
         <v>2316500</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V94" s="3">
+      <c r="V94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W94" s="3">
         <v>83800</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X94" s="3">
+      <c r="X94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-34200</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="Z94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA94" s="3">
         <v>272000</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB94" s="3">
+      <c r="AB94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-238300</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD94" s="3">
+      <c r="AD94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-413500</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF94" s="3">
+      <c r="AF94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-790700</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8127,10 +8361,10 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-541000</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-554800</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -8139,20 +8373,20 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-467600</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-479500</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-401300</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -8160,11 +8394,11 @@
         <v>0</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-145500</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -8172,11 +8406,11 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-1023500</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -8184,11 +8418,11 @@
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-987200</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
@@ -8196,11 +8430,11 @@
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-980200</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
         <v>0</v>
       </c>
@@ -8208,13 +8442,16 @@
         <v>0</v>
       </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-811800</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-1157700</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G100" s="3">
-        <v>410000</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-2445300</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="D100" s="3">
+        <v>1040600</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-1187100</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H100" s="3">
+        <v>420400</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-2507600</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" s="3">
         <v>1548600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2622900</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-298700</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U100" s="3">
         <v>-3561900</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="V100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W100" s="3">
         <v>-426000</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="X100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-1759300</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="Z100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-364300</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB100" s="3">
+      <c r="AB100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-1706200</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD100" s="3">
+      <c r="AD100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE100" s="3">
         <v>681500</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AF100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-1132700</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E101" s="3">
-        <v>-101900</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-75500</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I101" s="3">
-        <v>82200</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="D101" s="3">
+        <v>-77400</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-104500</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-77400</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3">
+        <v>84200</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" s="3">
         <v>278100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-165900</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-118300</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T101" s="3">
+      <c r="R101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U101" s="3">
         <v>-138300</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V101" s="3">
+      <c r="V101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W101" s="3">
         <v>16100</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X101" s="3">
+      <c r="X101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y101" s="3">
         <v>21900</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z101" s="3">
+      <c r="Z101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-101000</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB101" s="3">
+      <c r="AB101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-58700</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD101" s="3">
+      <c r="AD101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE101" s="3">
         <v>23200</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF101" s="3">
+      <c r="AF101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG101" s="3">
         <v>71900</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E102" s="3">
-        <v>-161900</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-602300</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-1989500</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K102" s="3">
+      <c r="D102" s="3">
+        <v>110200</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-166000</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-617700</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-2040200</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L102" s="3">
         <v>-1600000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1015600</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P102" s="3">
+      <c r="P102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q102" s="3">
         <v>1833500</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U102" s="3">
         <v>1312400</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V102" s="3">
+      <c r="V102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W102" s="3">
         <v>-499700</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X102" s="3">
+      <c r="X102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y102" s="3">
         <v>369300</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="Z102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-99000</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB102" s="3">
+      <c r="AB102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-278200</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD102" s="3">
+      <c r="AD102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE102" s="3">
         <v>402900</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF102" s="3">
+      <c r="AF102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG102" s="3">
         <v>397000</v>
       </c>
-      <c r="AG102" s="3" t="s">
+      <c r="AH102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WPP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WPP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="92">
   <si>
     <t>WPP</t>
   </si>
@@ -801,25 +801,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>9483300</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>5</v>
+        <v>4566700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>4563800</v>
       </c>
       <c r="F8" s="3">
-        <v>10003700</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>5</v>
+        <v>4855300</v>
+      </c>
+      <c r="G8" s="3">
+        <v>4651600</v>
       </c>
       <c r="H8" s="3">
-        <v>9475700</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>5</v>
+        <v>4588200</v>
+      </c>
+      <c r="I8" s="3">
+        <v>4466700</v>
       </c>
       <c r="J8" s="3">
-        <v>10069000</v>
+        <v>4622800</v>
       </c>
       <c r="K8" s="3">
         <v>4572000</v>
@@ -899,25 +899,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>8118600</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
+        <v>3909500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3907000</v>
       </c>
       <c r="F9" s="3">
-        <v>8094700</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>5</v>
+        <v>3928800</v>
+      </c>
+      <c r="G9" s="3">
+        <v>3763900</v>
       </c>
       <c r="H9" s="3">
-        <v>8079200</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
+        <v>3912100</v>
+      </c>
+      <c r="I9" s="3">
+        <v>3808500</v>
       </c>
       <c r="J9" s="3">
-        <v>8112000</v>
+        <v>3724300</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
@@ -997,25 +997,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1364700</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
+        <v>657200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>656700</v>
       </c>
       <c r="F10" s="3">
-        <v>1909000</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
+        <v>926500</v>
+      </c>
+      <c r="G10" s="3">
+        <v>887700</v>
       </c>
       <c r="H10" s="3">
-        <v>1396400</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
+        <v>676100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>658200</v>
       </c>
       <c r="J10" s="3">
-        <v>1957000</v>
+        <v>898500</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1333,10 +1333,10 @@
         <v>5</v>
       </c>
       <c r="F14" s="3">
-        <v>-44600</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
+        <v>-18100</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-17300</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>5</v>
@@ -1345,7 +1345,7 @@
         <v>5</v>
       </c>
       <c r="J14" s="3">
-        <v>76400</v>
+        <v>-24900</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
@@ -1425,25 +1425,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>83400</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>83400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>88100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>84400</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>80700</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>78600</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1556,25 +1556,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8928200</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>5</v>
+        <v>4299400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4296600</v>
       </c>
       <c r="F17" s="3">
-        <v>9664000</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>5</v>
+        <v>4718600</v>
+      </c>
+      <c r="G17" s="3">
+        <v>4520700</v>
       </c>
       <c r="H17" s="3">
-        <v>9074000</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>5</v>
+        <v>4393800</v>
+      </c>
+      <c r="I17" s="3">
+        <v>4277400</v>
       </c>
       <c r="J17" s="3">
-        <v>9070100</v>
+        <v>4132700</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>5</v>
@@ -1654,25 +1654,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>555100</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>5</v>
+        <v>267300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>267100</v>
       </c>
       <c r="F18" s="3">
-        <v>339700</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>5</v>
+        <v>136700</v>
+      </c>
+      <c r="G18" s="3">
+        <v>130900</v>
       </c>
       <c r="H18" s="3">
-        <v>401700</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>5</v>
+        <v>194400</v>
+      </c>
+      <c r="I18" s="3">
+        <v>189300</v>
       </c>
       <c r="J18" s="3">
-        <v>999000</v>
+        <v>490200</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>5</v>
@@ -1788,25 +1788,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>164000</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>5</v>
+        <v>-32200</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-32200</v>
       </c>
       <c r="F20" s="3">
-        <v>40800</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>5</v>
+        <v>-14100</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-13500</v>
       </c>
       <c r="H20" s="3">
-        <v>169100</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>5</v>
+        <v>-16500</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-16100</v>
       </c>
       <c r="J20" s="3">
-        <v>247300</v>
+        <v>-3000</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>5</v>
@@ -1886,25 +1886,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1062900</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>5</v>
+        <v>382900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>382700</v>
       </c>
       <c r="F21" s="3">
-        <v>1921800</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>5</v>
+        <v>238900</v>
+      </c>
+      <c r="G21" s="3">
+        <v>228900</v>
       </c>
       <c r="H21" s="3">
-        <v>910100</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>5</v>
+        <v>291600</v>
+      </c>
+      <c r="I21" s="3">
+        <v>283900</v>
       </c>
       <c r="J21" s="3">
-        <v>1919600</v>
+        <v>568100</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -1984,25 +1984,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>275600</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>5</v>
+        <v>132700</v>
+      </c>
+      <c r="E22" s="3">
+        <v>132600</v>
       </c>
       <c r="F22" s="3">
-        <v>194200</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>5</v>
+        <v>94300</v>
+      </c>
+      <c r="G22" s="3">
+        <v>90300</v>
       </c>
       <c r="H22" s="3">
-        <v>302700</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>5</v>
+        <v>146800</v>
+      </c>
+      <c r="I22" s="3">
+        <v>142900</v>
       </c>
       <c r="J22" s="3">
-        <v>273700</v>
+        <v>125700</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>5</v>
@@ -2082,25 +2082,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>443500</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>5</v>
+        <v>213600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>213400</v>
       </c>
       <c r="F23" s="3">
-        <v>186300</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>5</v>
+        <v>90400</v>
+      </c>
+      <c r="G23" s="3">
+        <v>86600</v>
       </c>
       <c r="H23" s="3">
-        <v>268100</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>5</v>
+        <v>129600</v>
+      </c>
+      <c r="I23" s="3">
+        <v>126200</v>
       </c>
       <c r="J23" s="3">
-        <v>972600</v>
+        <v>446500</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>5</v>
@@ -2180,25 +2180,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>120700</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>5</v>
+        <v>58100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>58100</v>
       </c>
       <c r="F24" s="3">
-        <v>123500</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>5</v>
+        <v>59900</v>
+      </c>
+      <c r="G24" s="3">
+        <v>57400</v>
       </c>
       <c r="H24" s="3">
-        <v>72200</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>5</v>
+        <v>34900</v>
+      </c>
+      <c r="I24" s="3">
+        <v>34000</v>
       </c>
       <c r="J24" s="3">
-        <v>350200</v>
+        <v>160800</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>5</v>
@@ -2376,25 +2376,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>322800</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>5</v>
+        <v>155400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>155300</v>
       </c>
       <c r="F26" s="3">
-        <v>62900</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>5</v>
+        <v>30500</v>
+      </c>
+      <c r="G26" s="3">
+        <v>29200</v>
       </c>
       <c r="H26" s="3">
-        <v>195900</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>5</v>
+        <v>94700</v>
+      </c>
+      <c r="I26" s="3">
+        <v>92200</v>
       </c>
       <c r="J26" s="3">
-        <v>622400</v>
+        <v>285700</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>5</v>
@@ -2474,25 +2474,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>269000</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>5</v>
+        <v>129500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>129500</v>
       </c>
       <c r="F27" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>5</v>
+        <v>-1000</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-1000</v>
       </c>
       <c r="H27" s="3">
-        <v>147000</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>5</v>
+        <v>71200</v>
+      </c>
+      <c r="I27" s="3">
+        <v>69300</v>
       </c>
       <c r="J27" s="3">
-        <v>557400</v>
+        <v>255900</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>5</v>
@@ -2964,25 +2964,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-164000</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>5</v>
+        <v>32200</v>
+      </c>
+      <c r="E32" s="3">
+        <v>32200</v>
       </c>
       <c r="F32" s="3">
-        <v>-40800</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>5</v>
+        <v>14100</v>
+      </c>
+      <c r="G32" s="3">
+        <v>13500</v>
       </c>
       <c r="H32" s="3">
-        <v>-169100</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>5</v>
+        <v>16500</v>
+      </c>
+      <c r="I32" s="3">
+        <v>16100</v>
       </c>
       <c r="J32" s="3">
-        <v>-247300</v>
+        <v>3000</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>5</v>
@@ -3062,25 +3062,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>269000</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>5</v>
+        <v>129500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>129500</v>
       </c>
       <c r="F33" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>5</v>
+        <v>-1000</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-1000</v>
       </c>
       <c r="H33" s="3">
-        <v>147000</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>5</v>
+        <v>71200</v>
+      </c>
+      <c r="I33" s="3">
+        <v>69300</v>
       </c>
       <c r="J33" s="3">
-        <v>557400</v>
+        <v>255900</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>5</v>
@@ -3258,25 +3258,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>269000</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>5</v>
+        <v>129500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>129500</v>
       </c>
       <c r="F35" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>5</v>
+        <v>-1000</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-1000</v>
       </c>
       <c r="H35" s="3">
-        <v>147000</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>5</v>
+        <v>71200</v>
+      </c>
+      <c r="I35" s="3">
+        <v>69300</v>
       </c>
       <c r="J35" s="3">
-        <v>557400</v>
+        <v>255900</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>5</v>
@@ -3531,25 +3531,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2792400</v>
+        <v>2689300</v>
       </c>
       <c r="E41" s="3">
-        <v>2909800</v>
+        <v>2687600</v>
       </c>
       <c r="F41" s="3">
-        <v>2575300</v>
+        <v>2594400</v>
       </c>
       <c r="G41" s="3">
-        <v>3269300</v>
+        <v>2485500</v>
       </c>
       <c r="H41" s="3">
-        <v>2329200</v>
+        <v>2494100</v>
       </c>
       <c r="I41" s="3">
-        <v>5095100</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>5</v>
+        <v>2428000</v>
+      </c>
+      <c r="J41" s="3">
+        <v>2737000</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>5</v>
@@ -3635,10 +3635,10 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>230200</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>220500</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
@@ -3647,7 +3647,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>265000</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3727,25 +3727,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>14758300</v>
+        <v>14213900</v>
       </c>
       <c r="E43" s="3">
-        <v>14712300</v>
+        <v>14204700</v>
       </c>
       <c r="F43" s="3">
-        <v>13867500</v>
+        <v>14629700</v>
       </c>
       <c r="G43" s="3">
-        <v>15763100</v>
+        <v>14015900</v>
       </c>
       <c r="H43" s="3">
-        <v>14676400</v>
+        <v>13801800</v>
       </c>
       <c r="I43" s="3">
-        <v>14409100</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>5</v>
+        <v>13436300</v>
+      </c>
+      <c r="J43" s="3">
+        <v>14898600</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>5</v>
@@ -3827,20 +3827,20 @@
       <c r="D44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E44" s="3">
-        <v>359000</v>
-      </c>
-      <c r="F44" s="3">
-        <v>384100</v>
-      </c>
-      <c r="G44" s="3">
-        <v>462400</v>
-      </c>
-      <c r="H44" s="3">
-        <v>451100</v>
-      </c>
-      <c r="I44" s="3">
-        <v>333300</v>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>5</v>
@@ -3925,23 +3925,23 @@
       <c r="D45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E45" s="3">
-        <v>315700</v>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F45" s="3">
-        <v>404300</v>
+        <v>2000</v>
       </c>
       <c r="G45" s="3">
-        <v>317200</v>
+        <v>2000</v>
       </c>
       <c r="H45" s="3">
-        <v>390000</v>
+        <v>3000</v>
       </c>
       <c r="I45" s="3">
-        <v>285800</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>5</v>
+        <v>3000</v>
+      </c>
+      <c r="J45" s="3">
+        <v>6100</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>5</v>
@@ -4021,25 +4021,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>17550700</v>
+        <v>16903200</v>
       </c>
       <c r="E46" s="3">
-        <v>18296800</v>
+        <v>16892300</v>
       </c>
       <c r="F46" s="3">
-        <v>17231200</v>
+        <v>17760700</v>
       </c>
       <c r="G46" s="3">
-        <v>19812000</v>
+        <v>17015600</v>
       </c>
       <c r="H46" s="3">
-        <v>17846700</v>
+        <v>16687400</v>
       </c>
       <c r="I46" s="3">
-        <v>20123400</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>5</v>
+        <v>16245400</v>
+      </c>
+      <c r="J46" s="3">
+        <v>18191800</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>5</v>
@@ -4119,25 +4119,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1066800</v>
+        <v>711500</v>
       </c>
       <c r="E47" s="3">
-        <v>912900</v>
+        <v>711100</v>
       </c>
       <c r="F47" s="3">
-        <v>896800</v>
+        <v>788700</v>
       </c>
       <c r="G47" s="3">
-        <v>982800</v>
+        <v>755600</v>
       </c>
       <c r="H47" s="3">
-        <v>1017000</v>
+        <v>738300</v>
       </c>
       <c r="I47" s="3">
-        <v>1020600</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>5</v>
+        <v>718800</v>
+      </c>
+      <c r="J47" s="3">
+        <v>813200</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>5</v>
@@ -4217,25 +4217,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2817300</v>
+        <v>2713400</v>
       </c>
       <c r="E48" s="3">
-        <v>2900900</v>
+        <v>2711600</v>
       </c>
       <c r="F48" s="3">
-        <v>3145200</v>
+        <v>2815900</v>
       </c>
       <c r="G48" s="3">
-        <v>3318800</v>
+        <v>2697800</v>
       </c>
       <c r="H48" s="3">
-        <v>3181800</v>
+        <v>3046000</v>
       </c>
       <c r="I48" s="3">
-        <v>3006900</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
+        <v>2965300</v>
+      </c>
+      <c r="J48" s="3">
+        <v>3047400</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
@@ -4315,25 +4315,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>11990900</v>
+        <v>11548500</v>
       </c>
       <c r="E49" s="3">
-        <v>12123200</v>
+        <v>11541100</v>
       </c>
       <c r="F49" s="3">
-        <v>12856500</v>
+        <v>11768000</v>
       </c>
       <c r="G49" s="3">
-        <v>12997700</v>
+        <v>11274300</v>
       </c>
       <c r="H49" s="3">
-        <v>12737100</v>
+        <v>12450900</v>
       </c>
       <c r="I49" s="3">
-        <v>11772800</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>5</v>
+        <v>12121100</v>
+      </c>
+      <c r="J49" s="3">
+        <v>11934800</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>5</v>
@@ -4609,25 +4609,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>446100</v>
+        <v>315900</v>
       </c>
       <c r="E52" s="3">
-        <v>700200</v>
+        <v>315700</v>
       </c>
       <c r="F52" s="3">
-        <v>583400</v>
+        <v>363900</v>
       </c>
       <c r="G52" s="3">
-        <v>709500</v>
+        <v>348600</v>
       </c>
       <c r="H52" s="3">
-        <v>667400</v>
+        <v>329400</v>
       </c>
       <c r="I52" s="3">
-        <v>648400</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>5</v>
+        <v>320700</v>
+      </c>
+      <c r="J52" s="3">
+        <v>352700</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>5</v>
@@ -4805,25 +4805,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>33871800</v>
+        <v>32622200</v>
       </c>
       <c r="E54" s="3">
-        <v>34933900</v>
+        <v>32601200</v>
       </c>
       <c r="F54" s="3">
-        <v>34713100</v>
+        <v>33910400</v>
       </c>
       <c r="G54" s="3">
-        <v>37820900</v>
+        <v>32487700</v>
       </c>
       <c r="H54" s="3">
-        <v>35450000</v>
+        <v>33617700</v>
       </c>
       <c r="I54" s="3">
-        <v>36572100</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>5</v>
+        <v>32727300</v>
+      </c>
+      <c r="J54" s="3">
+        <v>34728000</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>5</v>
@@ -4975,25 +4975,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>15630900</v>
+        <v>15054300</v>
       </c>
       <c r="E57" s="3">
-        <v>14301700</v>
+        <v>15044600</v>
       </c>
       <c r="F57" s="3">
-        <v>12366700</v>
+        <v>13789300</v>
       </c>
       <c r="G57" s="3">
-        <v>14754800</v>
+        <v>13210800</v>
       </c>
       <c r="H57" s="3">
-        <v>12747200</v>
+        <v>11883300</v>
       </c>
       <c r="I57" s="3">
-        <v>14017600</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>5</v>
+        <v>11568600</v>
+      </c>
+      <c r="J57" s="3">
+        <v>13473500</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>5</v>
@@ -5073,25 +5073,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1921100</v>
+        <v>1850200</v>
       </c>
       <c r="E58" s="3">
-        <v>1625300</v>
+        <v>1849000</v>
       </c>
       <c r="F58" s="3">
-        <v>1825400</v>
+        <v>1577700</v>
       </c>
       <c r="G58" s="3">
-        <v>1904500</v>
+        <v>1511500</v>
       </c>
       <c r="H58" s="3">
-        <v>764600</v>
+        <v>1767800</v>
       </c>
       <c r="I58" s="3">
-        <v>1111300</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>5</v>
+        <v>1721000</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1748800</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>5</v>
@@ -5171,25 +5171,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2115300</v>
+        <v>2037200</v>
       </c>
       <c r="E59" s="3">
-        <v>5397300</v>
+        <v>2035900</v>
       </c>
       <c r="F59" s="3">
-        <v>5321600</v>
+        <v>5332600</v>
       </c>
       <c r="G59" s="3">
-        <v>6577500</v>
+        <v>5108900</v>
       </c>
       <c r="H59" s="3">
-        <v>6017400</v>
+        <v>5246900</v>
       </c>
       <c r="I59" s="3">
-        <v>6503300</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>5</v>
+        <v>5107900</v>
+      </c>
+      <c r="J59" s="3">
+        <v>6114300</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>5</v>
@@ -5269,25 +5269,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>19667300</v>
+        <v>18941700</v>
       </c>
       <c r="E60" s="3">
-        <v>21324300</v>
+        <v>18929500</v>
       </c>
       <c r="F60" s="3">
-        <v>19513700</v>
+        <v>20699500</v>
       </c>
       <c r="G60" s="3">
-        <v>23236800</v>
+        <v>19831100</v>
       </c>
       <c r="H60" s="3">
-        <v>19529200</v>
+        <v>18898000</v>
       </c>
       <c r="I60" s="3">
-        <v>21632100</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>5</v>
+        <v>18397400</v>
+      </c>
+      <c r="J60" s="3">
+        <v>21336600</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>5</v>
@@ -5367,25 +5367,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7975600</v>
+        <v>7681300</v>
       </c>
       <c r="E61" s="3">
-        <v>7397100</v>
+        <v>7676400</v>
       </c>
       <c r="F61" s="3">
-        <v>8193200</v>
+        <v>7180400</v>
       </c>
       <c r="G61" s="3">
-        <v>7518900</v>
+        <v>6879200</v>
       </c>
       <c r="H61" s="3">
-        <v>8473500</v>
+        <v>7934700</v>
       </c>
       <c r="I61" s="3">
-        <v>7845500</v>
+        <v>7724500</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>6904000</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5465,25 +5465,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1035300</v>
+        <v>595200</v>
       </c>
       <c r="E62" s="3">
-        <v>1183200</v>
+        <v>594900</v>
       </c>
       <c r="F62" s="3">
-        <v>1671900</v>
+        <v>748100</v>
       </c>
       <c r="G62" s="3">
-        <v>1605900</v>
+        <v>716700</v>
       </c>
       <c r="H62" s="3">
-        <v>1843600</v>
+        <v>1018200</v>
       </c>
       <c r="I62" s="3">
-        <v>1755100</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>5</v>
+        <v>991200</v>
+      </c>
+      <c r="J62" s="3">
+        <v>886200</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>5</v>
@@ -5857,25 +5857,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>29283100</v>
+        <v>27620200</v>
       </c>
       <c r="E66" s="3">
-        <v>30504500</v>
+        <v>27602400</v>
       </c>
       <c r="F66" s="3">
-        <v>29940300</v>
+        <v>29028500</v>
       </c>
       <c r="G66" s="3">
-        <v>32990900</v>
+        <v>27810600</v>
       </c>
       <c r="H66" s="3">
-        <v>30474300</v>
+        <v>28451800</v>
       </c>
       <c r="I66" s="3">
-        <v>31826600</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>5</v>
+        <v>27698200</v>
+      </c>
+      <c r="J66" s="3">
+        <v>29715200</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>5</v>
@@ -6383,25 +6383,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4915500</v>
+        <v>4559800</v>
       </c>
       <c r="E72" s="3">
-        <v>4822300</v>
+        <v>4556800</v>
       </c>
       <c r="F72" s="3">
-        <v>5195500</v>
+        <v>4443400</v>
       </c>
       <c r="G72" s="3">
-        <v>5307700</v>
+        <v>4256900</v>
       </c>
       <c r="H72" s="3">
-        <v>5489200</v>
+        <v>4898300</v>
       </c>
       <c r="I72" s="3">
-        <v>5290000</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>5</v>
+        <v>4768500</v>
+      </c>
+      <c r="J72" s="3">
+        <v>4530000</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>5</v>
@@ -6775,25 +6775,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4588800</v>
+        <v>4419500</v>
       </c>
       <c r="E76" s="3">
-        <v>4429500</v>
+        <v>4416600</v>
       </c>
       <c r="F76" s="3">
-        <v>4772700</v>
+        <v>4299700</v>
       </c>
       <c r="G76" s="3">
-        <v>4829900</v>
+        <v>4119300</v>
       </c>
       <c r="H76" s="3">
-        <v>4975700</v>
+        <v>4622100</v>
       </c>
       <c r="I76" s="3">
-        <v>4745400</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>5</v>
+        <v>4499700</v>
+      </c>
+      <c r="J76" s="3">
+        <v>4435000</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>5</v>
@@ -7074,25 +7074,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>269000</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>5</v>
+        <v>129500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>129500</v>
       </c>
       <c r="F81" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>5</v>
+        <v>-1000</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-1000</v>
       </c>
       <c r="H81" s="3">
-        <v>147000</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>5</v>
+        <v>71200</v>
+      </c>
+      <c r="I81" s="3">
+        <v>69300</v>
       </c>
       <c r="J81" s="3">
-        <v>557400</v>
+        <v>255900</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>5</v>
@@ -7208,25 +7208,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>325400</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>5</v>
+        <v>135300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>131800</v>
       </c>
       <c r="F83" s="3">
-        <v>1508800</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>5</v>
+        <v>132100</v>
+      </c>
+      <c r="G83" s="3">
+        <v>122200</v>
       </c>
       <c r="H83" s="3">
-        <v>327500</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>5</v>
+        <v>127500</v>
+      </c>
+      <c r="I83" s="3">
+        <v>137900</v>
       </c>
       <c r="J83" s="3">
-        <v>644600</v>
+        <v>144600</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>5</v>
@@ -7796,25 +7796,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-708600</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>5</v>
+        <v>-341200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-341000</v>
       </c>
       <c r="F89" s="3">
-        <v>1624800</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>5</v>
+        <v>1071400</v>
+      </c>
+      <c r="G89" s="3">
+        <v>1026500</v>
       </c>
       <c r="H89" s="3">
-        <v>-582700</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>5</v>
+        <v>-282800</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-275300</v>
       </c>
       <c r="J89" s="3">
-        <v>919700</v>
+        <v>1104500</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>5</v>
@@ -7930,25 +7930,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-107000</v>
+        <v>-51800</v>
       </c>
       <c r="E91" s="3">
-        <v>-113400</v>
+        <v>-51800</v>
       </c>
       <c r="F91" s="3">
-        <v>-103800</v>
+        <v>-61500</v>
       </c>
       <c r="G91" s="3">
-        <v>-106300</v>
+        <v>-58900</v>
       </c>
       <c r="H91" s="3">
-        <v>-117000</v>
+        <v>-51500</v>
       </c>
       <c r="I91" s="3">
-        <v>-154800</v>
+        <v>-50100</v>
       </c>
       <c r="J91" s="3">
-        <v>-138300</v>
+        <v>-63900</v>
       </c>
       <c r="K91" s="3">
         <v>-132200</v>
@@ -8224,25 +8224,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-144300</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>5</v>
+        <v>-69500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-69500</v>
       </c>
       <c r="F94" s="3">
-        <v>-499200</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>5</v>
+        <v>-58800</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-56400</v>
       </c>
       <c r="H94" s="3">
-        <v>-377900</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>5</v>
+        <v>-183000</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-178100</v>
       </c>
       <c r="J94" s="3">
-        <v>-536600</v>
+        <v>-147400</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>5</v>
@@ -8357,26 +8357,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F96" s="3">
-        <v>-554800</v>
+        <v>269300</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
+        <v>258000</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J96" s="3">
-        <v>-479500</v>
+        <v>220100</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8750,25 +8750,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1040600</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>5</v>
+        <v>501100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>500800</v>
       </c>
       <c r="F100" s="3">
-        <v>-1187100</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>5</v>
+        <v>-780200</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-747500</v>
       </c>
       <c r="H100" s="3">
-        <v>420400</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>5</v>
+        <v>204000</v>
+      </c>
+      <c r="I100" s="3">
+        <v>198600</v>
       </c>
       <c r="J100" s="3">
-        <v>-2507600</v>
+        <v>-643700</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>5</v>
@@ -8848,25 +8848,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-77400</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>5</v>
+        <v>-37500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-36500</v>
       </c>
       <c r="F101" s="3">
-        <v>-104500</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>5</v>
+        <v>-14300</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-13300</v>
       </c>
       <c r="H101" s="3">
-        <v>-77400</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>5</v>
+        <v>53500</v>
+      </c>
+      <c r="I101" s="3">
+        <v>57800</v>
       </c>
       <c r="J101" s="3">
-        <v>84200</v>
+        <v>-18600</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>5</v>
@@ -8946,25 +8946,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>110200</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>5</v>
+        <v>53100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>53000</v>
       </c>
       <c r="F102" s="3">
-        <v>-166000</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>5</v>
+        <v>219200</v>
+      </c>
+      <c r="G102" s="3">
+        <v>210000</v>
       </c>
       <c r="H102" s="3">
-        <v>-617700</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>5</v>
+        <v>-299300</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-291300</v>
       </c>
       <c r="J102" s="3">
-        <v>-2040200</v>
+        <v>299100</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>5</v>

--- a/AAII_Financials/Quarterly/WPP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WPP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="92">
   <si>
     <t>WPP</t>
   </si>
@@ -656,441 +656,466 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4703500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>5035500</v>
+      </c>
+      <c r="F8" s="3">
         <v>4566700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>4563800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>4855300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>4651600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>4588200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>4466700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>4622800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>4572000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>8613700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>8503100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>4106100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>7609200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>3454700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>7656000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>3512000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>6810300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>3811700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>9363600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>5576900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>8744700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>4927000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>7335700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>4628400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>9686600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>4595900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>10635100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>4759400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>9978500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>4831200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>10340000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>4754900</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3820200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4089900</v>
+      </c>
+      <c r="F9" s="3">
         <v>3909500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>3907000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>3928800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>3763900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>3912100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>3808500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>3724300</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" s="3">
         <v>7278400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>6887300</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3">
         <v>6447300</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3">
         <v>6181000</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U9" s="3">
         <v>5861300</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W9" s="3">
         <v>7495800</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y9" s="3">
         <v>7317500</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA9" s="3">
         <v>5732800</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC9" s="3">
         <v>8039600</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE9" s="3">
         <v>8278100</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG9" s="3">
         <v>8194100</v>
       </c>
-      <c r="AF9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI9" s="3">
         <v>13701700</v>
       </c>
-      <c r="AH9" s="3" t="s">
+      <c r="AJ9" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>883200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>945600</v>
+      </c>
+      <c r="F10" s="3">
         <v>657200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>656700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>926500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>887700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>676100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>658200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>898500</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N10" s="3">
         <v>1335300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1615800</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3">
         <v>1161900</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3">
         <v>1475000</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U10" s="3">
         <v>949100</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W10" s="3">
         <v>1867800</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y10" s="3">
         <v>1427300</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA10" s="3">
         <v>1602900</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC10" s="3">
         <v>1647000</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE10" s="3">
         <v>2357000</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="3">
         <v>1784400</v>
       </c>
-      <c r="AF10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI10" s="3">
         <v>-3361800</v>
       </c>
-      <c r="AH10" s="3" t="s">
+      <c r="AJ10" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,8 +1150,10 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,8 +1250,14 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,8 +1354,14 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1332,125 +1371,131 @@
       <c r="E14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
         <v>-18100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>-17300</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>-24900</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>97000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>94400</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-14500</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3">
         <v>112900</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="3">
         <v>62700</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W14" s="3">
         <v>46600</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y14" s="3">
         <v>18700</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA14" s="3">
         <v>17300</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC14" s="3">
         <v>36700</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG14" s="3">
         <v>25300</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI14" s="3">
         <v>-295800</v>
       </c>
-      <c r="AH14" s="3" t="s">
+      <c r="AJ14" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>80700</v>
+      </c>
+      <c r="E15" s="3">
+        <v>86400</v>
+      </c>
+      <c r="F15" s="3">
         <v>83400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>83400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>88100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>84400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>80700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>78600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>75000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1487,11 +1532,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z15" s="3" t="s">
-        <v>5</v>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
       </c>
       <c r="AA15" s="3" t="s">
         <v>5</v>
@@ -1505,20 +1550,26 @@
       <c r="AD15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AE15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG15" s="3">
         <v>127600</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI15" s="3">
         <v>119600</v>
       </c>
-      <c r="AH15" s="3" t="s">
+      <c r="AJ15" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1601,218 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4138900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4431000</v>
+      </c>
+      <c r="F17" s="3">
         <v>4299400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>4296600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>4718600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>4520700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>4393800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>4277400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4132700</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N17" s="3">
         <v>8023800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>7647000</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="3">
         <v>6994600</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S17" s="3">
         <v>7559900</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U17" s="3">
         <v>10228500</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W17" s="3">
         <v>8456200</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y17" s="3">
         <v>7944600</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA17" s="3">
         <v>6829900</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC17" s="3">
         <v>8634900</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE17" s="3">
         <v>9091000</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG17" s="3">
         <v>9033700</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI17" s="3">
         <v>8352300</v>
       </c>
-      <c r="AH17" s="3" t="s">
+      <c r="AJ17" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>564600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>604500</v>
+      </c>
+      <c r="F18" s="3">
         <v>267300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>267100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>136700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>130900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>194400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>189300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>490200</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N18" s="3">
         <v>589900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>856100</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="3">
         <v>614600</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S18" s="3">
         <v>96100</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U18" s="3">
         <v>-3418200</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W18" s="3">
         <v>907500</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y18" s="3">
         <v>800200</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA18" s="3">
         <v>505700</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC18" s="3">
         <v>1051700</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE18" s="3">
         <v>1544000</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG18" s="3">
         <v>944800</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI18" s="3">
         <v>1987700</v>
       </c>
-      <c r="AH18" s="3" t="s">
+      <c r="AJ18" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,498 +1847,530 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E20" s="3">
+        <v>43600</v>
+      </c>
+      <c r="F20" s="3">
         <v>-32200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-32200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-14100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-13500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-16500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-16100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-3000</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>128700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>21900</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="3">
         <v>57400</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S20" s="3">
         <v>-164900</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U20" s="3">
         <v>-265800</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W20" s="3">
         <v>429700</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y20" s="3">
         <v>3800</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA20" s="3">
         <v>224700</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC20" s="3">
         <v>210900</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE20" s="3">
         <v>361800</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG20" s="3">
         <v>239100</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI20" s="3">
         <v>109800</v>
       </c>
-      <c r="AH20" s="3" t="s">
+      <c r="AJ20" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>604700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>647400</v>
+      </c>
+      <c r="F21" s="3">
         <v>382900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>382700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>238900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>228900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>291600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>283900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>568100</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N21" s="3">
         <v>352700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>1568900</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S21" s="3">
         <v>683700</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W21" s="3">
         <v>1782500</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y21" s="3">
         <v>1298100</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA21" s="3">
         <v>1169300</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC21" s="3">
         <v>1536000</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE21" s="3">
         <v>2206400</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG21" s="3">
         <v>1486100</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI21" s="3">
         <v>2400000</v>
       </c>
-      <c r="AH21" s="3" t="s">
+      <c r="AJ21" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>129600</v>
+      </c>
+      <c r="E22" s="3">
+        <v>138700</v>
+      </c>
+      <c r="F22" s="3">
         <v>132700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>132600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>94300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>90300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>146800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>142900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>125700</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N22" s="3">
         <v>184800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>168600</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="3">
         <v>182600</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S22" s="3">
         <v>180700</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U22" s="3">
         <v>191900</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W22" s="3">
         <v>238900</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y22" s="3">
         <v>242400</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA22" s="3">
         <v>187400</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC22" s="3">
         <v>168200</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE22" s="3">
         <v>171000</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG22" s="3">
         <v>167600</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI22" s="3">
         <v>167900</v>
       </c>
-      <c r="AH22" s="3" t="s">
+      <c r="AJ22" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>433800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>464400</v>
+      </c>
+      <c r="F23" s="3">
         <v>213600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>213400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>90400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>86600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>129600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>126200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>446500</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N23" s="3">
         <v>533800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>709500</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="3">
         <v>489400</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S23" s="3">
         <v>-249500</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U23" s="3">
         <v>-3875900</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W23" s="3">
         <v>1098300</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y23" s="3">
         <v>561600</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA23" s="3">
         <v>543000</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC23" s="3">
         <v>1094400</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE23" s="3">
         <v>1734900</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG23" s="3">
         <v>1016300</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI23" s="3">
         <v>1929600</v>
       </c>
-      <c r="AH23" s="3" t="s">
+      <c r="AJ23" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>194000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>207700</v>
+      </c>
+      <c r="F24" s="3">
         <v>58100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>58100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>59900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>57400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>34900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>34000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>160800</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N24" s="3">
         <v>149800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>156800</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q24" s="3">
         <v>132900</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S24" s="3">
         <v>125600</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U24" s="3">
         <v>13300</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W24" s="3">
         <v>226000</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y24" s="3">
         <v>150100</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA24" s="3">
         <v>151900</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC24" s="3">
         <v>182300</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE24" s="3">
         <v>335900</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG24" s="3">
         <v>189800</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI24" s="3">
         <v>323700</v>
       </c>
-      <c r="AH24" s="3" t="s">
+      <c r="AJ24" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2467,222 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>239700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>256700</v>
+      </c>
+      <c r="F26" s="3">
         <v>155400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>155300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>30500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>29200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>94700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>92200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>285700</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N26" s="3">
         <v>383900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>552600</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q26" s="3">
         <v>356500</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S26" s="3">
         <v>-375000</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U26" s="3">
         <v>-3889200</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W26" s="3">
         <v>872300</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y26" s="3">
         <v>411500</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA26" s="3">
         <v>391100</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC26" s="3">
         <v>912100</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE26" s="3">
         <v>1399000</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG26" s="3">
         <v>826500</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI26" s="3">
         <v>1606000</v>
       </c>
-      <c r="AH26" s="3" t="s">
+      <c r="AJ26" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>210900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>225800</v>
+      </c>
+      <c r="F27" s="3">
         <v>129500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>129500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>71200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>69300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>255900</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N27" s="3">
         <v>328800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>490900</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="3">
         <v>313600</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S27" s="3">
         <v>-414200</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U27" s="3">
         <v>-3914900</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W27" s="3">
         <v>805900</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y27" s="3">
         <v>369700</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA27" s="3">
         <v>348800</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC27" s="3">
         <v>869300</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE27" s="3">
         <v>1323200</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG27" s="3">
         <v>777500</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI27" s="3">
         <v>1520000</v>
       </c>
-      <c r="AH27" s="3" t="s">
+      <c r="AJ27" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2779,14 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2690,14 +2811,14 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>5</v>
@@ -2709,50 +2830,50 @@
         <v>5</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S29" s="3">
         <v>15900</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U29" s="3">
         <v>-8300</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W29" s="3">
         <v>-64100</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y29" s="3">
         <v>59300</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA29" s="3">
         <v>166900</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE29" s="3">
         <v>268700</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2762,8 +2883,14 @@
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2987,14 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3091,222 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-40700</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-43600</v>
+      </c>
+      <c r="F32" s="3">
         <v>32200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>32200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>14100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>13500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>16500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>16100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>3000</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>-128700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-21900</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-57400</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S32" s="3">
         <v>164900</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U32" s="3">
         <v>265800</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W32" s="3">
         <v>-429700</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-3800</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-224700</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-210900</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-361800</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-239100</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-109800</v>
       </c>
-      <c r="AH32" s="3" t="s">
+      <c r="AJ32" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>210900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>225800</v>
+      </c>
+      <c r="F33" s="3">
         <v>129500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>129500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>71200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>69300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>255900</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N33" s="3">
         <v>328800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>490900</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="3">
         <v>313600</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S33" s="3">
         <v>-398300</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U33" s="3">
         <v>-3923200</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W33" s="3">
         <v>741800</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y33" s="3">
         <v>429000</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA33" s="3">
         <v>515800</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC33" s="3">
         <v>869300</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE33" s="3">
         <v>1591900</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG33" s="3">
         <v>777500</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI33" s="3">
         <v>1520000</v>
       </c>
-      <c r="AH33" s="3" t="s">
+      <c r="AJ33" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3403,227 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>210900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>225800</v>
+      </c>
+      <c r="F35" s="3">
         <v>129500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>129500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>71200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>69300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>255900</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N35" s="3">
         <v>328800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>490900</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="3">
         <v>313600</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S35" s="3">
         <v>-398300</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U35" s="3">
         <v>-3923200</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W35" s="3">
         <v>741800</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y35" s="3">
         <v>429000</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA35" s="3">
         <v>515800</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC35" s="3">
         <v>869300</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE35" s="3">
         <v>1591900</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG35" s="3">
         <v>777500</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI35" s="3">
         <v>1520000</v>
       </c>
-      <c r="AH35" s="3" t="s">
+      <c r="AJ35" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3658,10 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,136 +3696,144 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2482600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2657800</v>
+      </c>
+      <c r="F41" s="3">
         <v>2689300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2687600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2594400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>2485500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2494100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2428000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2737000</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N41" s="3">
         <v>16447600</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P41" s="3">
+      <c r="P41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R41" s="3">
         <v>13482200</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U41" s="3">
+      <c r="U41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W41" s="3">
         <v>15418600</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y41" s="3">
         <v>2984200</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA41" s="3">
         <v>3491100</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC41" s="3">
         <v>2871300</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE41" s="3">
         <v>3119100</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG41" s="3">
         <v>3725100</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI41" s="3">
         <v>2970900</v>
       </c>
-      <c r="AH41" s="3" t="s">
+      <c r="AJ41" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>820000</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>877900</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>230200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>220500</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>265000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3703,11 +3882,11 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD42" s="3" t="s">
-        <v>5</v>
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="3">
+        <v>0</v>
       </c>
       <c r="AE42" s="3" t="s">
         <v>5</v>
@@ -3715,112 +3894,124 @@
       <c r="AF42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AG42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI42" s="3">
         <v>237900</v>
       </c>
-      <c r="AH42" s="3" t="s">
+      <c r="AJ42" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13522000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>14476600</v>
+      </c>
+      <c r="F43" s="3">
         <v>14213900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>14204700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>14629700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>14015900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>13801800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>13436300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>14898600</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N43" s="3">
         <v>13478100</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P43" s="3">
+      <c r="P43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R43" s="3">
         <v>27605700</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U43" s="3">
+      <c r="U43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W43" s="3">
         <v>15478600</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y43" s="3">
         <v>17299200</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA43" s="3">
         <v>16701500</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC43" s="3">
         <v>15659500</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE43" s="3">
         <v>15736500</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG43" s="3">
         <v>14605800</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI43" s="3">
         <v>16171500</v>
       </c>
-      <c r="AH43" s="3" t="s">
+      <c r="AJ43" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3848,567 +4039,603 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N44" s="3">
         <v>336800</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P44" s="3">
+      <c r="P44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R44" s="3">
         <v>416800</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U44" s="3">
+      <c r="U44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W44" s="3">
         <v>476600</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y44" s="3">
         <v>576100</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA44" s="3">
         <v>484100</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC44" s="3">
         <v>524600</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE44" s="3">
         <v>1076600</v>
       </c>
-      <c r="AD44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG44" s="3">
         <v>1113600</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI44" s="3">
         <v>527200</v>
       </c>
-      <c r="AH44" s="3" t="s">
+      <c r="AJ44" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="D45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3">
         <v>2000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>2000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>3000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>3000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>6100</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N45" s="3">
         <v>316600</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R45" s="3">
         <v>922800</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U45" s="3">
+      <c r="U45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W45" s="3">
         <v>1055300</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y45" s="3">
         <v>550600</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA45" s="3">
         <v>381200</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC45" s="3">
         <v>546200</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE45" s="3">
         <v>390400</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG45" s="3">
         <v>529400</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI45" s="3">
         <v>427600</v>
       </c>
-      <c r="AH45" s="3" t="s">
+      <c r="AJ45" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>17102500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>18309900</v>
+      </c>
+      <c r="F46" s="3">
         <v>16903200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>16892300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>17760700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>17015600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>16687400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>16245400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>18191800</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N46" s="3">
         <v>30579100</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P46" s="3">
+      <c r="P46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R46" s="3">
         <v>28329100</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U46" s="3">
+      <c r="U46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W46" s="3">
         <v>32429200</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y46" s="3">
         <v>21410100</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA46" s="3">
         <v>21057900</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC46" s="3">
         <v>19601700</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE46" s="3">
         <v>19769200</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG46" s="3">
         <v>19395900</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI46" s="3">
         <v>20335200</v>
       </c>
-      <c r="AH46" s="3" t="s">
+      <c r="AJ46" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>815000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>872500</v>
+      </c>
+      <c r="F47" s="3">
         <v>711500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>711100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>788700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>755600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>738300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>718800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>813200</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N47" s="3">
         <v>947100</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R47" s="3">
         <v>1727800</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U47" s="3">
+      <c r="U47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W47" s="3">
         <v>1788300</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y47" s="3">
         <v>1804800</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA47" s="3">
         <v>1933000</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC47" s="3">
         <v>2366400</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE47" s="3">
         <v>2893900</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG47" s="3">
         <v>3138300</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI47" s="3">
         <v>3133600</v>
       </c>
-      <c r="AH47" s="3" t="s">
+      <c r="AJ47" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2871900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3074700</v>
+      </c>
+      <c r="F48" s="3">
         <v>2713400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2711600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2815900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2697800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3046000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2965300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3047400</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N48" s="3">
         <v>2926900</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P48" s="3">
+      <c r="P48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R48" s="3">
         <v>3113000</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U48" s="3">
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W48" s="3">
         <v>3560200</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y48" s="3">
         <v>3858100</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA48" s="3">
         <v>1430400</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC48" s="3">
         <v>1332600</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE48" s="3">
         <v>1277600</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG48" s="3">
         <v>1213700</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI48" s="3">
         <v>1275600</v>
       </c>
-      <c r="AH48" s="3" t="s">
+      <c r="AJ48" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10449800</v>
+      </c>
+      <c r="E49" s="3">
+        <v>11187500</v>
+      </c>
+      <c r="F49" s="3">
         <v>11548500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>11541100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>11768000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>11274300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>12450900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>12121100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>11934800</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N49" s="3">
         <v>11193000</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P49" s="3">
+      <c r="P49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R49" s="3">
         <v>13808600</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U49" s="3">
+      <c r="U49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W49" s="3">
         <v>15791900</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y49" s="3">
         <v>20650400</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA49" s="3">
         <v>19871000</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC49" s="3">
         <v>19246300</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE49" s="3">
         <v>19527200</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG49" s="3">
         <v>19816900</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI49" s="3">
         <v>20320200</v>
       </c>
-      <c r="AH49" s="3" t="s">
+      <c r="AJ49" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4732,14 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4836,118 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>291700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>312300</v>
+      </c>
+      <c r="F52" s="3">
         <v>315900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>315700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>363900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>348600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>329400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>320700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>352700</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N52" s="3">
         <v>470600</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P52" s="3">
+      <c r="P52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R52" s="3">
         <v>388200</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U52" s="3">
+      <c r="U52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W52" s="3">
         <v>443900</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y52" s="3">
         <v>464300</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA52" s="3">
         <v>439800</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC52" s="3">
         <v>439900</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE52" s="3">
         <v>438900</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG52" s="3">
         <v>466900</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI52" s="3">
         <v>454700</v>
       </c>
-      <c r="AH52" s="3" t="s">
+      <c r="AJ52" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +5044,118 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>31935400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>34189800</v>
+      </c>
+      <c r="F54" s="3">
         <v>32622200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>32601200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>33910400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>32487700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>33617700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>32727300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>34728000</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N54" s="3">
         <v>46116700</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P54" s="3">
+      <c r="P54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R54" s="3">
         <v>47202600</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U54" s="3">
+      <c r="U54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W54" s="3">
         <v>54013400</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y54" s="3">
         <v>48187700</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA54" s="3">
         <v>44732100</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC54" s="3">
         <v>42987000</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE54" s="3">
         <v>43906700</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG54" s="3">
         <v>44031700</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI54" s="3">
         <v>45519200</v>
       </c>
-      <c r="AH54" s="3" t="s">
+      <c r="AJ54" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5190,10 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,448 +5228,474 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13316700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>14256800</v>
+      </c>
+      <c r="F57" s="3">
         <v>15054300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>15044600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>13789300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>13210800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>11883300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>11568600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>13473500</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N57" s="3">
         <v>13088000</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R57" s="3">
         <v>29450100</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W57" s="3">
         <v>14330400</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y57" s="3">
         <v>13887500</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA57" s="3">
         <v>14096100</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC57" s="3">
         <v>12676500</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE57" s="3">
         <v>13139200</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG57" s="3">
         <v>12223200</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI57" s="3">
         <v>13939300</v>
       </c>
-      <c r="AH57" s="3" t="s">
+      <c r="AJ57" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1031600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1104400</v>
+      </c>
+      <c r="F58" s="3">
         <v>1850200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1849000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1577700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1511500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1767800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1721000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1748800</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N58" s="3">
         <v>11403200</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P58" s="3">
+      <c r="P58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R58" s="3">
         <v>21343800</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U58" s="3">
+      <c r="U58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W58" s="3">
         <v>12732200</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y58" s="3">
         <v>2091600</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA58" s="3">
         <v>1353900</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC58" s="3">
         <v>413100</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE58" s="3">
         <v>1628000</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG58" s="3">
         <v>2433800</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI58" s="3">
         <v>1320100</v>
       </c>
-      <c r="AH58" s="3" t="s">
+      <c r="AJ58" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5076600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>5434900</v>
+      </c>
+      <c r="F59" s="3">
         <v>2037200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2035900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>5332600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>5108900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>5246900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>5107900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>6114300</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N59" s="3">
         <v>5125600</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R59" s="3">
         <v>5603100</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W59" s="3">
         <v>6277400</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y59" s="3">
         <v>6517600</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA59" s="3">
         <v>6487500</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC59" s="3">
         <v>6098600</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE59" s="3">
         <v>6282500</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG59" s="3">
         <v>6122800</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI59" s="3">
         <v>6816900</v>
       </c>
-      <c r="AH59" s="3" t="s">
+      <c r="AJ59" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19424900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>20796100</v>
+      </c>
+      <c r="F60" s="3">
         <v>18941700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>18929500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>20699500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>19831100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>18898000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>18397400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>21336600</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N60" s="3">
         <v>29616900</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P60" s="3">
+      <c r="P60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R60" s="3">
         <v>28685000</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U60" s="3">
+      <c r="U60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W60" s="3">
         <v>32674500</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y60" s="3">
         <v>22496700</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA60" s="3">
         <v>21937500</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC60" s="3">
         <v>19188100</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE60" s="3">
         <v>20235700</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG60" s="3">
         <v>19563000</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI60" s="3">
         <v>22076200</v>
       </c>
-      <c r="AH60" s="3" t="s">
+      <c r="AJ60" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6915600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>7403800</v>
+      </c>
+      <c r="F61" s="3">
         <v>7681300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>7676400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>7180400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>6879200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>7934700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>7724500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>6904000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>8680900</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>7148900</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -5418,147 +5703,159 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>8175600</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
         <v>9978600</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>7442400</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>8446400</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>8152500</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
         <v>8598700</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
         <v>7327800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>577100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>617900</v>
+      </c>
+      <c r="F62" s="3">
         <v>595200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>594900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>748100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>716700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1018200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>991200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>886200</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N62" s="3">
         <v>1379500</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R62" s="3">
         <v>2010300</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U62" s="3">
+      <c r="U62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W62" s="3">
         <v>1685900</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y62" s="3">
         <v>1930800</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA62" s="3">
         <v>2399700</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC62" s="3">
         <v>2432700</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE62" s="3">
         <v>2532700</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG62" s="3">
         <v>3021700</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI62" s="3">
         <v>3253300</v>
       </c>
-      <c r="AH62" s="3" t="s">
+      <c r="AJ62" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5952,14 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +6056,14 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6160,118 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>27260700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>29185100</v>
+      </c>
+      <c r="F66" s="3">
         <v>27620200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>27602400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>29028500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>27810600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>28451800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>27698200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>29715200</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N66" s="3">
         <v>40082900</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P66" s="3">
+      <c r="P66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R66" s="3">
         <v>37750900</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U66" s="3">
+      <c r="U66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W66" s="3">
         <v>43042600</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y66" s="3">
         <v>34961600</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA66" s="3">
         <v>32340200</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC66" s="3">
         <v>30603800</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE66" s="3">
         <v>31532300</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG66" s="3">
         <v>31753700</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI66" s="3">
         <v>33240800</v>
       </c>
-      <c r="AH66" s="3" t="s">
+      <c r="AJ66" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6306,10 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6406,14 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6510,14 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6614,14 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6718,118 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3539200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3789000</v>
+      </c>
+      <c r="F72" s="3">
         <v>4559800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>4556800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>4443400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>4256900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>4898300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>4768500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>4530000</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N72" s="3">
         <v>6567300</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R72" s="3">
         <v>10018900</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W72" s="3">
         <v>11619500</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y72" s="3">
         <v>13918500</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA72" s="3">
         <v>13121900</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC72" s="3">
         <v>13135200</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE72" s="3">
         <v>12986500</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG72" s="3">
         <v>12828500</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI72" s="3">
         <v>12629500</v>
       </c>
-      <c r="AH72" s="3" t="s">
+      <c r="AJ72" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6926,14 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +7030,14 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +7134,118 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4350400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4657600</v>
+      </c>
+      <c r="F76" s="3">
         <v>4419500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4416600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>4299700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>4119300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>4622100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>4499700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>4435000</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N76" s="3">
         <v>6033800</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P76" s="3">
+      <c r="P76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R76" s="3">
         <v>9451700</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U76" s="3">
+      <c r="U76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W76" s="3">
         <v>10970900</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y76" s="3">
         <v>13226200</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA76" s="3">
         <v>12391900</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC76" s="3">
         <v>12383200</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE76" s="3">
         <v>12374400</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG76" s="3">
         <v>12278000</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI76" s="3">
         <v>12278400</v>
       </c>
-      <c r="AH76" s="3" t="s">
+      <c r="AJ76" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7342,227 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>210900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>225800</v>
+      </c>
+      <c r="F81" s="3">
         <v>129500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>129500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>71200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>69300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>255900</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N81" s="3">
         <v>328800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>490900</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q81" s="3">
         <v>313600</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S81" s="3">
         <v>-398300</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U81" s="3">
         <v>-3923200</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W81" s="3">
         <v>741800</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y81" s="3">
         <v>429000</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA81" s="3">
         <v>515800</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC81" s="3">
         <v>869300</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE81" s="3">
         <v>1591900</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG81" s="3">
         <v>777500</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI81" s="3">
         <v>1520000</v>
       </c>
-      <c r="AH81" s="3" t="s">
+      <c r="AJ81" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7597,114 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>133000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>127500</v>
+      </c>
+      <c r="F83" s="3">
         <v>135300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>131800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>132100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>122200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>127500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>137900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>144600</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3">
         <v>-357800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>665500</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S83" s="3">
         <v>710500</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W83" s="3">
         <v>429900</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y83" s="3">
         <v>468900</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA83" s="3">
         <v>412000</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC83" s="3">
         <v>249800</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE83" s="3">
         <v>277000</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG83" s="3">
         <v>278300</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI83" s="3">
         <v>275200</v>
       </c>
-      <c r="AH83" s="3" t="s">
+      <c r="AJ83" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7801,14 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7905,14 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +8009,14 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +8113,14 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8217,118 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1219400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1305500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-341200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-341000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1071400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>1026500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-282800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-275300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1104500</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N89" s="3">
         <v>-4008400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>2592000</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S89" s="3">
         <v>2450400</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W89" s="3">
         <v>2696100</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-173600</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA89" s="3">
         <v>2140900</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC89" s="3">
         <v>94200</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE89" s="3">
         <v>1724900</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG89" s="3">
         <v>111600</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI89" s="3">
         <v>2248600</v>
       </c>
-      <c r="AH89" s="3" t="s">
+      <c r="AJ89" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8363,114 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-67000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-71700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-51800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-51800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-61500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-58900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-51500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-50100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-63900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-132200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-132200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-140500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-140500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-227100</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S91" s="3">
         <v>-260300</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W91" s="3">
         <v>-263800</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-200300</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-207100</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-204300</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-246400</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-130400</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-187600</v>
       </c>
-      <c r="AH91" s="3" t="s">
+      <c r="AJ91" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8567,14 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8671,118 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>242900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>260000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-69500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-69500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-58800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-56400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-183000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-178100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-147400</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
         <v>581700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-818900</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S94" s="3">
         <v>-199900</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W94" s="3">
         <v>2316500</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y94" s="3">
         <v>83800</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-34200</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC94" s="3">
         <v>272000</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-238300</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-413500</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-790700</v>
       </c>
-      <c r="AH94" s="3" t="s">
+      <c r="AJ94" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,106 +8817,114 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="D96" s="3">
+        <v>266000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>284800</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3">
         <v>269300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>258000</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L96" s="3">
         <v>220100</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-401300</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-145500</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-1023500</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-987200</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-980200</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-811800</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AJ96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +9021,14 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +9125,14 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +9229,322 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1115500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1194200</v>
+      </c>
+      <c r="F100" s="3">
         <v>501100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>500800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-780200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-747500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>204000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>198600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-643700</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3">
         <v>1548600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-2622900</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S100" s="3">
         <v>-298700</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W100" s="3">
         <v>-3561900</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-426000</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-1759300</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-364300</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-1706200</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG100" s="3">
         <v>681500</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI100" s="3">
         <v>-1132700</v>
       </c>
-      <c r="AH100" s="3" t="s">
+      <c r="AJ100" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="F101" s="3">
         <v>-37500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-36500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-14300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-13300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>53500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>57800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-18600</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3">
         <v>278100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-165900</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S101" s="3">
         <v>-118300</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W101" s="3">
         <v>-138300</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y101" s="3">
         <v>16100</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA101" s="3">
         <v>21900</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-101000</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE101" s="3">
         <v>-58700</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG101" s="3">
         <v>23200</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI101" s="3">
         <v>71900</v>
       </c>
-      <c r="AH101" s="3" t="s">
+      <c r="AJ101" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>327400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>350500</v>
+      </c>
+      <c r="F102" s="3">
         <v>53100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>53000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>219200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>210000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-299300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-291300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>299100</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N102" s="3">
         <v>-1600000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1015600</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S102" s="3">
         <v>1833500</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W102" s="3">
         <v>1312400</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-499700</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA102" s="3">
         <v>369300</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-99000</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE102" s="3">
         <v>-278200</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG102" s="3">
         <v>402900</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI102" s="3">
         <v>397000</v>
       </c>
-      <c r="AH102" s="3" t="s">
+      <c r="AJ102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WPP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WPP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="92">
   <si>
     <t>WPP</t>
   </si>
@@ -820,10 +820,10 @@
         <v>4563800</v>
       </c>
       <c r="H8" s="3">
-        <v>4855300</v>
+        <v>4855600</v>
       </c>
       <c r="I8" s="3">
-        <v>4651600</v>
+        <v>4651800</v>
       </c>
       <c r="J8" s="3">
         <v>4588200</v>
@@ -924,10 +924,10 @@
         <v>3907000</v>
       </c>
       <c r="H9" s="3">
-        <v>3928800</v>
+        <v>3928900</v>
       </c>
       <c r="I9" s="3">
-        <v>3763900</v>
+        <v>3764100</v>
       </c>
       <c r="J9" s="3">
         <v>3912100</v>
@@ -1028,10 +1028,10 @@
         <v>656700</v>
       </c>
       <c r="H10" s="3">
-        <v>926500</v>
+        <v>926700</v>
       </c>
       <c r="I10" s="3">
-        <v>887700</v>
+        <v>887800</v>
       </c>
       <c r="J10" s="3">
         <v>676100</v>
@@ -1365,11 +1365,11 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E14" s="3">
+        <v>18800</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
@@ -1378,10 +1378,10 @@
         <v>5</v>
       </c>
       <c r="H14" s="3">
-        <v>-18100</v>
+        <v>-27400</v>
       </c>
       <c r="I14" s="3">
-        <v>-17300</v>
+        <v>-26200</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>5</v>
@@ -1482,10 +1482,10 @@
         <v>83400</v>
       </c>
       <c r="H15" s="3">
-        <v>88100</v>
+        <v>89800</v>
       </c>
       <c r="I15" s="3">
-        <v>84400</v>
+        <v>86000</v>
       </c>
       <c r="J15" s="3">
         <v>80700</v>
@@ -1609,10 +1609,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4138900</v>
+        <v>4145100</v>
       </c>
       <c r="E17" s="3">
-        <v>4431000</v>
+        <v>4437700</v>
       </c>
       <c r="F17" s="3">
         <v>4299400</v>
@@ -1713,10 +1713,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>564600</v>
+        <v>558400</v>
       </c>
       <c r="E18" s="3">
-        <v>604500</v>
+        <v>597800</v>
       </c>
       <c r="F18" s="3">
         <v>267300</v>
@@ -1725,10 +1725,10 @@
         <v>267100</v>
       </c>
       <c r="H18" s="3">
-        <v>136700</v>
+        <v>136900</v>
       </c>
       <c r="I18" s="3">
-        <v>130900</v>
+        <v>131200</v>
       </c>
       <c r="J18" s="3">
         <v>194400</v>
@@ -1855,10 +1855,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>40700</v>
+        <v>16300</v>
       </c>
       <c r="E20" s="3">
-        <v>43600</v>
+        <v>17400</v>
       </c>
       <c r="F20" s="3">
         <v>-32200</v>
@@ -1867,10 +1867,10 @@
         <v>-32200</v>
       </c>
       <c r="H20" s="3">
-        <v>-14100</v>
+        <v>-13400</v>
       </c>
       <c r="I20" s="3">
-        <v>-13500</v>
+        <v>-12800</v>
       </c>
       <c r="J20" s="3">
         <v>-16500</v>
@@ -1959,10 +1959,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>604700</v>
+        <v>622800</v>
       </c>
       <c r="E21" s="3">
-        <v>647400</v>
+        <v>666800</v>
       </c>
       <c r="F21" s="3">
         <v>382900</v>
@@ -1971,10 +1971,10 @@
         <v>382700</v>
       </c>
       <c r="H21" s="3">
-        <v>238900</v>
+        <v>240100</v>
       </c>
       <c r="I21" s="3">
-        <v>228900</v>
+        <v>230000</v>
       </c>
       <c r="J21" s="3">
         <v>291600</v>
@@ -2063,10 +2063,10 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>129600</v>
+        <v>123300</v>
       </c>
       <c r="E22" s="3">
-        <v>138700</v>
+        <v>132000</v>
       </c>
       <c r="F22" s="3">
         <v>132700</v>
@@ -2491,10 +2491,10 @@
         <v>155300</v>
       </c>
       <c r="H26" s="3">
-        <v>30500</v>
+        <v>30600</v>
       </c>
       <c r="I26" s="3">
-        <v>29200</v>
+        <v>29300</v>
       </c>
       <c r="J26" s="3">
         <v>94700</v>
@@ -2595,10 +2595,10 @@
         <v>129500</v>
       </c>
       <c r="H27" s="3">
-        <v>-1000</v>
+        <v>-1300</v>
       </c>
       <c r="I27" s="3">
-        <v>-1000</v>
+        <v>-1200</v>
       </c>
       <c r="J27" s="3">
         <v>71200</v>
@@ -3103,10 +3103,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-40700</v>
+        <v>-16300</v>
       </c>
       <c r="E32" s="3">
-        <v>-43600</v>
+        <v>-17400</v>
       </c>
       <c r="F32" s="3">
         <v>32200</v>
@@ -3115,10 +3115,10 @@
         <v>32200</v>
       </c>
       <c r="H32" s="3">
-        <v>14100</v>
+        <v>13400</v>
       </c>
       <c r="I32" s="3">
-        <v>13500</v>
+        <v>12800</v>
       </c>
       <c r="J32" s="3">
         <v>16500</v>
@@ -3219,10 +3219,10 @@
         <v>129500</v>
       </c>
       <c r="H33" s="3">
-        <v>-1000</v>
+        <v>-1300</v>
       </c>
       <c r="I33" s="3">
-        <v>-1000</v>
+        <v>-1200</v>
       </c>
       <c r="J33" s="3">
         <v>71200</v>
@@ -3427,10 +3427,10 @@
         <v>129500</v>
       </c>
       <c r="H35" s="3">
-        <v>-1000</v>
+        <v>-1300</v>
       </c>
       <c r="I35" s="3">
-        <v>-1000</v>
+        <v>-1200</v>
       </c>
       <c r="J35" s="3">
         <v>71200</v>
@@ -3704,10 +3704,10 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2482600</v>
+        <v>3302600</v>
       </c>
       <c r="E41" s="3">
-        <v>2657800</v>
+        <v>3535700</v>
       </c>
       <c r="F41" s="3">
         <v>2689300</v>
@@ -3716,10 +3716,10 @@
         <v>2687600</v>
       </c>
       <c r="H41" s="3">
-        <v>2594400</v>
+        <v>2825200</v>
       </c>
       <c r="I41" s="3">
-        <v>2485500</v>
+        <v>2706700</v>
       </c>
       <c r="J41" s="3">
         <v>2494100</v>
@@ -3808,10 +3808,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>820000</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>877900</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -3820,10 +3820,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>230200</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>220500</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -3924,10 +3924,10 @@
         <v>14204700</v>
       </c>
       <c r="H43" s="3">
-        <v>14629700</v>
+        <v>14630400</v>
       </c>
       <c r="I43" s="3">
-        <v>14015900</v>
+        <v>14016500</v>
       </c>
       <c r="J43" s="3">
         <v>13801800</v>
@@ -4132,10 +4132,10 @@
         <v>5</v>
       </c>
       <c r="H45" s="3">
-        <v>2000</v>
+        <v>1300</v>
       </c>
       <c r="I45" s="3">
-        <v>2000</v>
+        <v>1200</v>
       </c>
       <c r="J45" s="3">
         <v>3000</v>
@@ -4236,10 +4236,10 @@
         <v>16892300</v>
       </c>
       <c r="H46" s="3">
-        <v>17760700</v>
+        <v>17761200</v>
       </c>
       <c r="I46" s="3">
-        <v>17015600</v>
+        <v>17016100</v>
       </c>
       <c r="J46" s="3">
         <v>16687400</v>
@@ -4340,10 +4340,10 @@
         <v>711100</v>
       </c>
       <c r="H47" s="3">
-        <v>788700</v>
+        <v>789700</v>
       </c>
       <c r="I47" s="3">
-        <v>755600</v>
+        <v>756600</v>
       </c>
       <c r="J47" s="3">
         <v>738300</v>
@@ -4444,10 +4444,10 @@
         <v>2711600</v>
       </c>
       <c r="H48" s="3">
-        <v>2815900</v>
+        <v>2815000</v>
       </c>
       <c r="I48" s="3">
-        <v>2697800</v>
+        <v>2696900</v>
       </c>
       <c r="J48" s="3">
         <v>3046000</v>
@@ -4548,10 +4548,10 @@
         <v>11541100</v>
       </c>
       <c r="H49" s="3">
-        <v>11768000</v>
+        <v>11768200</v>
       </c>
       <c r="I49" s="3">
-        <v>11274300</v>
+        <v>11274500</v>
       </c>
       <c r="J49" s="3">
         <v>12450900</v>
@@ -4860,10 +4860,10 @@
         <v>315700</v>
       </c>
       <c r="H52" s="3">
-        <v>363900</v>
+        <v>364300</v>
       </c>
       <c r="I52" s="3">
-        <v>348600</v>
+        <v>349000</v>
       </c>
       <c r="J52" s="3">
         <v>329400</v>
@@ -5068,10 +5068,10 @@
         <v>32601200</v>
       </c>
       <c r="H54" s="3">
-        <v>33910400</v>
+        <v>33911200</v>
       </c>
       <c r="I54" s="3">
-        <v>32487700</v>
+        <v>32488500</v>
       </c>
       <c r="J54" s="3">
         <v>33617700</v>
@@ -5248,10 +5248,10 @@
         <v>15044600</v>
       </c>
       <c r="H57" s="3">
-        <v>13789300</v>
+        <v>13789700</v>
       </c>
       <c r="I57" s="3">
-        <v>13210800</v>
+        <v>13211100</v>
       </c>
       <c r="J57" s="3">
         <v>11883300</v>
@@ -5352,10 +5352,10 @@
         <v>1849000</v>
       </c>
       <c r="H58" s="3">
-        <v>1577700</v>
+        <v>1576900</v>
       </c>
       <c r="I58" s="3">
-        <v>1511500</v>
+        <v>1510800</v>
       </c>
       <c r="J58" s="3">
         <v>1767800</v>
@@ -5456,10 +5456,10 @@
         <v>2035900</v>
       </c>
       <c r="H59" s="3">
-        <v>5332600</v>
+        <v>5402000</v>
       </c>
       <c r="I59" s="3">
-        <v>5108900</v>
+        <v>5175400</v>
       </c>
       <c r="J59" s="3">
         <v>5246900</v>
@@ -5560,10 +5560,10 @@
         <v>18929500</v>
       </c>
       <c r="H60" s="3">
-        <v>20699500</v>
+        <v>20768600</v>
       </c>
       <c r="I60" s="3">
-        <v>19831100</v>
+        <v>19897200</v>
       </c>
       <c r="J60" s="3">
         <v>18898000</v>
@@ -5664,10 +5664,10 @@
         <v>7676400</v>
       </c>
       <c r="H61" s="3">
-        <v>7180400</v>
+        <v>7180200</v>
       </c>
       <c r="I61" s="3">
-        <v>6879200</v>
+        <v>6878900</v>
       </c>
       <c r="J61" s="3">
         <v>7934700</v>
@@ -5768,10 +5768,10 @@
         <v>594900</v>
       </c>
       <c r="H62" s="3">
-        <v>748100</v>
+        <v>678900</v>
       </c>
       <c r="I62" s="3">
-        <v>716700</v>
+        <v>650400</v>
       </c>
       <c r="J62" s="3">
         <v>1018200</v>
@@ -6184,10 +6184,10 @@
         <v>27602400</v>
       </c>
       <c r="H66" s="3">
-        <v>29028500</v>
+        <v>29028900</v>
       </c>
       <c r="I66" s="3">
-        <v>27810600</v>
+        <v>27811000</v>
       </c>
       <c r="J66" s="3">
         <v>28451800</v>
@@ -6730,10 +6730,10 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>3539200</v>
+        <v>3096000</v>
       </c>
       <c r="E72" s="3">
-        <v>3789000</v>
+        <v>3314600</v>
       </c>
       <c r="F72" s="3">
         <v>4559800</v>
@@ -6742,10 +6742,10 @@
         <v>4556800</v>
       </c>
       <c r="H72" s="3">
-        <v>4443400</v>
+        <v>4000900</v>
       </c>
       <c r="I72" s="3">
-        <v>4256900</v>
+        <v>3833000</v>
       </c>
       <c r="J72" s="3">
         <v>4898300</v>
@@ -7158,10 +7158,10 @@
         <v>4416600</v>
       </c>
       <c r="H76" s="3">
-        <v>4299700</v>
+        <v>4300200</v>
       </c>
       <c r="I76" s="3">
-        <v>4119300</v>
+        <v>4119800</v>
       </c>
       <c r="J76" s="3">
         <v>4622100</v>
@@ -7475,10 +7475,10 @@
         <v>129500</v>
       </c>
       <c r="H81" s="3">
-        <v>-1000</v>
+        <v>-1300</v>
       </c>
       <c r="I81" s="3">
-        <v>-1000</v>
+        <v>-1200</v>
       </c>
       <c r="J81" s="3">
         <v>71200</v>
@@ -7605,7 +7605,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>133000</v>
+        <v>133100</v>
       </c>
       <c r="E83" s="3">
         <v>127500</v>
@@ -7617,7 +7617,7 @@
         <v>131800</v>
       </c>
       <c r="H83" s="3">
-        <v>132100</v>
+        <v>132000</v>
       </c>
       <c r="I83" s="3">
         <v>122200</v>
@@ -8241,10 +8241,10 @@
         <v>-341000</v>
       </c>
       <c r="H89" s="3">
-        <v>1071400</v>
+        <v>1071900</v>
       </c>
       <c r="I89" s="3">
-        <v>1026500</v>
+        <v>1026900</v>
       </c>
       <c r="J89" s="3">
         <v>-282800</v>
@@ -8383,10 +8383,10 @@
         <v>-51800</v>
       </c>
       <c r="H91" s="3">
-        <v>-61500</v>
+        <v>-61100</v>
       </c>
       <c r="I91" s="3">
-        <v>-58900</v>
+        <v>-58600</v>
       </c>
       <c r="J91" s="3">
         <v>-51500</v>
@@ -8695,10 +8695,10 @@
         <v>-69500</v>
       </c>
       <c r="H94" s="3">
-        <v>-58800</v>
+        <v>-58600</v>
       </c>
       <c r="I94" s="3">
-        <v>-56400</v>
+        <v>-56100</v>
       </c>
       <c r="J94" s="3">
         <v>-183000</v>
@@ -8837,10 +8837,10 @@
         <v>5</v>
       </c>
       <c r="H96" s="3">
-        <v>269300</v>
+        <v>269400</v>
       </c>
       <c r="I96" s="3">
-        <v>258000</v>
+        <v>258100</v>
       </c>
       <c r="J96" s="3" t="s">
         <v>5</v>
@@ -9256,7 +9256,7 @@
         <v>-780200</v>
       </c>
       <c r="I100" s="3">
-        <v>-747500</v>
+        <v>-747400</v>
       </c>
       <c r="J100" s="3">
         <v>204000</v>
@@ -9345,10 +9345,10 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-13100</v>
+        <v>-13400</v>
       </c>
       <c r="E101" s="3">
-        <v>-12600</v>
+        <v>-12800</v>
       </c>
       <c r="F101" s="3">
         <v>-37500</v>
@@ -9357,7 +9357,7 @@
         <v>-36500</v>
       </c>
       <c r="H101" s="3">
-        <v>-14300</v>
+        <v>-14600</v>
       </c>
       <c r="I101" s="3">
         <v>-13300</v>
@@ -9461,10 +9461,10 @@
         <v>53000</v>
       </c>
       <c r="H102" s="3">
-        <v>219200</v>
+        <v>219700</v>
       </c>
       <c r="I102" s="3">
-        <v>210000</v>
+        <v>210500</v>
       </c>
       <c r="J102" s="3">
         <v>-299300</v>

--- a/AAII_Financials/Quarterly/WPP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WPP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="92">
   <si>
     <t>WPP</t>
   </si>
@@ -656,466 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4564300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>4304300</v>
+      </c>
+      <c r="F8" s="3">
         <v>4703500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>5035500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>4566700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>4563800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>4855600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>4651800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>4588200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>4466700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>4622800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>4572000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>8613700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>8503100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>4106100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>7609200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>3454700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>7656000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>3512000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>6810300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>3811700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>9363600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>5576900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>8744700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>4927000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>7335700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>4628400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>9686600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>4595900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>10635100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>4759400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>9978500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>4831200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>10340000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>4754900</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3991000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3763600</v>
+      </c>
+      <c r="F9" s="3">
         <v>3820200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>4089900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>3909500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>3907000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>3928900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>3764100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>3912100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>3808500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>3724300</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="3">
         <v>7278400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>6887300</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3">
         <v>6447300</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U9" s="3">
         <v>6181000</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W9" s="3">
         <v>5861300</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y9" s="3">
         <v>7495800</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA9" s="3">
         <v>7317500</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC9" s="3">
         <v>5732800</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE9" s="3">
         <v>8039600</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG9" s="3">
         <v>8278100</v>
       </c>
-      <c r="AF9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI9" s="3">
         <v>8194100</v>
       </c>
-      <c r="AH9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK9" s="3">
         <v>13701700</v>
       </c>
-      <c r="AJ9" s="3" t="s">
+      <c r="AL9" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>573400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>540700</v>
+      </c>
+      <c r="F10" s="3">
         <v>883200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>945600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>657200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>656700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>926700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>887800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>676100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>658200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>898500</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="3">
         <v>1335300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1615800</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3">
         <v>1161900</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U10" s="3">
         <v>1475000</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W10" s="3">
         <v>949100</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y10" s="3">
         <v>1867800</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA10" s="3">
         <v>1427300</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC10" s="3">
         <v>1602900</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE10" s="3">
         <v>1647000</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="3">
         <v>2357000</v>
       </c>
-      <c r="AF10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI10" s="3">
         <v>1784400</v>
       </c>
-      <c r="AH10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK10" s="3">
         <v>-3361800</v>
       </c>
-      <c r="AJ10" s="3" t="s">
+      <c r="AL10" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1152,8 +1178,10 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1256,8 +1284,14 @@
       <c r="AJ12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1360,148 +1394,160 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>17500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>18800</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>-27400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-26200</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>-24900</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
         <v>97000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>94400</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3">
         <v>-14500</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="3">
         <v>112900</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W14" s="3">
         <v>62700</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y14" s="3">
         <v>46600</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA14" s="3">
         <v>18700</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC14" s="3">
         <v>17300</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE14" s="3">
         <v>36700</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI14" s="3">
         <v>25300</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK14" s="3">
         <v>-295800</v>
       </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AL14" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>91800</v>
+      </c>
+      <c r="E15" s="3">
+        <v>86600</v>
+      </c>
+      <c r="F15" s="3">
         <v>80700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>86400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>83400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>83400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>89800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>86000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>80700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>78600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>75000</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
@@ -1538,11 +1584,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB15" s="3" t="s">
-        <v>5</v>
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>0</v>
       </c>
       <c r="AC15" s="3" t="s">
         <v>5</v>
@@ -1556,20 +1602,26 @@
       <c r="AF15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AG15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI15" s="3">
         <v>127600</v>
       </c>
-      <c r="AH15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK15" s="3">
         <v>119600</v>
       </c>
-      <c r="AJ15" s="3" t="s">
+      <c r="AL15" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1603,216 +1655,230 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4412900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4161600</v>
+      </c>
+      <c r="F17" s="3">
         <v>4145100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>4437700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>4299400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>4296600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>4718600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>4520700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4393800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4277400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>4132700</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P17" s="3">
         <v>8023800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>7647000</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S17" s="3">
         <v>6994600</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U17" s="3">
         <v>7559900</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W17" s="3">
         <v>10228500</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y17" s="3">
         <v>8456200</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA17" s="3">
         <v>7944600</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC17" s="3">
         <v>6829900</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE17" s="3">
         <v>8634900</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG17" s="3">
         <v>9091000</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI17" s="3">
         <v>9033700</v>
       </c>
-      <c r="AH17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK17" s="3">
         <v>8352300</v>
       </c>
-      <c r="AJ17" s="3" t="s">
+      <c r="AL17" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>151400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>142800</v>
+      </c>
+      <c r="F18" s="3">
         <v>558400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>597800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>267300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>267100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>136900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>131200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>194400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>189300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>490200</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P18" s="3">
         <v>589900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>856100</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S18" s="3">
         <v>614600</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U18" s="3">
         <v>96100</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W18" s="3">
         <v>-3418200</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y18" s="3">
         <v>907500</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA18" s="3">
         <v>800200</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC18" s="3">
         <v>505700</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE18" s="3">
         <v>1051700</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG18" s="3">
         <v>1544000</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI18" s="3">
         <v>944800</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK18" s="3">
         <v>1987700</v>
       </c>
-      <c r="AJ18" s="3" t="s">
+      <c r="AL18" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1849,528 +1915,560 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="F20" s="3">
         <v>16300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>17400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-32200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-32200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-13400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-12800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-16500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-16100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-3000</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3">
         <v>128700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>21900</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S20" s="3">
         <v>57400</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U20" s="3">
         <v>-164900</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W20" s="3">
         <v>-265800</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y20" s="3">
         <v>429700</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA20" s="3">
         <v>3800</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC20" s="3">
         <v>224700</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE20" s="3">
         <v>210900</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG20" s="3">
         <v>361800</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI20" s="3">
         <v>239100</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK20" s="3">
         <v>109800</v>
       </c>
-      <c r="AJ20" s="3" t="s">
+      <c r="AL20" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>247300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>233200</v>
+      </c>
+      <c r="F21" s="3">
         <v>622800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>666800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>382900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>382700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>240100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>230000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>291600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>283900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>568100</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
         <v>352700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>1568900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U21" s="3">
         <v>683700</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y21" s="3">
         <v>1782500</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA21" s="3">
         <v>1298100</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC21" s="3">
         <v>1169300</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE21" s="3">
         <v>1536000</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG21" s="3">
         <v>2206400</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI21" s="3">
         <v>1486100</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK21" s="3">
         <v>2400000</v>
       </c>
-      <c r="AJ21" s="3" t="s">
+      <c r="AL21" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>121900</v>
+      </c>
+      <c r="E22" s="3">
+        <v>115000</v>
+      </c>
+      <c r="F22" s="3">
         <v>123300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>132000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>132700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>132600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>94300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>90300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>146800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>142900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>125700</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P22" s="3">
         <v>184800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>168600</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S22" s="3">
         <v>182600</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U22" s="3">
         <v>180700</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W22" s="3">
         <v>191900</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y22" s="3">
         <v>238900</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA22" s="3">
         <v>242400</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC22" s="3">
         <v>187400</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE22" s="3">
         <v>168200</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG22" s="3">
         <v>171000</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI22" s="3">
         <v>167600</v>
       </c>
-      <c r="AH22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK22" s="3">
         <v>167900</v>
       </c>
-      <c r="AJ22" s="3" t="s">
+      <c r="AL22" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>67100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>63300</v>
+      </c>
+      <c r="F23" s="3">
         <v>433800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>464400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>213600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>213400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>90400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>86600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>129600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>126200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>446500</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P23" s="3">
         <v>533800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>709500</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S23" s="3">
         <v>489400</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U23" s="3">
         <v>-249500</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W23" s="3">
         <v>-3875900</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y23" s="3">
         <v>1098300</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA23" s="3">
         <v>561600</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC23" s="3">
         <v>543000</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE23" s="3">
         <v>1094400</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG23" s="3">
         <v>1734900</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI23" s="3">
         <v>1016300</v>
       </c>
-      <c r="AH23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK23" s="3">
         <v>1929600</v>
       </c>
-      <c r="AJ23" s="3" t="s">
+      <c r="AL23" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E24" s="3">
+        <v>18100</v>
+      </c>
+      <c r="F24" s="3">
         <v>194000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>207700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>58100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>58100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>59900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>57400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>34900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>34000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>160800</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P24" s="3">
         <v>149800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>156800</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S24" s="3">
         <v>132900</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U24" s="3">
         <v>125600</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W24" s="3">
         <v>13300</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y24" s="3">
         <v>226000</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA24" s="3">
         <v>150100</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC24" s="3">
         <v>151900</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE24" s="3">
         <v>182300</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG24" s="3">
         <v>335900</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI24" s="3">
         <v>189800</v>
       </c>
-      <c r="AH24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK24" s="3">
         <v>323700</v>
       </c>
-      <c r="AJ24" s="3" t="s">
+      <c r="AL24" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2473,216 +2571,234 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>45200</v>
+      </c>
+      <c r="F26" s="3">
         <v>239700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>256700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>155400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>155300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>30600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>29300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>94700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>92200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>285700</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P26" s="3">
         <v>383900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>552600</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S26" s="3">
         <v>356500</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U26" s="3">
         <v>-375000</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W26" s="3">
         <v>-3889200</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y26" s="3">
         <v>872300</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA26" s="3">
         <v>411500</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC26" s="3">
         <v>391100</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE26" s="3">
         <v>912100</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG26" s="3">
         <v>1399000</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI26" s="3">
         <v>826500</v>
       </c>
-      <c r="AH26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK26" s="3">
         <v>1606000</v>
       </c>
-      <c r="AJ26" s="3" t="s">
+      <c r="AL26" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>28400</v>
+      </c>
+      <c r="F27" s="3">
         <v>210900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>225800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>129500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>129500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>71200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>69300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>255900</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P27" s="3">
         <v>328800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>490900</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S27" s="3">
         <v>313600</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U27" s="3">
         <v>-414200</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W27" s="3">
         <v>-3914900</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y27" s="3">
         <v>805900</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA27" s="3">
         <v>369700</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC27" s="3">
         <v>348800</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE27" s="3">
         <v>869300</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG27" s="3">
         <v>1323200</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI27" s="3">
         <v>777500</v>
       </c>
-      <c r="AH27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK27" s="3">
         <v>1520000</v>
       </c>
-      <c r="AJ27" s="3" t="s">
+      <c r="AL27" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2785,8 +2901,14 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2817,14 +2939,14 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>5</v>
@@ -2836,50 +2958,50 @@
         <v>5</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U29" s="3">
         <v>15900</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W29" s="3">
         <v>-8300</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-64100</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA29" s="3">
         <v>59300</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="3">
         <v>166900</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG29" s="3">
         <v>268700</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2889,8 +3011,14 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2993,8 +3121,14 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3097,216 +3231,234 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E32" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F32" s="3">
         <v>-16300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-17400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>32200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>32200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>13400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>12800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>16500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>16100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>3000</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3">
         <v>-128700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-21900</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S32" s="3">
         <v>-57400</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U32" s="3">
         <v>164900</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W32" s="3">
         <v>265800</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-429700</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-224700</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-210900</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-361800</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-239100</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK32" s="3">
         <v>-109800</v>
       </c>
-      <c r="AJ32" s="3" t="s">
+      <c r="AL32" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>28400</v>
+      </c>
+      <c r="F33" s="3">
         <v>210900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>225800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>129500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>129500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>71200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>69300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>255900</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P33" s="3">
         <v>328800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>490900</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S33" s="3">
         <v>313600</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U33" s="3">
         <v>-398300</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W33" s="3">
         <v>-3923200</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y33" s="3">
         <v>741800</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA33" s="3">
         <v>429000</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC33" s="3">
         <v>515800</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE33" s="3">
         <v>869300</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG33" s="3">
         <v>1591900</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI33" s="3">
         <v>777500</v>
       </c>
-      <c r="AH33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK33" s="3">
         <v>1520000</v>
       </c>
-      <c r="AJ33" s="3" t="s">
+      <c r="AL33" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3409,221 +3561,239 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>28400</v>
+      </c>
+      <c r="F35" s="3">
         <v>210900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>225800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>129500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>129500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>71200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>69300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>255900</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P35" s="3">
         <v>328800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>490900</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S35" s="3">
         <v>313600</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U35" s="3">
         <v>-398300</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W35" s="3">
         <v>-3923200</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y35" s="3">
         <v>741800</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA35" s="3">
         <v>429000</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC35" s="3">
         <v>515800</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE35" s="3">
         <v>869300</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG35" s="3">
         <v>1591900</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI35" s="3">
         <v>777500</v>
       </c>
-      <c r="AH35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK35" s="3">
         <v>1520000</v>
       </c>
-      <c r="AJ35" s="3" t="s">
+      <c r="AL35" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3660,8 +3830,10 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3698,112 +3870,120 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1968800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1856600</v>
+      </c>
+      <c r="F41" s="3">
         <v>3302600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3535700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2689300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>2687600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2825200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2706700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2494100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>2428000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2737000</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P41" s="3">
         <v>16447600</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R41" s="3">
+      <c r="R41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T41" s="3">
         <v>13482200</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W41" s="3">
+      <c r="W41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y41" s="3">
         <v>15418600</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA41" s="3">
         <v>2984200</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC41" s="3">
         <v>3491100</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE41" s="3">
         <v>2871300</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG41" s="3">
         <v>3119100</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI41" s="3">
         <v>3725100</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK41" s="3">
         <v>2970900</v>
       </c>
-      <c r="AJ41" s="3" t="s">
+      <c r="AL41" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3832,14 +4012,14 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>265000</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
@@ -3888,11 +4068,11 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF42" s="3" t="s">
-        <v>5</v>
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="3">
+        <v>0</v>
       </c>
       <c r="AG42" s="3" t="s">
         <v>5</v>
@@ -3900,118 +4080,130 @@
       <c r="AH42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AI42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK42" s="3">
         <v>237900</v>
       </c>
-      <c r="AJ42" s="3" t="s">
+      <c r="AL42" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14267700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>13455000</v>
+      </c>
+      <c r="F43" s="3">
         <v>13522000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>14476600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>14213900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>14204700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>14630400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>14016500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>13801800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>13436300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>14898600</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P43" s="3">
         <v>13478100</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R43" s="3">
+      <c r="R43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T43" s="3">
         <v>27605700</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W43" s="3">
+      <c r="W43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y43" s="3">
         <v>15478600</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA43" s="3">
         <v>17299200</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC43" s="3">
         <v>16701500</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE43" s="3">
         <v>15659500</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG43" s="3">
         <v>15736500</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI43" s="3">
         <v>14605800</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK43" s="3">
         <v>16171500</v>
       </c>
-      <c r="AJ43" s="3" t="s">
+      <c r="AL43" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4045,597 +4237,633 @@
       <c r="M44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N44" s="3">
+      <c r="N44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P44" s="3">
         <v>336800</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R44" s="3">
+      <c r="R44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T44" s="3">
         <v>416800</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W44" s="3">
+      <c r="W44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y44" s="3">
         <v>476600</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA44" s="3">
         <v>576100</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC44" s="3">
         <v>484100</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE44" s="3">
         <v>524600</v>
       </c>
-      <c r="AD44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG44" s="3">
         <v>1076600</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI44" s="3">
         <v>1113600</v>
       </c>
-      <c r="AH44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK44" s="3">
         <v>527200</v>
       </c>
-      <c r="AJ44" s="3" t="s">
+      <c r="AL44" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3">
         <v>1300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1300</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3">
         <v>1300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>3000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>3000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>6100</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P45" s="3">
         <v>316600</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R45" s="3">
+      <c r="R45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T45" s="3">
         <v>922800</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W45" s="3">
+      <c r="W45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y45" s="3">
         <v>1055300</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA45" s="3">
         <v>550600</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC45" s="3">
         <v>381200</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE45" s="3">
         <v>546200</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG45" s="3">
         <v>390400</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI45" s="3">
         <v>529400</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK45" s="3">
         <v>427600</v>
       </c>
-      <c r="AJ45" s="3" t="s">
+      <c r="AL45" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16236500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>15311600</v>
+      </c>
+      <c r="F46" s="3">
         <v>17102500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>18309900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>16903200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>16892300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>17761200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>17016100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>16687400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>16245400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>18191800</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P46" s="3">
         <v>30579100</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R46" s="3">
+      <c r="R46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T46" s="3">
         <v>28329100</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W46" s="3">
+      <c r="W46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y46" s="3">
         <v>32429200</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA46" s="3">
         <v>21410100</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC46" s="3">
         <v>21057900</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE46" s="3">
         <v>19601700</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG46" s="3">
         <v>19769200</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI46" s="3">
         <v>19395900</v>
       </c>
-      <c r="AH46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK46" s="3">
         <v>20335200</v>
       </c>
-      <c r="AJ46" s="3" t="s">
+      <c r="AL46" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>800100</v>
+      </c>
+      <c r="E47" s="3">
+        <v>754500</v>
+      </c>
+      <c r="F47" s="3">
         <v>815000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>872500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>711500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>711100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>789700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>756600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>738300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>718800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>813200</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P47" s="3">
         <v>947100</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R47" s="3">
+      <c r="R47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T47" s="3">
         <v>1727800</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W47" s="3">
+      <c r="W47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y47" s="3">
         <v>1788300</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA47" s="3">
         <v>1804800</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC47" s="3">
         <v>1933000</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE47" s="3">
         <v>2366400</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG47" s="3">
         <v>2893900</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI47" s="3">
         <v>3138300</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK47" s="3">
         <v>3133600</v>
       </c>
-      <c r="AJ47" s="3" t="s">
+      <c r="AL47" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3064800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2890200</v>
+      </c>
+      <c r="F48" s="3">
         <v>2871900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3074700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2713400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2711600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2815000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2696900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3046000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2965300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3047400</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P48" s="3">
         <v>2926900</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R48" s="3">
+      <c r="R48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T48" s="3">
         <v>3113000</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W48" s="3">
+      <c r="W48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y48" s="3">
         <v>3560200</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA48" s="3">
         <v>3858100</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC48" s="3">
         <v>1430400</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE48" s="3">
         <v>1332600</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG48" s="3">
         <v>1277600</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI48" s="3">
         <v>1213700</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK48" s="3">
         <v>1275600</v>
       </c>
-      <c r="AJ48" s="3" t="s">
+      <c r="AL48" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11061800</v>
+      </c>
+      <c r="E49" s="3">
+        <v>10431700</v>
+      </c>
+      <c r="F49" s="3">
         <v>10449800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>11187500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>11548500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>11541100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>11768200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>11274500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>12450900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>12121100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>11934800</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P49" s="3">
         <v>11193000</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R49" s="3">
+      <c r="R49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T49" s="3">
         <v>13808600</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W49" s="3">
+      <c r="W49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y49" s="3">
         <v>15791900</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA49" s="3">
         <v>20650400</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC49" s="3">
         <v>19871000</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE49" s="3">
         <v>19246300</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG49" s="3">
         <v>19527200</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI49" s="3">
         <v>19816900</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK49" s="3">
         <v>20320200</v>
       </c>
-      <c r="AJ49" s="3" t="s">
+      <c r="AL49" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4738,8 +4966,14 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4842,112 +5076,124 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>471300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>444500</v>
+      </c>
+      <c r="F52" s="3">
         <v>291700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>312300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>315900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>315700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>364300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>349000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>329400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>320700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>352700</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P52" s="3">
         <v>470600</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R52" s="3">
+      <c r="R52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T52" s="3">
         <v>388200</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W52" s="3">
+      <c r="W52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y52" s="3">
         <v>443900</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA52" s="3">
         <v>464300</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC52" s="3">
         <v>439800</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE52" s="3">
         <v>439900</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG52" s="3">
         <v>438900</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI52" s="3">
         <v>466900</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK52" s="3">
         <v>454700</v>
       </c>
-      <c r="AJ52" s="3" t="s">
+      <c r="AL52" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5050,112 +5296,124 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>32051000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>30225200</v>
+      </c>
+      <c r="F54" s="3">
         <v>31935400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>34189800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>32622200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>32601200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>33911200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>32488500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>33617700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>32727300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>34728000</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P54" s="3">
         <v>46116700</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R54" s="3">
+      <c r="R54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T54" s="3">
         <v>47202600</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W54" s="3">
+      <c r="W54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y54" s="3">
         <v>54013400</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA54" s="3">
         <v>48187700</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC54" s="3">
         <v>44732100</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE54" s="3">
         <v>42987000</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG54" s="3">
         <v>43906700</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI54" s="3">
         <v>44031700</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK54" s="3">
         <v>45519200</v>
       </c>
-      <c r="AJ54" s="3" t="s">
+      <c r="AL54" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5192,8 +5450,10 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5230,478 +5490,504 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15162400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>14298600</v>
+      </c>
+      <c r="F57" s="3">
         <v>13316700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>14256800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>15054300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>15044600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>13789700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>13211100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>11883300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>11568600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>13473500</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P57" s="3">
         <v>13088000</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R57" s="3">
+      <c r="R57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T57" s="3">
         <v>29450100</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W57" s="3">
+      <c r="W57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y57" s="3">
         <v>14330400</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA57" s="3">
         <v>13887500</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC57" s="3">
         <v>14096100</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE57" s="3">
         <v>12676500</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG57" s="3">
         <v>13139200</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI57" s="3">
         <v>12223200</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK57" s="3">
         <v>13939300</v>
       </c>
-      <c r="AJ57" s="3" t="s">
+      <c r="AL57" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1586500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1496100</v>
+      </c>
+      <c r="F58" s="3">
         <v>1031600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1104400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1850200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1849000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1576900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1510800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1767800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1721000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1748800</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P58" s="3">
         <v>11403200</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R58" s="3">
+      <c r="R58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T58" s="3">
         <v>21343800</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W58" s="3">
+      <c r="W58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y58" s="3">
         <v>12732200</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA58" s="3">
         <v>2091600</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC58" s="3">
         <v>1353900</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE58" s="3">
         <v>413100</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG58" s="3">
         <v>1628000</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI58" s="3">
         <v>2433800</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK58" s="3">
         <v>1320100</v>
       </c>
-      <c r="AJ58" s="3" t="s">
+      <c r="AL58" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2103000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1983200</v>
+      </c>
+      <c r="F59" s="3">
         <v>5076600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>5434900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2037200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2035900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>5402000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>5175400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>5246900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>5107900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>6114300</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P59" s="3">
         <v>5125600</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R59" s="3">
+      <c r="R59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T59" s="3">
         <v>5603100</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y59" s="3">
         <v>6277400</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA59" s="3">
         <v>6517600</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC59" s="3">
         <v>6487500</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE59" s="3">
         <v>6098600</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG59" s="3">
         <v>6282500</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI59" s="3">
         <v>6122800</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK59" s="3">
         <v>6816900</v>
       </c>
-      <c r="AJ59" s="3" t="s">
+      <c r="AL59" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18851900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>17778000</v>
+      </c>
+      <c r="F60" s="3">
         <v>19424900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>20796100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>18941700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>18929500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>20768600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>19897200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>18898000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>18397400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>21336600</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P60" s="3">
         <v>29616900</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R60" s="3">
+      <c r="R60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T60" s="3">
         <v>28685000</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W60" s="3">
+      <c r="W60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y60" s="3">
         <v>32674500</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA60" s="3">
         <v>22496700</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC60" s="3">
         <v>21937500</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE60" s="3">
         <v>19188100</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG60" s="3">
         <v>20235700</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI60" s="3">
         <v>19563000</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK60" s="3">
         <v>22076200</v>
       </c>
-      <c r="AJ60" s="3" t="s">
+      <c r="AL60" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7666800</v>
+      </c>
+      <c r="E61" s="3">
+        <v>7230100</v>
+      </c>
+      <c r="F61" s="3">
         <v>6915600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>7403800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>7681300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>7676400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>7180200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>6878900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>7934700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>7724500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>6904000</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>8680900</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>7148900</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -5709,153 +5995,165 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
         <v>8175600</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>9978600</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>7442400</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>8446400</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
         <v>8152500</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
         <v>8598700</v>
       </c>
-      <c r="AH61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3">
         <v>7327800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>449400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>423800</v>
+      </c>
+      <c r="F62" s="3">
         <v>577100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>617900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>595200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>594900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>678900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>650400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1018200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>991200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>886200</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P62" s="3">
         <v>1379500</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R62" s="3">
+      <c r="R62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T62" s="3">
         <v>2010300</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W62" s="3">
+      <c r="W62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y62" s="3">
         <v>1685900</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA62" s="3">
         <v>1930800</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC62" s="3">
         <v>2399700</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE62" s="3">
         <v>2432700</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG62" s="3">
         <v>2532700</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI62" s="3">
         <v>3021700</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK62" s="3">
         <v>3253300</v>
       </c>
-      <c r="AJ62" s="3" t="s">
+      <c r="AL62" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5958,8 +6256,14 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6062,8 +6366,14 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6166,112 +6476,124 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>27381800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>25822000</v>
+      </c>
+      <c r="F66" s="3">
         <v>27260700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>29185100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>27620200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>27602400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>29028900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>27811000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>28451800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>27698200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>29715200</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P66" s="3">
         <v>40082900</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R66" s="3">
+      <c r="R66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T66" s="3">
         <v>37750900</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W66" s="3">
+      <c r="W66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y66" s="3">
         <v>43042600</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA66" s="3">
         <v>34961600</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC66" s="3">
         <v>32340200</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE66" s="3">
         <v>30603800</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG66" s="3">
         <v>31532300</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI66" s="3">
         <v>31753700</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK66" s="3">
         <v>33240800</v>
       </c>
-      <c r="AJ66" s="3" t="s">
+      <c r="AL66" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6308,8 +6630,10 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6412,8 +6736,14 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6516,8 +6846,14 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6620,8 +6956,14 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6724,112 +7066,124 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3869000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3648600</v>
+      </c>
+      <c r="F72" s="3">
         <v>3096000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>3314600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>4559800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>4556800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>4000900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>3833000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>4898300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>4768500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>4530000</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P72" s="3">
         <v>6567300</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R72" s="3">
+      <c r="R72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T72" s="3">
         <v>10018900</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y72" s="3">
         <v>11619500</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA72" s="3">
         <v>13918500</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC72" s="3">
         <v>13121900</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE72" s="3">
         <v>13135200</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG72" s="3">
         <v>12986500</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI72" s="3">
         <v>12828500</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK72" s="3">
         <v>12629500</v>
       </c>
-      <c r="AJ72" s="3" t="s">
+      <c r="AL72" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6932,8 +7286,14 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7036,8 +7396,14 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7140,112 +7506,124 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4334800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4087900</v>
+      </c>
+      <c r="F76" s="3">
         <v>4350400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4657600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>4419500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>4416600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>4300200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>4119800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>4622100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>4499700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>4435000</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P76" s="3">
         <v>6033800</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R76" s="3">
+      <c r="R76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T76" s="3">
         <v>9451700</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W76" s="3">
+      <c r="W76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y76" s="3">
         <v>10970900</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA76" s="3">
         <v>13226200</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC76" s="3">
         <v>12391900</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE76" s="3">
         <v>12383200</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG76" s="3">
         <v>12374400</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI76" s="3">
         <v>12278000</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK76" s="3">
         <v>12278400</v>
       </c>
-      <c r="AJ76" s="3" t="s">
+      <c r="AL76" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7348,221 +7726,239 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>28400</v>
+      </c>
+      <c r="F81" s="3">
         <v>210900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>225800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>129500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>129500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>71200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>69300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>255900</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P81" s="3">
         <v>328800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>490900</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S81" s="3">
         <v>313600</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U81" s="3">
         <v>-398300</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W81" s="3">
         <v>-3923200</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y81" s="3">
         <v>741800</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA81" s="3">
         <v>429000</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC81" s="3">
         <v>515800</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE81" s="3">
         <v>869300</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG81" s="3">
         <v>1591900</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI81" s="3">
         <v>777500</v>
       </c>
-      <c r="AH81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK81" s="3">
         <v>1520000</v>
       </c>
-      <c r="AJ81" s="3" t="s">
+      <c r="AL81" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7599,112 +7995,120 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>120700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>120600</v>
+      </c>
+      <c r="F83" s="3">
         <v>133100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>127500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>135300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>131800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>132000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>122200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>127500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>137900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>144600</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
         <v>-357800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>665500</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U83" s="3">
         <v>710500</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W83" s="3">
+        <v>0</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y83" s="3">
         <v>429900</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA83" s="3">
         <v>468900</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC83" s="3">
         <v>412000</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE83" s="3">
         <v>249800</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG83" s="3">
         <v>277000</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI83" s="3">
         <v>278300</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK83" s="3">
         <v>275200</v>
       </c>
-      <c r="AJ83" s="3" t="s">
+      <c r="AL83" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7807,8 +8211,14 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7911,8 +8321,14 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8015,8 +8431,14 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8119,8 +8541,14 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8223,112 +8651,124 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-709700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-669300</v>
+      </c>
+      <c r="F89" s="3">
         <v>1219400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1305500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-341200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-341000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1071900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1026900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-282800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-275300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1104500</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3">
         <v>-4008400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>2592000</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U89" s="3">
         <v>2450400</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y89" s="3">
         <v>2696100</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-173600</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC89" s="3">
         <v>2140900</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE89" s="3">
         <v>94200</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG89" s="3">
         <v>1724900</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI89" s="3">
         <v>111600</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK89" s="3">
         <v>2248600</v>
       </c>
-      <c r="AJ89" s="3" t="s">
+      <c r="AL89" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8365,112 +8805,120 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-27100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-67000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-71700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-51800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-51800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-61100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-58600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-51500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-50100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-63900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-132200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-132200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-140500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-140500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-227100</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U91" s="3">
         <v>-260300</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-263800</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-200300</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-207100</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-204300</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-246400</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-130400</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-187600</v>
       </c>
-      <c r="AJ91" s="3" t="s">
+      <c r="AL91" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8573,8 +9021,14 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8677,112 +9131,124 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-143200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-135000</v>
+      </c>
+      <c r="F94" s="3">
         <v>242900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>260000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-69500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-69500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-58600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-56100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-183000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-178100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-147400</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
         <v>581700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-818900</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U94" s="3">
         <v>-199900</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y94" s="3">
         <v>2316500</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA94" s="3">
         <v>83800</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-34200</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE94" s="3">
         <v>272000</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-238300</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-413500</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK94" s="3">
         <v>-790700</v>
       </c>
-      <c r="AJ94" s="3" t="s">
+      <c r="AL94" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8819,112 +9285,120 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3">
         <v>266000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>284800</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3">
         <v>269400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>258100</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N96" s="3">
         <v>220100</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-401300</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-145500</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-1023500</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-987200</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
         <v>0</v>
       </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-980200</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
         <v>0</v>
       </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-811800</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AL96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9027,8 +9501,14 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9131,8 +9611,14 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9235,316 +9721,340 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1115500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-1194200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>501100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>500800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-780200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-747400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>204000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>198600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-643700</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
         <v>1548600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-2622900</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U100" s="3">
         <v>-298700</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-3561900</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-426000</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-1759300</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-364300</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-1706200</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI100" s="3">
         <v>681500</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK100" s="3">
         <v>-1132700</v>
       </c>
-      <c r="AJ100" s="3" t="s">
+      <c r="AL100" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-37300</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-37300</v>
+      </c>
+      <c r="F101" s="3">
         <v>-13400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-12800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-37500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-36500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-14600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-13300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>53500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>57800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-18600</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
         <v>278100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-165900</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U101" s="3">
         <v>-118300</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-138300</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA101" s="3">
         <v>16100</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC101" s="3">
         <v>21900</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE101" s="3">
         <v>-101000</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG101" s="3">
         <v>-58700</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI101" s="3">
         <v>23200</v>
       </c>
-      <c r="AH101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK101" s="3">
         <v>71900</v>
       </c>
-      <c r="AJ101" s="3" t="s">
+      <c r="AL101" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-889800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-839200</v>
+      </c>
+      <c r="F102" s="3">
         <v>327400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>350500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>53100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>53000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>219700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>210500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-299300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-291300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>299100</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3">
         <v>-1600000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1015600</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U102" s="3">
         <v>1833500</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y102" s="3">
         <v>1312400</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-499700</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC102" s="3">
         <v>369300</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE102" s="3">
         <v>-99000</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG102" s="3">
         <v>-278200</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI102" s="3">
         <v>402900</v>
       </c>
-      <c r="AH102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK102" s="3">
         <v>397000</v>
       </c>
-      <c r="AJ102" s="3" t="s">
+      <c r="AL102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WPP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WPP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="92">
   <si>
     <t>WPP</t>
   </si>
@@ -656,492 +656,517 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AN102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4634600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>4628700</v>
+      </c>
+      <c r="F8" s="3">
         <v>4564300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>4304300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>4703500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>5035500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>4566700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>4563800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>4855600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>4651800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>4588200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>4466700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>4622800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>4572000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>8613700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>8503100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>4106100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>7609200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>3454700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>7656000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>3512000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>6810300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>3811700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>9363600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>5576900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>8744700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>4927000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>7335700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>4628400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>9686600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>4595900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>10635100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>4759400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>9978500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>4831200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>10340000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>4754900</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3753700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3749000</v>
+      </c>
+      <c r="F9" s="3">
         <v>3991000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>3763600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>3820200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>4089900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>3909500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>3907000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>3928900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>3764100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>3912100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>3808500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>3724300</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3">
         <v>7278400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>6887300</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U9" s="3">
         <v>6447300</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W9" s="3">
         <v>6181000</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y9" s="3">
         <v>5861300</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA9" s="3">
         <v>7495800</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC9" s="3">
         <v>7317500</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE9" s="3">
         <v>5732800</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG9" s="3">
         <v>8039600</v>
       </c>
-      <c r="AF9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI9" s="3">
         <v>8278100</v>
       </c>
-      <c r="AH9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK9" s="3">
         <v>8194100</v>
       </c>
-      <c r="AJ9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM9" s="3">
         <v>13701700</v>
       </c>
-      <c r="AL9" s="3" t="s">
+      <c r="AN9" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>880900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>879800</v>
+      </c>
+      <c r="F10" s="3">
         <v>573400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>540700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>883200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>945600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>657200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>656700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>926700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>887800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>676100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>658200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>898500</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3">
         <v>1335300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1615800</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U10" s="3">
         <v>1161900</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W10" s="3">
         <v>1475000</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y10" s="3">
         <v>949100</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA10" s="3">
         <v>1867800</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC10" s="3">
         <v>1427300</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE10" s="3">
         <v>1602900</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="3">
         <v>1647000</v>
       </c>
-      <c r="AF10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI10" s="3">
         <v>2357000</v>
       </c>
-      <c r="AH10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK10" s="3">
         <v>1784400</v>
       </c>
-      <c r="AJ10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM10" s="3">
         <v>-3361800</v>
       </c>
-      <c r="AL10" s="3" t="s">
+      <c r="AN10" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1180,8 +1205,10 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1290,8 +1317,14 @@
       <c r="AL12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,160 +1433,172 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="D14" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
         <v>17500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>18800</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>-27400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-26200</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
         <v>-24900</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>97000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>94400</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="3">
         <v>-14500</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W14" s="3">
         <v>112900</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y14" s="3">
         <v>62700</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA14" s="3">
         <v>46600</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC14" s="3">
         <v>18700</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE14" s="3">
         <v>17300</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG14" s="3">
         <v>36700</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK14" s="3">
         <v>25300</v>
       </c>
-      <c r="AJ14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM14" s="3">
         <v>-295800</v>
       </c>
-      <c r="AL14" s="3" t="s">
+      <c r="AN14" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E15" s="3">
+        <v>34300</v>
+      </c>
+      <c r="F15" s="3">
         <v>91800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>86600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>80700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>86400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>83400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>83400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>89800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>86000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>80700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>78600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>75000</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1590,11 +1635,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD15" s="3" t="s">
-        <v>5</v>
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>0</v>
       </c>
       <c r="AE15" s="3" t="s">
         <v>5</v>
@@ -1608,20 +1653,26 @@
       <c r="AH15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AI15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK15" s="3">
         <v>127600</v>
       </c>
-      <c r="AJ15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM15" s="3">
         <v>119600</v>
       </c>
-      <c r="AL15" s="3" t="s">
+      <c r="AN15" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1708,242 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4532300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4526600</v>
+      </c>
+      <c r="F17" s="3">
         <v>4412900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>4161600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>4145100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>4437700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>4299400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>4296600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4718600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4520700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>4393800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>4277400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>4132700</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="3">
         <v>8023800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>7647000</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U17" s="3">
         <v>6994600</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W17" s="3">
         <v>7559900</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y17" s="3">
         <v>10228500</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA17" s="3">
         <v>8456200</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC17" s="3">
         <v>7944600</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE17" s="3">
         <v>6829900</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG17" s="3">
         <v>8634900</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI17" s="3">
         <v>9091000</v>
       </c>
-      <c r="AH17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK17" s="3">
         <v>9033700</v>
       </c>
-      <c r="AJ17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM17" s="3">
         <v>8352300</v>
       </c>
-      <c r="AL17" s="3" t="s">
+      <c r="AN17" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>102300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>102200</v>
+      </c>
+      <c r="F18" s="3">
         <v>151400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>142800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>558400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>597800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>267300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>267100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>136900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>131200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>194400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>189300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>490200</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="3">
         <v>589900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>856100</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U18" s="3">
         <v>614600</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W18" s="3">
         <v>96100</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-3418200</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA18" s="3">
         <v>907500</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC18" s="3">
         <v>800200</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE18" s="3">
         <v>505700</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG18" s="3">
         <v>1051700</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI18" s="3">
         <v>1544000</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK18" s="3">
         <v>944800</v>
       </c>
-      <c r="AJ18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM18" s="3">
         <v>1987700</v>
       </c>
-      <c r="AL18" s="3" t="s">
+      <c r="AN18" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,558 +1982,590 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-4100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-3900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>16300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>17400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-32200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-32200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-13400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-12800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-16500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-16100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-3000</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>128700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>21900</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U20" s="3">
         <v>57400</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W20" s="3">
         <v>-164900</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-265800</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA20" s="3">
         <v>429700</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC20" s="3">
         <v>3800</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE20" s="3">
         <v>224700</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG20" s="3">
         <v>210900</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI20" s="3">
         <v>361800</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK20" s="3">
         <v>239100</v>
       </c>
-      <c r="AJ20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM20" s="3">
         <v>109800</v>
       </c>
-      <c r="AL20" s="3" t="s">
+      <c r="AN20" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>144700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>144500</v>
+      </c>
+      <c r="F21" s="3">
         <v>247300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>233200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>622800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>666800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>382900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>382700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>240100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>230000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>291600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>283900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>568100</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3">
         <v>352700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1568900</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W21" s="3">
         <v>683700</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA21" s="3">
         <v>1782500</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC21" s="3">
         <v>1298100</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE21" s="3">
         <v>1169300</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG21" s="3">
         <v>1536000</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI21" s="3">
         <v>2206400</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK21" s="3">
         <v>1486100</v>
       </c>
-      <c r="AJ21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM21" s="3">
         <v>2400000</v>
       </c>
-      <c r="AL21" s="3" t="s">
+      <c r="AN21" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>110900</v>
+      </c>
+      <c r="F22" s="3">
         <v>121900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>115000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>123300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>132000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>132700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>132600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>94300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>90300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>146800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>142900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>125700</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R22" s="3">
         <v>184800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>168600</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U22" s="3">
         <v>182600</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W22" s="3">
         <v>180700</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y22" s="3">
         <v>191900</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA22" s="3">
         <v>238900</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC22" s="3">
         <v>242400</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE22" s="3">
         <v>187400</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG22" s="3">
         <v>168200</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI22" s="3">
         <v>171000</v>
       </c>
-      <c r="AH22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK22" s="3">
         <v>167600</v>
       </c>
-      <c r="AJ22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM22" s="3">
         <v>167900</v>
       </c>
-      <c r="AL22" s="3" t="s">
+      <c r="AN22" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>22200</v>
+      </c>
+      <c r="F23" s="3">
         <v>67100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>63300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>433800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>464400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>213600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>213400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>90400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>86600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>129600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>126200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>446500</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R23" s="3">
         <v>533800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>709500</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U23" s="3">
         <v>489400</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W23" s="3">
         <v>-249500</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y23" s="3">
         <v>-3875900</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA23" s="3">
         <v>1098300</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC23" s="3">
         <v>561600</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE23" s="3">
         <v>543000</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG23" s="3">
         <v>1094400</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI23" s="3">
         <v>1734900</v>
       </c>
-      <c r="AH23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK23" s="3">
         <v>1016300</v>
       </c>
-      <c r="AJ23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM23" s="3">
         <v>1929600</v>
       </c>
-      <c r="AL23" s="3" t="s">
+      <c r="AN23" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>185100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>184800</v>
+      </c>
+      <c r="F24" s="3">
         <v>19200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>18100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>194000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>207700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>58100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>58100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>59900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>57400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>34900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>34000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>160800</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" s="3">
         <v>149800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>156800</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U24" s="3">
         <v>132900</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W24" s="3">
         <v>125600</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y24" s="3">
         <v>13300</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA24" s="3">
         <v>226000</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC24" s="3">
         <v>150100</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE24" s="3">
         <v>151900</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG24" s="3">
         <v>182300</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI24" s="3">
         <v>335900</v>
       </c>
-      <c r="AH24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK24" s="3">
         <v>189800</v>
       </c>
-      <c r="AJ24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM24" s="3">
         <v>323700</v>
       </c>
-      <c r="AL24" s="3" t="s">
+      <c r="AN24" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2674,246 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-162900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-162600</v>
+      </c>
+      <c r="F26" s="3">
         <v>48000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>45200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>239700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>256700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>155400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>155300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>30600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>29300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>94700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>92200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>285700</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R26" s="3">
         <v>383900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>552600</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U26" s="3">
         <v>356500</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W26" s="3">
         <v>-375000</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-3889200</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA26" s="3">
         <v>872300</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC26" s="3">
         <v>411500</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE26" s="3">
         <v>391100</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG26" s="3">
         <v>912100</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI26" s="3">
         <v>1399000</v>
       </c>
-      <c r="AH26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK26" s="3">
         <v>826500</v>
       </c>
-      <c r="AJ26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM26" s="3">
         <v>1606000</v>
       </c>
-      <c r="AL26" s="3" t="s">
+      <c r="AN26" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-174300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-174100</v>
+      </c>
+      <c r="F27" s="3">
         <v>30100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>28400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>210900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>225800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>129500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>129500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-1200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>71200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>69300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>255900</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R27" s="3">
         <v>328800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>490900</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U27" s="3">
         <v>313600</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W27" s="3">
         <v>-414200</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-3914900</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA27" s="3">
         <v>805900</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC27" s="3">
         <v>369700</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE27" s="3">
         <v>348800</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG27" s="3">
         <v>869300</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI27" s="3">
         <v>1323200</v>
       </c>
-      <c r="AH27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK27" s="3">
         <v>777500</v>
       </c>
-      <c r="AJ27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM27" s="3">
         <v>1520000</v>
       </c>
-      <c r="AL27" s="3" t="s">
+      <c r="AN27" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +3022,14 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2945,14 +3066,14 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>5</v>
@@ -2964,50 +3085,50 @@
         <v>5</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W29" s="3">
         <v>15900</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-8300</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-64100</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="3">
         <v>59300</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE29" s="3">
         <v>166900</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI29" s="3">
         <v>268700</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3017,8 +3138,14 @@
       <c r="AL29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3254,14 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,228 +3370,246 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E32" s="3">
+        <v>8100</v>
+      </c>
+      <c r="F32" s="3">
         <v>4100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>3900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-16300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-17400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>32200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>32200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>13400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>12800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>16500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>16100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>3000</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>-128700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-21900</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U32" s="3">
         <v>-57400</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W32" s="3">
         <v>164900</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y32" s="3">
         <v>265800</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-429700</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-224700</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-210900</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-361800</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK32" s="3">
         <v>-239100</v>
       </c>
-      <c r="AJ32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM32" s="3">
         <v>-109800</v>
       </c>
-      <c r="AL32" s="3" t="s">
+      <c r="AN32" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-174300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-174100</v>
+      </c>
+      <c r="F33" s="3">
         <v>30100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>28400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>210900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>225800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>129500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>129500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>71200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>69300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>255900</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R33" s="3">
         <v>328800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>490900</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U33" s="3">
         <v>313600</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W33" s="3">
         <v>-398300</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-3923200</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA33" s="3">
         <v>741800</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC33" s="3">
         <v>429000</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE33" s="3">
         <v>515800</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG33" s="3">
         <v>869300</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI33" s="3">
         <v>1591900</v>
       </c>
-      <c r="AH33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK33" s="3">
         <v>777500</v>
       </c>
-      <c r="AJ33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM33" s="3">
         <v>1520000</v>
       </c>
-      <c r="AL33" s="3" t="s">
+      <c r="AN33" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3718,251 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-174300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-174100</v>
+      </c>
+      <c r="F35" s="3">
         <v>30100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>28400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>210900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>225800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>129500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>129500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>71200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>69300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>255900</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R35" s="3">
         <v>328800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>490900</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U35" s="3">
         <v>313600</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W35" s="3">
         <v>-398300</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-3923200</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA35" s="3">
         <v>741800</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC35" s="3">
         <v>429000</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE35" s="3">
         <v>515800</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG35" s="3">
         <v>869300</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI35" s="3">
         <v>1591900</v>
       </c>
-      <c r="AH35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK35" s="3">
         <v>777500</v>
       </c>
-      <c r="AJ35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM35" s="3">
         <v>1520000</v>
       </c>
-      <c r="AL35" s="3" t="s">
+      <c r="AN35" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +4001,10 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,118 +4043,126 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3625800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3621300</v>
+      </c>
+      <c r="F41" s="3">
         <v>1968800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1856600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>3302600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3535700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2689300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2687600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2825200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>2706700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2494100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2428000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2737000</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R41" s="3">
         <v>16447600</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T41" s="3">
+      <c r="T41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V41" s="3">
         <v>13482200</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Y41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA41" s="3">
         <v>15418600</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC41" s="3">
         <v>2984200</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE41" s="3">
         <v>3491100</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG41" s="3">
         <v>2871300</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI41" s="3">
         <v>3119100</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK41" s="3">
         <v>3725100</v>
       </c>
-      <c r="AJ41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM41" s="3">
         <v>2970900</v>
       </c>
-      <c r="AL41" s="3" t="s">
+      <c r="AN41" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4018,14 +4197,14 @@
         <v>0</v>
       </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>265000</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -4074,11 +4253,11 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH42" s="3" t="s">
-        <v>5</v>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
       </c>
       <c r="AI42" s="3" t="s">
         <v>5</v>
@@ -4086,124 +4265,136 @@
       <c r="AJ42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AK42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM42" s="3">
         <v>237900</v>
       </c>
-      <c r="AL42" s="3" t="s">
+      <c r="AN42" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13819700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>13802200</v>
+      </c>
+      <c r="F43" s="3">
         <v>14267700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>13455000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>13522000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>14476600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>14213900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>14204700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>14630400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>14016500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>13801800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>13436300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>14898600</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R43" s="3">
         <v>13478100</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T43" s="3">
+      <c r="T43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V43" s="3">
         <v>27605700</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Y43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA43" s="3">
         <v>15478600</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC43" s="3">
         <v>17299200</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE43" s="3">
         <v>16701500</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG43" s="3">
         <v>15659500</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI43" s="3">
         <v>15736500</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK43" s="3">
         <v>14605800</v>
       </c>
-      <c r="AJ43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM43" s="3">
         <v>16171500</v>
       </c>
-      <c r="AL43" s="3" t="s">
+      <c r="AN43" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4243,627 +4434,663 @@
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P44" s="3">
+      <c r="P44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R44" s="3">
         <v>336800</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T44" s="3">
+      <c r="T44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V44" s="3">
         <v>416800</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Y44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA44" s="3">
         <v>476600</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC44" s="3">
         <v>576100</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE44" s="3">
         <v>484100</v>
       </c>
-      <c r="AD44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG44" s="3">
         <v>524600</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI44" s="3">
         <v>1076600</v>
       </c>
-      <c r="AH44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK44" s="3">
         <v>1113600</v>
       </c>
-      <c r="AJ44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM44" s="3">
         <v>527200</v>
       </c>
-      <c r="AL44" s="3" t="s">
+      <c r="AN44" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="D45" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3">
         <v>1300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>1300</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L45" s="3">
         <v>1300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>3000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>3000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>6100</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R45" s="3">
         <v>316600</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T45" s="3">
+      <c r="T45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V45" s="3">
         <v>922800</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Y45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA45" s="3">
         <v>1055300</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC45" s="3">
         <v>550600</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE45" s="3">
         <v>381200</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG45" s="3">
         <v>546200</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI45" s="3">
         <v>390400</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK45" s="3">
         <v>529400</v>
       </c>
-      <c r="AJ45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM45" s="3">
         <v>427600</v>
       </c>
-      <c r="AL45" s="3" t="s">
+      <c r="AN45" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>17725400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>17703000</v>
+      </c>
+      <c r="F46" s="3">
         <v>16236500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>15311600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>17102500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>18309900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>16903200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>16892300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>17761200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>17016100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>16687400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>16245400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>18191800</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R46" s="3">
         <v>30579100</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T46" s="3">
+      <c r="T46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V46" s="3">
         <v>28329100</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Y46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA46" s="3">
         <v>32429200</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC46" s="3">
         <v>21410100</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE46" s="3">
         <v>21057900</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG46" s="3">
         <v>19601700</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI46" s="3">
         <v>19769200</v>
       </c>
-      <c r="AH46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK46" s="3">
         <v>19395900</v>
       </c>
-      <c r="AJ46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM46" s="3">
         <v>20335200</v>
       </c>
-      <c r="AL46" s="3" t="s">
+      <c r="AN46" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>760400</v>
+      </c>
+      <c r="E47" s="3">
+        <v>759500</v>
+      </c>
+      <c r="F47" s="3">
         <v>800100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>754500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>815000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>872500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>711500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>711100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>789700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>756600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>738300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>718800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>813200</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R47" s="3">
         <v>947100</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T47" s="3">
+      <c r="T47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V47" s="3">
         <v>1727800</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Y47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA47" s="3">
         <v>1788300</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC47" s="3">
         <v>1804800</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE47" s="3">
         <v>1933000</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG47" s="3">
         <v>2366400</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI47" s="3">
         <v>2893900</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK47" s="3">
         <v>3138300</v>
       </c>
-      <c r="AJ47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM47" s="3">
         <v>3133600</v>
       </c>
-      <c r="AL47" s="3" t="s">
+      <c r="AN47" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2747000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2743500</v>
+      </c>
+      <c r="F48" s="3">
         <v>3064800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2890200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2871900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3074700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2713400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2711600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2815000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2696900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3046000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2965300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>3047400</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R48" s="3">
         <v>2926900</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T48" s="3">
+      <c r="T48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V48" s="3">
         <v>3113000</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA48" s="3">
         <v>3560200</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC48" s="3">
         <v>3858100</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE48" s="3">
         <v>1430400</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG48" s="3">
         <v>1332600</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI48" s="3">
         <v>1277600</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK48" s="3">
         <v>1213700</v>
       </c>
-      <c r="AJ48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM48" s="3">
         <v>1275600</v>
       </c>
-      <c r="AL48" s="3" t="s">
+      <c r="AN48" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10336500</v>
+      </c>
+      <c r="E49" s="3">
+        <v>10323400</v>
+      </c>
+      <c r="F49" s="3">
         <v>11061800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>10431700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>10449800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>11187500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>11548500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>11541100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>11768200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>11274500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>12450900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>12121100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>11934800</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R49" s="3">
         <v>11193000</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T49" s="3">
+      <c r="T49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V49" s="3">
         <v>13808600</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Y49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA49" s="3">
         <v>15791900</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC49" s="3">
         <v>20650400</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE49" s="3">
         <v>19871000</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG49" s="3">
         <v>19246300</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI49" s="3">
         <v>19527200</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK49" s="3">
         <v>19816900</v>
       </c>
-      <c r="AJ49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM49" s="3">
         <v>20320200</v>
       </c>
-      <c r="AL49" s="3" t="s">
+      <c r="AN49" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5199,14 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,118 +5315,130 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>440100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>439600</v>
+      </c>
+      <c r="F52" s="3">
         <v>471300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>444500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>291700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>312300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>315900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>315700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>364300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>349000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>329400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>320700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>352700</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R52" s="3">
         <v>470600</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T52" s="3">
+      <c r="T52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V52" s="3">
         <v>388200</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Y52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA52" s="3">
         <v>443900</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC52" s="3">
         <v>464300</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE52" s="3">
         <v>439800</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG52" s="3">
         <v>439900</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI52" s="3">
         <v>438900</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK52" s="3">
         <v>466900</v>
       </c>
-      <c r="AJ52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM52" s="3">
         <v>454700</v>
       </c>
-      <c r="AL52" s="3" t="s">
+      <c r="AN52" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5547,130 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>32402400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>32361500</v>
+      </c>
+      <c r="F54" s="3">
         <v>32051000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>30225200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>31935400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>34189800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>32622200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>32601200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>33911200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>32488500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>33617700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>32727300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>34728000</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R54" s="3">
         <v>46116700</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T54" s="3">
+      <c r="T54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V54" s="3">
         <v>47202600</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Y54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA54" s="3">
         <v>54013400</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC54" s="3">
         <v>48187700</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE54" s="3">
         <v>44732100</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG54" s="3">
         <v>42987000</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI54" s="3">
         <v>43906700</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK54" s="3">
         <v>44031700</v>
       </c>
-      <c r="AJ54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM54" s="3">
         <v>45519200</v>
       </c>
-      <c r="AL54" s="3" t="s">
+      <c r="AN54" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5709,10 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,508 +5751,534 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13549100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>13532000</v>
+      </c>
+      <c r="F57" s="3">
         <v>15162400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>14298600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>13316700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>14256800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>15054300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>15044600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>13789700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>13211100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>11883300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>11568600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>13473500</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R57" s="3">
         <v>13088000</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T57" s="3">
+      <c r="T57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V57" s="3">
         <v>29450100</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA57" s="3">
         <v>14330400</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC57" s="3">
         <v>13887500</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE57" s="3">
         <v>14096100</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG57" s="3">
         <v>12676500</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI57" s="3">
         <v>13139200</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK57" s="3">
         <v>12223200</v>
       </c>
-      <c r="AJ57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM57" s="3">
         <v>13939300</v>
       </c>
-      <c r="AL57" s="3" t="s">
+      <c r="AN57" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1406500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1404700</v>
+      </c>
+      <c r="F58" s="3">
         <v>1586500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1496100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1031600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1104400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1850200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1849000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1576900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1510800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1767800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1721000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1748800</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R58" s="3">
         <v>11403200</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T58" s="3">
+      <c r="T58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V58" s="3">
         <v>21343800</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Y58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA58" s="3">
         <v>12732200</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC58" s="3">
         <v>2091600</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE58" s="3">
         <v>1353900</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG58" s="3">
         <v>413100</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI58" s="3">
         <v>1628000</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK58" s="3">
         <v>2433800</v>
       </c>
-      <c r="AJ58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM58" s="3">
         <v>1320100</v>
       </c>
-      <c r="AL58" s="3" t="s">
+      <c r="AN58" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5010800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>5004400</v>
+      </c>
+      <c r="F59" s="3">
         <v>2103000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1983200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>5076600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>5434900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2037200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2035900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>5402000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>5175400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>5246900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>5107900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>6114300</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R59" s="3">
         <v>5125600</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T59" s="3">
+      <c r="T59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V59" s="3">
         <v>5603100</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA59" s="3">
         <v>6277400</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC59" s="3">
         <v>6517600</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE59" s="3">
         <v>6487500</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG59" s="3">
         <v>6098600</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI59" s="3">
         <v>6282500</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK59" s="3">
         <v>6122800</v>
       </c>
-      <c r="AJ59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM59" s="3">
         <v>6816900</v>
       </c>
-      <c r="AL59" s="3" t="s">
+      <c r="AN59" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19966400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>19941100</v>
+      </c>
+      <c r="F60" s="3">
         <v>18851900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>17778000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>19424900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>20796100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>18941700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>18929500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>20768600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>19897200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>18898000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>18397400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>21336600</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R60" s="3">
         <v>29616900</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T60" s="3">
+      <c r="T60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V60" s="3">
         <v>28685000</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Y60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA60" s="3">
         <v>32674500</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC60" s="3">
         <v>22496700</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE60" s="3">
         <v>21937500</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG60" s="3">
         <v>19188100</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI60" s="3">
         <v>20235700</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK60" s="3">
         <v>19563000</v>
       </c>
-      <c r="AJ60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM60" s="3">
         <v>22076200</v>
       </c>
-      <c r="AL60" s="3" t="s">
+      <c r="AN60" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7788700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>7778900</v>
+      </c>
+      <c r="F61" s="3">
         <v>7666800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>7230100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>6915600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>7403800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>7681300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>7676400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>7180200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>6878900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>7934700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>7724500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>6904000</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>8680900</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>7148900</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -6001,159 +6286,171 @@
         <v>0</v>
       </c>
       <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>8175600</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>9978600</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>7442400</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
         <v>8446400</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
         <v>8152500</v>
       </c>
-      <c r="AH61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3">
         <v>8598700</v>
       </c>
-      <c r="AJ61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM61" s="3">
         <v>7327800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>547800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>547100</v>
+      </c>
+      <c r="F62" s="3">
         <v>449400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>423800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>577100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>617900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>595200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>594900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>678900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>650400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1018200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>991200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>886200</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R62" s="3">
         <v>1379500</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T62" s="3">
+      <c r="T62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V62" s="3">
         <v>2010300</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Y62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA62" s="3">
         <v>1685900</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC62" s="3">
         <v>1930800</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE62" s="3">
         <v>2399700</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG62" s="3">
         <v>2432700</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI62" s="3">
         <v>2532700</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK62" s="3">
         <v>3021700</v>
       </c>
-      <c r="AJ62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM62" s="3">
         <v>3253300</v>
       </c>
-      <c r="AL62" s="3" t="s">
+      <c r="AN62" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6559,14 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6675,14 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6791,130 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>28671600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>28635400</v>
+      </c>
+      <c r="F66" s="3">
         <v>27381800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>25822000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>27260700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>29185100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>27620200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>27602400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>29028900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>27811000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>28451800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>27698200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>29715200</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R66" s="3">
         <v>40082900</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T66" s="3">
+      <c r="T66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V66" s="3">
         <v>37750900</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Y66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA66" s="3">
         <v>43042600</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC66" s="3">
         <v>34961600</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE66" s="3">
         <v>32340200</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG66" s="3">
         <v>30603800</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI66" s="3">
         <v>31532300</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK66" s="3">
         <v>31753700</v>
       </c>
-      <c r="AJ66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM66" s="3">
         <v>33240800</v>
       </c>
-      <c r="AL66" s="3" t="s">
+      <c r="AN66" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6953,10 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +7065,14 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7181,14 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7297,14 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7413,130 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2212700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2209900</v>
+      </c>
+      <c r="F72" s="3">
         <v>3869000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>3648600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>3096000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>3314600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>4559800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>4556800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>4000900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>3833000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>4898300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>4768500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>4530000</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R72" s="3">
         <v>6567300</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V72" s="3">
         <v>10018900</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA72" s="3">
         <v>11619500</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC72" s="3">
         <v>13918500</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE72" s="3">
         <v>13121900</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG72" s="3">
         <v>13135200</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI72" s="3">
         <v>12986500</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK72" s="3">
         <v>12828500</v>
       </c>
-      <c r="AJ72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM72" s="3">
         <v>12629500</v>
       </c>
-      <c r="AL72" s="3" t="s">
+      <c r="AN72" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7645,14 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7761,14 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7877,130 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3418600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3414300</v>
+      </c>
+      <c r="F76" s="3">
         <v>4334800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4087900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>4350400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>4657600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>4419500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>4416600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>4300200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>4119800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>4622100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>4499700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>4435000</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R76" s="3">
         <v>6033800</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T76" s="3">
+      <c r="T76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V76" s="3">
         <v>9451700</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Y76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA76" s="3">
         <v>10970900</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC76" s="3">
         <v>13226200</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE76" s="3">
         <v>12391900</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG76" s="3">
         <v>12383200</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI76" s="3">
         <v>12374400</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK76" s="3">
         <v>12278000</v>
       </c>
-      <c r="AJ76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM76" s="3">
         <v>12278400</v>
       </c>
-      <c r="AL76" s="3" t="s">
+      <c r="AN76" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +8109,251 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-174300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-174100</v>
+      </c>
+      <c r="F81" s="3">
         <v>30100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>28400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>210900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>225800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>129500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>129500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>71200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>69300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>255900</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R81" s="3">
         <v>328800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>490900</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U81" s="3">
         <v>313600</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W81" s="3">
         <v>-398300</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-3923200</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA81" s="3">
         <v>741800</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC81" s="3">
         <v>429000</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE81" s="3">
         <v>515800</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG81" s="3">
         <v>869300</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI81" s="3">
         <v>1591900</v>
       </c>
-      <c r="AH81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK81" s="3">
         <v>777500</v>
       </c>
-      <c r="AJ81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM81" s="3">
         <v>1520000</v>
       </c>
-      <c r="AL81" s="3" t="s">
+      <c r="AN81" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,118 +8392,126 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>111400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>119300</v>
+      </c>
+      <c r="F83" s="3">
         <v>120700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>120600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>133100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>127500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>135300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>131800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>132000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>122200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>127500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>137900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>144600</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
         <v>-357800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>665500</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W83" s="3">
         <v>710500</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W83" s="3">
-        <v>0</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA83" s="3">
         <v>429900</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC83" s="3">
         <v>468900</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE83" s="3">
         <v>412000</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG83" s="3">
         <v>249800</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI83" s="3">
         <v>277000</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK83" s="3">
         <v>278300</v>
       </c>
-      <c r="AJ83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM83" s="3">
         <v>275200</v>
       </c>
-      <c r="AL83" s="3" t="s">
+      <c r="AN83" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8620,14 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8736,14 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8852,14 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8968,14 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +9084,130 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1184400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1182900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-709700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-669300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1219400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>1305500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-341200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-341000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1071900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1026900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-282800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-275300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1104500</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
         <v>-4008400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>2592000</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W89" s="3">
         <v>2450400</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA89" s="3">
         <v>2696100</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-173600</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE89" s="3">
         <v>2140900</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG89" s="3">
         <v>94200</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI89" s="3">
         <v>1724900</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK89" s="3">
         <v>111600</v>
       </c>
-      <c r="AJ89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM89" s="3">
         <v>2248600</v>
       </c>
-      <c r="AL89" s="3" t="s">
+      <c r="AN89" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,118 +9246,126 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-32900</v>
+      </c>
+      <c r="F91" s="3">
         <v>-28800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-27100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-67000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-71700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-51800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-51800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-61100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-58600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-51500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-50100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-63900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-132200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-132200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-140500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-140500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-227100</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W91" s="3">
         <v>-260300</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-263800</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-200300</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-207100</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-204300</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-246400</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-130400</v>
       </c>
-      <c r="AJ91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM91" s="3">
         <v>-187600</v>
       </c>
-      <c r="AL91" s="3" t="s">
+      <c r="AN91" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9474,14 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,118 +9590,130 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-92900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-92700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-143200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-135000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>242900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>260000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-69500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-69500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-58600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-56100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-183000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-178100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-147400</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
         <v>581700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-818900</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W94" s="3">
         <v>-199900</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA94" s="3">
         <v>2316500</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC94" s="3">
         <v>83800</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-34200</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG94" s="3">
         <v>272000</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-238300</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK94" s="3">
         <v>-413500</v>
       </c>
-      <c r="AJ94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM94" s="3">
         <v>-790700</v>
       </c>
-      <c r="AL94" s="3" t="s">
+      <c r="AN94" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,118 +9752,126 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="D96" s="3">
+        <v>230800</v>
+      </c>
+      <c r="E96" s="3">
+        <v>230500</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3">
         <v>266000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>284800</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L96" s="3">
         <v>269400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>258100</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P96" s="3">
         <v>220100</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-401300</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-145500</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-1023500</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-987200</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-980200</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-811800</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AN96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9980,14 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +10096,14 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,334 +10212,358 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-199200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-198900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-15800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-14900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1115500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-1194200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>501100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>500800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-780200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-747400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>204000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>198600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-643700</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
         <v>1548600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-2622900</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W100" s="3">
         <v>-298700</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-3561900</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-426000</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-1759300</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-364300</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI100" s="3">
         <v>-1706200</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK100" s="3">
         <v>681500</v>
       </c>
-      <c r="AJ100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM100" s="3">
         <v>-1132700</v>
       </c>
-      <c r="AL100" s="3" t="s">
+      <c r="AN100" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-20800</v>
+      </c>
+      <c r="F101" s="3">
         <v>-37300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-37300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-13400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-12800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-37500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-36500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-14600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-13300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>53500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>57800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-18600</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
         <v>278100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-165900</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U101" s="3">
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W101" s="3">
         <v>-118300</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-138300</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC101" s="3">
         <v>16100</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE101" s="3">
         <v>21900</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG101" s="3">
         <v>-101000</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-58700</v>
       </c>
-      <c r="AH101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK101" s="3">
         <v>23200</v>
       </c>
-      <c r="AJ101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM101" s="3">
         <v>71900</v>
       </c>
-      <c r="AL101" s="3" t="s">
+      <c r="AN101" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>913900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>912700</v>
+      </c>
+      <c r="F102" s="3">
         <v>-889800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-839200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>327400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>350500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>53100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>53000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>219700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>210500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-299300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-291300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>299100</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3">
         <v>-1600000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1015600</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W102" s="3">
         <v>1833500</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA102" s="3">
         <v>1312400</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-499700</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE102" s="3">
         <v>369300</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG102" s="3">
         <v>-99000</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI102" s="3">
         <v>-278200</v>
       </c>
-      <c r="AH102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK102" s="3">
         <v>402900</v>
       </c>
-      <c r="AJ102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM102" s="3">
         <v>397000</v>
       </c>
-      <c r="AL102" s="3" t="s">
+      <c r="AN102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
